--- a/code/Get_Paper_info/Mt_Paper_filter.xlsx
+++ b/code/Get_Paper_info/Mt_Paper_filter.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="683">
   <si>
     <t>PMID</t>
   </si>
@@ -355,7 +355,7 @@
     <t>BACKGROUND: With D-xylose being the second most abundant sugar in nature, its conversion into products could significantly improve biomass-based process economy. There are two well-studied phosphorylative pathways for D-xylose metabolism. One is isomerase pathway mainly found in bacteria, and the other one is oxo-reductive pathway that always exists in fungi. Except for these two pathways, there are also non-phosphorylative pathways named xylose oxidative pathways and they have several advantages over traditional phosphorylative pathways. In Myceliophthora thermophila, D-xylose can be metabolized through oxo-reductive pathway after plant biomass degradation. The survey of non-phosphorylative pathways in this filamentous fungus will offer a potential way for carbon-efficient production of fuels and chemicals using D-xylose. RESULTS: In this study, an alternative for utilization of D-xylose, the non-phosphorylative Weimberg pathway was established in M. thermophila. Growth on D-xylose of strains whose D-xylose reductase gene was disrupted, was restored after overexpression of the entire Weimberg pathway. During the construction, a native D-xylose dehydrogenase with highest activity in M. thermophila was discovered. Here, M. thermophila was also engineered to produce 1,2,4-butanetriol using D-xylose through non-phosphorylative pathway. Afterwards, transcriptome analysis revealed that the D-xylose dehydrogenase gene was obviously upregulated after deletion of D-xylose reductase gene when cultured in a D-xylose medium. Besides, genes involved in growth were enriched in strains containing the Weimberg pathway. CONCLUSIONS: The Weimberg pathway was established in M. thermophila to support its growth with D-xylose being the sole carbon source. Besides, M. thermophila was engineered to produce 1,2,4-butanetriol using D-xylose through non-phosphorylative pathway. To our knowledge, this is the first report of non-phosphorylative pathway recombinant in filamentous fungi, which shows great potential to convert D-xylose to valuable chemicals.</t>
   </si>
   <si>
-    <t>['1,2,4-Butanetriol', 'D-Xylose', 'D-Xylose dehydrogenase', 'Myceliophthora', 'Weimberg pathway']</t>
+    <t>['1.2.4-Butanetriol', 'D-Xylose', 'D-Xylose dehydrogenase', 'Myceliophthora', 'Weimberg pathway']</t>
   </si>
   <si>
     <t>Biotechnology for biofuels and bioproducts</t>
@@ -871,21 +871,6 @@
     <t>2016 Mar</t>
   </si>
   <si>
-    <t>Cloning, expression and characterization of an ethanol tolerant GH3 beta-glucosidase from Myceliophthora thermophila.</t>
-  </si>
-  <si>
-    <t>The beta-glucosidase gene bgl3a from Myceliophthora thermophila, member of the fungal glycosyl hydrolase (GH) family 3, was cloned and expressed in Pichia pastoris. The mature beta-glucosidase gene, which results after the excision of one intron and the secreting signal peptide, was placed under the control of the strong alcohol oxidase promoter (AOX1) in the plasmid pPICZalphaC. The recombinant enzyme (90 kDa) was purified and characterized in order to evaluate its biotechnological potential. Recombinant P. pastoris efficiently secreted beta-glucosidase into the medium and produced high level of enzymatic activity (41 U/ml) after 192 h of growth, under methanol induction. MtBgl3a was able to hydrolyze low molecular weight substrates and polysaccharides containing beta-glucosidic residues. The K m was found to be 0.39 mM on p-beta-NPG and 2.64 mM on cellobiose. Optimal pH and temperature for the p-beta-NPG hydrolysis were 5.0 and 70  degrees C. The beta-glucosidase exhibits a half life of 143 min at 60  degrees C. Kinetic parameters of inhibition were determined for D-glucose, D-xylose and D-gluconic acid, indicating tolerance of the enzyme for these sugars and oxidized products. The recombinant enzyme was stimulated by short chain alcohols and has been shown to efficiently synthesize methyl-D-glucoside in the presence of methanol due to its transglycosylation activity. The stability of MtBgl3a in ethanol was prominent, and it retained most of its original activity after we exposed it to 50% ethanol for 6 h. The high catalytic performance, good thermal stability and tolerance to elevated concentrations of ethanol, D-xylose and D-glucose qualify this enzyme for use in the hydrolysis of lignocellulosic biomass for biofuel production, as part of an efficient complete multi-enzyme cocktail.</t>
-  </si>
-  <si>
-    <t>['Ethanol tolerance', 'Glycoside hydrolase family 3', 'Myceliophthora thermophila', 'Overexpression', 'Pichia pastoris', 'Thermophilic', 'Transglycosylation', 'beta-glucosidase']</t>
-  </si>
-  <si>
-    <t>PeerJ</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
     <t>The arabinose transporter MtLat-1 is involved in hemicellulase repression as a pentose transceptor in Myceliophthora thermophila.</t>
   </si>
   <si>
@@ -913,781 +898,754 @@
     <t>2017</t>
   </si>
   <si>
-    <t>Chemical modification and immobilisation of laccase from Trametes hirsuta and from Myceliophthora thermophila.</t>
-  </si>
-  <si>
-    <t>Laccase from two different source organisms, Myceliophthora thermophila and Trametes hirsuta, were subjected to chemical modification in solution by (i) two bifunctional reagents, ethylene-glycol-N-hydroxy succinimide (EGNHS) and glutaraldehyde and (ii) by the monofunctional citraconic anhydride. The untreated and chemically modified forms of both enzymes were then immobilised onto three different types of mesoporous silicate (MPS) particle (MCM, CNS and SBA-15). Thermal stabilities of native, modified-soluble and immobilised laccases were then evaluated. Although the two laccases have similar lysine contents, those of M. thermophila are clearly more amenable to chemical modification. Treatment of the M. thermophila enzyme with EGNHS led to a 8.7-fold increase in thermal stability over the free soluble enzyme while glutaraldehyde gave a 5.7-fold increase. Increased activity of M. thermophila laccase occurred only with citraconic anhydride modification (a 3-fold increase), while the glutaraldehyde modification marginally increased the activity of the T. hirsuta enzyme (by 1.2-fold). Upon immobilisation onto MPS, the greatest increase in stability was for the glutaraldehyde-treated M. thermophila preparation on SBA-15 (24-fold over the soluble enzyme). Chemical modification of laccase from T. hirsuta with both glutaraldehyde and EGNHS gave only a 2-fold increase in stability, increasing &gt;4-fold upon immobilisation onto SBA-15 and MCM-41/98.</t>
-  </si>
-  <si>
-    <t>['Chemical modification', 'Immobilisation', 'Laccase', 'Mesoporous silicates', 'Stabilisation']</t>
+    <t>Breeding of a thermostable xylanase-producing strain of Myceliophthora thermophila by atmospheric room temperature plasma (ARTP) mutagenesis.</t>
+  </si>
+  <si>
+    <t>Introduction: Hemicellulose is an important component in lignocellulose materials, which is second only to cellulose, accounting for 15%-35% of the dry weight of plants. In the current situation of energy shortage, making full use of lignocellulose materials to produce fuel ethanol has become an important way to solve the energy problem. Xylanase plays a crucial role in the utilization of hemicellulose. It is a necessary means to reduce the cost of hemicellulose utilization by improving the activity of xylanase. Moreover, most naturally xylanases are mesophilic enzymes, which limits their industrial application. Methods:In this study, Myceliophthora thermophila was used to produce xylanases and a thermostable mutant M 2103 was obtained by atmospheric room temperature plasma (ARTP) mutagenesis. The research work started with exploring the effects of ARTP mutagenesis on the antioxidase system [superoxide dismutase (SOD), catalase (CAT), peroxidase (POD), polyphenol oxidase (PPO), and antioxidant capacity (AOC)] of M. thermophile, and found that superoxide dismutase activity increased by 221.13%, and polyphenol oxidase activity increased by 486.04% as compared with the original strain when the implantation time was 300 s. So as to determine the conditions for subsequent mutagenesis. Results and Discussion:For the mutant M 2103, the reaction temperature for xylanase production remained stable in the range of 70 degrees C-85 degrees C. Its optimum temperature was 75 degrees C, which was 15 degrees C higher than that of the original strain. And its xylanase activity increased by 21.71% as compared with the original strain. M 2103 displayed a significantly higher relative xylanase activity than the original strain in the acidic (pH 4.0-7.0) range, and the xylanase activity was relatively stable in the pH range of 6.0-8.5. These results provide an alternative biocatalyst for the production of xylooligosaccharide, and a potential usage of ARTP in the mutagenesis of thermostable mutant.</t>
+  </si>
+  <si>
+    <t>['ARTP', 'Myceliophthora thermophila', 'antioxidase', 'thermotolerant mutant', 'xylanase']</t>
+  </si>
+  <si>
+    <t>Stability and kinetic behavior of immobilized laccase from Myceliophthora thermophila in the presence of the ionic liquid 1-ethyl-3-methylimidazolium ethylsulfate.</t>
+  </si>
+  <si>
+    <t>The use of ionic liquids (ILs) as reaction media for enzymatic reactions has increased their potential because they can improve enzyme activity and stability. Kinetic and stability properties of immobilized commercial laccase from Myceliophthora thermophila in the water-soluble IL 1-ethyl-3-methylimidazolium ethylsulfate ([emim][EtSO4 ]) have been studied and compared with free laccase. Laccase immobilization was carried out by covalent binding on glyoxyl-agarose beads. The immobilization yield was 100%, and the activity was totally recovered. The Michaelis-Menten model fitted well to the kinetic data of enzymatic oxidation of a model substrate in the presence of the IL [emim][EtSO4 ]. When concentration of the IL was augmented, the values of Vmax for free and immobilized laccases showed an increase and slight decrease, respectively. The laccase-glyoxyl-agarose derivative improved the laccase stability in comparison with the free laccase regarding the enzymatic inactivation in [emim][EtSO4 ]. The stability of both free and immobilized laccase was slightly affected by small amounts of IL (&lt;50%). A high concentration of the IL (75%) produced a large inactivation of free laccase. However, immobilization prevented deactivation beyond 50%. Free and immobilized laccase showed a first-order thermal inactivation profile between 55 and 70 degrees C in the presence of the IL [emim][EtSO4 ]. Finally, thermal stability was scarcely affected by the presence of the IL.</t>
+  </si>
+  <si>
+    <t>['1-ethyl-3-methylimidazolium ethylsulfate', 'agarose', 'immobilization', 'ionic liquid', 'laccase', 'stability']</t>
+  </si>
+  <si>
+    <t>Biotechnology progress</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>2014 Jul-Aug</t>
+  </si>
+  <si>
+    <t>Optimized synthesis of novel prenyl ferulate performed by feruloyl esterases from Myceliophthora thermophila in microemulsions.</t>
+  </si>
+  <si>
+    <t>Five feruloyl esterases (FAEs; EC 3.1.1.73), FaeA1, FaeA2, FaeB1, and FaeB2 from Myceliophthora thermophila C1 and MtFae1a from M. thermophila ATCC 42464, were tested for their ability to catalyze the transesterification of vinyl ferulate (VFA) with prenol in detergentless microemulsions. Reaction conditions were optimized investigating parameters such as the medium composition, the substrate concentration, the enzyme load, the pH, the temperature, and agitation. FaeB2 offered the highest transesterification yield (71.5 +/- 0.2%) after 24 h of incubation at 30  degrees C using 60 mM VFA, 1 M prenol, and 0.02 mg FAE/mL in a mixture comprising of 53.4:43.4:3.2 v/v/v n-hexane:t-butanol:100 mM MOPS-NaOH, pH 6.0. At these conditions, the competitive side hydrolysis of VFA was 4.7-fold minimized. The ability of prenyl ferulate (PFA) and its corresponding ferulic acid (FA) to scavenge 1,1-diphenyl-2-picrylhydrazyl (DPPH) radicals was significant and similar (IC(50) 423.39 muM for PFA, 329.9 muM for FA). PFA was not cytotoxic at 0.8-100 muM (IC(50) 220.23 muM) and reduced intracellular reactive oxygen species (ROS) in human skin fibroblasts at concentrations ranging between 4 and 20 muM as determined with the dichloro-dihydro-fluorescein diacetate (DCFH-DA) assay.</t>
+  </si>
+  <si>
+    <t>['Antioxidant', 'DCFH-DA', 'DPPH', 'Feruloyl esterase', 'Myceliophthora thermophila', 'Prenyl ferulate', 'Transesterification']</t>
+  </si>
+  <si>
+    <t>2017 Apr</t>
+  </si>
+  <si>
+    <t>Characterization and application of a novel class II thermophilic peroxidase from Myceliophthora thermophila in biosynthesis of polycatechol.</t>
+  </si>
+  <si>
+    <t>A peroxidase from the thermophilic fungus Myceliophthora thermophila that belongs to ascomycete Class II based on PeroxiBase classification was functionally expressed in methylotrophic yeast Pichia pastoris. The putative peroxidase from the genomic DNA was successfully cloned in P. pastoris X-33 under the transcriptional control of the alcohol oxidase (AOX1) promoter. The heterologous production was greatly enhanced by the addition of hemin with a titer of 0.41 U mL(-1) peroxidase activity at the second day of incubation. The recombinant enzyme was purified to homogeneity (50 kDa) and characterized using a series of phenolic substrates that indicated similar characteristics with those of generic peroxidases. In addition, the enzyme was found thermostable, retaining its activity for temperatures up to 60  degrees C after eight hours incubation. Moreover, the enzyme displayed remarkable H2O2 stability, retaining more than 80% of its initial activity after 24h incubation in 5000-fold molar excess of H2O2. The ability of the peroxidase to polymerize catechol at high superoxide concentrations, together with its high thermostability and substrate specificity, indicate a potential commercial significance of the enzyme.</t>
+  </si>
+  <si>
+    <t>['Class II peroxidase', 'Heterologous production', 'Myceliophthora thermophila', 'Pichia pastoris', 'Polycatechol', 'Thermostability']</t>
+  </si>
+  <si>
+    <t>2015 Jul-Aug</t>
+  </si>
+  <si>
+    <t>Immobilisation on mesoporous silica and solvent rinsing improve the transesterification abilities of feruloyl esterases from Myceliophthora thermophila.</t>
+  </si>
+  <si>
+    <t>The immobilisation of four feruloyl esterases (FAEs) (FaeA1, FaeA2, FaeB1, FaeB2) from the thermophilic fungus Myceliophthora thermophila C1 was studied and optimised via physical adsorption onto various mesoporous silica particles with pore diameters varying from 6.6nm to 10.9nm. Using crude enzyme preparations, enrichment of immobilised FAEs was observed, depending on pore diameter and protein size. The immobilised enzymes were successfully used for the synthesis of butyl ferulate through transesterification of methyl ferulate with 1-butanol. Although the highest butyl ferulate yields were obtained with free enzyme, the synthesis-to-hydrolysis ratio was higher when using immobilised enzymes. Over 90% of the initial activity was observed in a reusability experiment after nine reaction cycles, each lasting 24h. Rinsing with solvent to remove water from the immobilised enzymes further improved their activity. This study demonstrates the suitability of immobilised crude enzyme preparations in the development of biocatalysts for esterification reactions.</t>
+  </si>
+  <si>
+    <t>['Biocatalysis', 'Butyl ferulate', 'Enzyme immobilisation', 'Esterification', 'SBA-15']</t>
+  </si>
+  <si>
+    <t>Sweden. Electronic address: huttner@chalmers.se</t>
+  </si>
+  <si>
+    <t>2017 Sep</t>
+  </si>
+  <si>
+    <t>Efficacy and safety of itraconazole use in infants.</t>
+  </si>
+  <si>
+    <t>BACKGROUND: Itraconazole has been used to treat fungal infections, in particular invasive fungal infections in infants or neonates in many countries. DATA SOURCES: Literature search was conducted through Ovid EMBASE, PubMed, ISI Web of Science, CNKI and Google scholarship using the following key words: "pediatric" or "infant" or "neonate" and "fungal infection" in combination with "itraconazole". Based on the literature and our clinical experience, we outline the administration of itraconazole in infants in order to develop evidence-based pharmacotherapy. RESULTS: Of 45 articles on the use of itraconazole in infancy, 13 are related to superficial fungal infections including tinea capitis, sporotrichosis, mucosal fungal infections and opportunistic infections. The other 32 articles are related to systemic fungal infections including candidiasis, aspergillosis, histoplasmosis, zygomycosis, trichosporonosis and opportunistic infections as caused by Myceliophthora thermophila. CONCLUSION: Itraconazole is safe and effective at a dose of 5 mg/kg per day in a short duration of therapy for superficial fungal infections and 10 mg/kg per day for systemic fungal infections in infants. With a good compliance, it is cost-effective in treating infantile fungal infections. The profiles of adverse events induced by itraconazole in infants are similar to those in adults and children.</t>
+  </si>
+  <si>
+    <t>['infant', 'itraconazole', 'prophylaxis', 'superficial fungal infections', 'systemic fungal infections']</t>
+  </si>
+  <si>
+    <t>World journal of pediatrics : WJP</t>
+  </si>
+  <si>
+    <t>2016 Nov</t>
+  </si>
+  <si>
+    <t>Engineered Fungus Thermothelomyces thermophilus Producing Plant Storage Proteins.</t>
+  </si>
+  <si>
+    <t>An efficient Agrobacterium-mediated genetic transformation based on the plant binary vector pPZP-RCS2 was carried out for the multiple heterologous protein production in filamentous fungus Thermothelomyces&amp;nbsp;thermophilus F-859 (formerly Myceliophthora&amp;nbsp;thermophila F-859). The engineered fungus Th.&amp;nbsp;thermophilus was able to produce plant storage proteins of Zea&amp;nbsp;mays (alpha-zein Z19) and Amaranthus&amp;nbsp;hypochondriacus (albumin A1) to enrich fungal biomass by valuable nutritional proteins and improved amino acid content. The mRNA levels of z19 and a1 genes were significantly dependent on their driving promoters: the promoter of tryptophan synthase (PtrpC) was more efficient to express a1, while the promoter of translation elongation factor (Ptef) provided much higher levels of z19 transcript abundance. In general, the total recombinant proteins and amino acid contents were higher in the Ptef-containing clones. This work describes a new strategy to improve mycoprotein nutritive value by overexpression of plant storage proteins.</t>
+  </si>
+  <si>
+    <t>['Myceliophthora thermophila', 'amaranth albumin A1', 'filamentous fungi', 'maize alpha-zein', 'mycoprotein', 'recombinant protein']</t>
+  </si>
+  <si>
+    <t>Journal of fungi (Basel, Switzerland)</t>
+  </si>
+  <si>
+    <t>2022 Jan 26</t>
+  </si>
+  <si>
+    <t>Increasing the lignin yield of the Alkaline Polyol Pulping process by treating black liquor with laccases of Myceliophthora thermophila.</t>
+  </si>
+  <si>
+    <t>The Alkaline Polyol Pulping process separates cellulose from lignocellulosic biomass by dissolving lignin to a great extent. Due to the pulping conditions the dissolved lignin depolymerises and only 75% can be precipitated. To increase this amount, a 24 h reaction of laccases of Myceliophthora thermophila with lignin dissolved in black liquor of the AlkaPolP process was investigated. The influence of pH, temperature, enzyme concentration and partial oxygen pressure was examined in a batch stirred tank reactor using a Box-Behnken factorial design. Due to the enzymatic reaction the lignin polymerises which results in an enhanced lignin precipitation. The addition of a mediator improves the polymerisation but decreases the amount of precipitable lignin. The influence of the parameters on precipitation yield and molecular mass can sufficiently be described with a second-order model and optimum conditions can be assessed. FT-IR spectra of the obtained lignins revealed that its typical phenolic structure is preserved.</t>
+  </si>
+  <si>
+    <t>['Biorefinery', 'Laccase', 'Lignin', 'Lignocellulose', 'Polymerisation']</t>
+  </si>
+  <si>
+    <t>Germany. Electronic address: norman.engel@b-tu.de</t>
+  </si>
+  <si>
+    <t>Ultrasound-assisted swelling of bacterial cellulose.</t>
+  </si>
+  <si>
+    <t>Bacterial cellulose (BC) was obtained by static cultivation using commercial BC gel from scoby. BC membranes (oven dried and freeze-dried) were swelled with 8% NaOH, in the absence and in the presence of ultrasound (US), for 30, 60, and 90 min. The influence of swelling conditions on both physico-chemical properties and molecules entrapment was evaluated. Considering the highest levels of entrapment, an optimum swelling procedure was established: 8% NaOH for 30 min at room temperature in the presence of US. Native and PEGylated laccase from Myceliophthora thermophila was immobilized on BC membranes and a different catalytic behaviour was observed after immobilization. Native laccase presented activity values similar to published reports (5-7 U/gBC) after immobilization whereas PEGylated enzymes showed much lower activity (1-2 U/gBC). BC swelled membranes are presented herein as a potential support for the preparation of immobilized enzymes for industrial applications, like phenolics polymerization.</t>
+  </si>
+  <si>
+    <t>['Bacterial cellulose', 'PEG-FITC', 'Polymerization', 'Swelling', 'Ultrasound']</t>
+  </si>
+  <si>
+    <t>Engineering in life sciences</t>
+  </si>
+  <si>
+    <t>Department of Clothing and Textiles Sookmyung Women's University Seoul South Korea</t>
+  </si>
+  <si>
+    <t>2017 Oct</t>
+  </si>
+  <si>
+    <t>Substrate selectivity in starch polysaccharide monooxygenases.</t>
+  </si>
+  <si>
+    <t>Degradation of polysaccharides is central to numerous biological and industrial processes. Starch-active polysaccharide monooxygenases (AA13 PMOs) oxidatively degrade starch and can potentially be used with industrial amylases to convert starch into a fermentable carbohydrate. The oxidative activities of the starch-active PMOs from the fungi Neurospora crassa and Myceliophthora thermophila, NcAA13 and MtAA13, respectively, on three different starch substrates are reported here. Using high-performance anion-exchange chromatography coupled with pulsed amperometry detection, we observed that both enzymes have significantly higher oxidative activity on amylose than on amylopectin and cornstarch. Analysis of the product distribution revealed that NcAA13 and MtAA13 more frequently oxidize glycosidic linkages separated by multiples of a helical turn consisting of six glucose units on the same amylose helix. Docking studies identified important residues that are involved in amylose binding and suggest that the shallow groove that spans the active-site surface of AA13 PMOs favors the binding of helical amylose substrates over nonhelical substrates. Truncations of NcAA13 that removed its native carbohydrate-binding module resulted in diminished binding to amylose, but truncated NcAA13 still favored amylose oxidation over other starch substrates. These findings establish that AA13 PMOs preferentially bind and oxidize the helical starch substrate amylose. Moreover, the product distributions of these two enzymes suggest a unique interaction with starch substrates.</t>
+  </si>
+  <si>
+    <t>['amylose', 'auxiliary activity (AA) enzyme', 'carbohydrate-binding protein', 'copper', 'copper monooxygenase', 'metalloprotein', 'oxygenase', 'polysaccharide', 'polysaccharide monooxygenase', 'starch']</t>
+  </si>
+  <si>
+    <t>Vietnam. Electronic address: vanvu@ntt.edu.vn</t>
+  </si>
+  <si>
+    <t>2019 Aug 9</t>
+  </si>
+  <si>
+    <t>Development of a genome-editing CRISPR/Cas9 system in thermophilic fungal Myceliophthora species and its application to hyper-cellulase production strain engineering.</t>
+  </si>
+  <si>
+    <t>BACKGROUND: Over the past 3 years, the CRISPR/Cas9 system has revolutionized the field of genome engineering. However, its application has not yet been validated in thermophilic fungi. Myceliophthora thermophila, an important thermophilic biomass-degrading fungus, has attracted industrial interest for the production of efficient thermostable enzymes. Genetic manipulation of Myceliophthora is crucial for metabolic engineering and to unravel the mechanism of lignocellulose deconstruction. The lack of a powerful, versatile genome-editing tool has impeded the broader exploitation of M. thermophila in biotechnology. RESULTS: In this study, a CRISPR/Cas9 system for efficient multiplexed genome engineering was successfully developed in the thermophilic species M. thermophila and M. heterothallica. This CRISPR/Cas9 system could efficiently mutate the imported amdS gene in the genome via NHEJ-mediated events. As a proof of principle, the genes of the cellulase production pathway, including cre-1, res-1, gh1-1, and alp-1, were chosen as editing targets. Simultaneous multigene disruptions of up to four of these different loci were accomplished with neomycin selection marker integration via a single transformation using the CRISPR/Cas9 system. Using this genome-engineering tool, multiple strains exhibiting pronounced hyper-cellulase production were generated, in which the extracellular secreted protein and lignocellulase activities were significantly increased (up to 5- and 13-fold, respectively) compared with the parental strain. CONCLUSIONS: A genome-wide engineering system for thermophilic fungi was established based on CRISPR/Cas9. Successful expansion of this system without modification to M. heterothallica indicates it has wide adaptability and flexibility for use in other Myceliophthora species. This system could greatly accelerate strain engineering of thermophilic fungi for production of industrial enzymes, such as cellulases as shown in this study and possibly bio-based fuels and chemicals in the future.</t>
+  </si>
+  <si>
+    <t>['CRISPR/Cas9 system', 'Cellulases', 'Myceliophthora', 'Thermophilic fungi']</t>
+  </si>
+  <si>
+    <t>300308 China</t>
+  </si>
+  <si>
+    <t>Designing and Constructing a Novel Artificial Pathway for Malonic Acid Production Biologically.</t>
+  </si>
+  <si>
+    <t>Malonic acid is used as a common component of many products and processes in the pharmaceutical and cosmetic industries. Here, we designed a novel artificial synthetic pathway of malonic acid, in which oxaloacetate, an intermediate of cytoplasmic reductive tricarboxylic acid (rTCA) pathway, is converted to malonic semialdehyde and then to malonic acid, sequentially catalyzed by a-keto decarboxylase and malonic semialdehyde dehydrogenase. After the systematic screening, we discovered the enzyme oxaloacetate decarboxylase Mdc, catalyzing the first step of the artificially designed pathway in vitro. Then, this synthetic pathway was functionally constructed in cellulolytic thermophilic fungus Myceliophthora thermophila. After enhancement of glucose uptake, the titer of malonic acid achieved 42.5 mg/L. This study presents a novel biological pathway for producing malonic acid from renewable resources in the future.</t>
+  </si>
+  <si>
+    <t>['Myceliophthora thermophila', 'a-keto decarboxylase', 'malonic acid', 'metabolic engineering', 'oxaloacetic acid']</t>
+  </si>
+  <si>
+    <t>Additives enhancing enzymatic hydrolysis of lignocellulosic biomass.</t>
+  </si>
+  <si>
+    <t>Linked to the development of cellulolytic enzyme cocktails from Myceliophthora thermophila, we studied the effect of different additives on the enzymatic hydrolysis yield. The hydrolysis of pretreated corn stover (PCS), sugar cane straw (PSCS) and microcrystalline cellulose (Avicel) was performed under industrial conditions using high solid loadings, limited mixing, and low enzyme dosages. The addition of polyethylene glycol (PEG4000) allowed to increase the glucose yields by 10%, 7.5%, and 32%, respectively in the three materials. PEG4000 did not have significant effect on the stability of the main individual enzymes but increased beta-glucosidase and endoglucanase activity by 20% and 60% respectively. Moreover, the presence of PEG4000 accelerated cellulase-catalyzed hydrolysis reducing up to 25% the liquefaction time. However, a preliminary economical assessment concludes that even with these improvements, a lower contribution of PEG4000 to the 2G bioethanol production costs would be needed to reach commercial feasibility.</t>
+  </si>
+  <si>
+    <t>['Additives', 'Enzymatic hydrolysis', 'Lignocellulose', 'Myceliophthora thermophila']</t>
+  </si>
+  <si>
+    <t>2017 Nov</t>
+  </si>
+  <si>
+    <t>Enzymatic Oxidation of Ferulic Acid as a Way of Preparing New Derivatives.</t>
+  </si>
+  <si>
+    <t>The ferulic acid (FA)-oxidation by Myceliophthora thermophila laccase was performed in phosphate buffer at 30  degrees C and pH 7.5 as an eco-friendly procedure. LC-MS analysis showed that oxidation products were four dehydrodimers (P1, P2, P3, P5) at MM = 386 g/mol, two dehydrotetramers (P6, P7) at MM = 770 g/mol and one decarboxylated dehydrodimer (P4) at MM = 340 g/mol. Structural characterization showed that FA-dehydrodimers were symmetric for P1 and P5 while asymmetric for P2, P3 and P4. Physicochemical characterization showed that oxidation products presented a higher lipophilicity than that of FA. Moreover, symmetric dimers and tetra dimers had a higher melting point compared to FA and its asymmetric dimers. Antioxidant and anti-proliferative assessments indicated that enzymatic oligomerization increased antioxidant and anti-proliferative properties of oxidation products for P2, P3 and P6 compared to FA. Finally, this enzymatic process in water could produce new molecules, having good antiradical and anti-proliferative activities.</t>
+  </si>
+  <si>
+    <t>['LC-MS', 'RMN', 'anti-proliferative', 'antioxidant', 'enzymatic oxidation']</t>
+  </si>
+  <si>
+    <t>Biotech (Basel (Switzerland))</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>2022 Dec 5</t>
+  </si>
+  <si>
+    <t>Polymers from Bamboo Extracts Produced by Laccase.</t>
+  </si>
+  <si>
+    <t>A green methodology for the production of polymers from bamboo powder was investigated. The optimal conditions for the extraction of components from bamboo were defined by incubating the powder in an acetate buffer (pH 5) under boiling for 2 h. Native laccase from Myceliophthora thermophila was used afterwards to oxidize the extracts from the final resulting extraction liquid. The reduction of the free OH content after enzymatic oxidation, as well as the (1)H NMR data, confirmed the efficient polymerization of the extracts. The bamboo powder samples were also subjected to high compression and curing, in the absence and in the presence of laccase, to evaluate the hardness of the tablets formed by enzymatic bonding events. The results revealed a higher hardness when the tablets were produced in the presence of laccase, confirming the role of the catalyst on the precipitation of colloidal lignin and phenolic extractives. Herein we produce new oligomers/polymers by laccase oxidation of the extracts resulting from a clean method boiling. At the same time, the data open up new routes for the exploitation of new lignocellulosic materials by the direct application of the enzyme on the bamboo powder material.</t>
+  </si>
+  <si>
+    <t>['bamboo powder', 'bamboo tablets', 'laccase', 'oxidation', 'phenolic compound extraction']</t>
+  </si>
+  <si>
+    <t>China. jingsu@ceb.uminho.pt</t>
+  </si>
+  <si>
+    <t>2018 Oct 12</t>
+  </si>
+  <si>
+    <t>Unique features of the bifunctional GH30 from Thermothelomyces thermophila revealed by structural and mutational studies.</t>
+  </si>
+  <si>
+    <t>Fungal xylanases belonging to family GH30_7, initially categorized as endo-glucuronoxylanases, are now known to differ both in terms of substrate specificity, as well as mode of action. Recently, TtXyn30A, a GH30_7 xylanase from Thermothelomyces thermophila, was shown to possess dual activity, acting on the xylan backbone in both an endo- and an exo- manner. Here, in an effort to identify the structural characteristics that append these functional properties to the enzyme, we present the biochemical characterization of various TtXyn30A mutants as well as its crystal structure, alone, and in complex with the reaction product. An auxiliary catalytic amino acid has been identified, while it is also shown that glucuronic acid recognition is not mediated by a conserved arginine residue, as shown by previously determined GH30 structures.</t>
+  </si>
+  <si>
+    <t>['Acidic xylooligosaccharides', 'GH30 xylanase', 'Glucuronic acid recognition', 'Protein engineering', 'X-ray structure', 'Xylobiohydrolase']</t>
+  </si>
+  <si>
+    <t>2021 Dec 1</t>
+  </si>
+  <si>
+    <t>Enzyme Catalyzed Copolymerization of Lignosulfonates for Hydrophobic Coatings.</t>
+  </si>
+  <si>
+    <t>Enzymatic polymerization of lignin can generate a variety of value-added products concomitantly replacing fossil-based resources. In line with this approach, a laccase from the thermophilic fungus Myceliophthora thermophila (MtL) was used to couple a hydrophobicity enhancing fluorophenol (FP) molecule, namely 4-[4-(trifluoromethyl)phenoxy]phenol (4,4-F3MPP), as a model substrate onto lignosulfonate (LS). During the coupling reaction changes in fluorescence, phenol content, viscosity and molecular weight (size exclusion chromatography; SEC) were monitored. The effects of enzymatic coupling of FP onto LS on hydrophobicity were investigated by the means of water contact angle (WCA) measurement and determination of swelling capacity. Full polymerization of LS resulting in the production of water-insoluble polymers was achieved at a pH of 7 and 33 degrees C. Incorporation of 2% (w/v) of FP led to an increase in WCA by 59.2% while the swelling capacity showed a decrease by 216.8%. Further, Fourier transform infrared spectroscopy (FTIR) and X-ray photoelectron spectroscopy (XPS) analysis indicated successful covalent coupling of the FP molecule onto LS by an emerging peak at 1,320 cm(-1) in the FTIR spectrum and the evidence of Fluor in the XPS spectrum. This study shows the ability of laccase to mediate the tailoring of LS properties to produce functional polymers.</t>
+  </si>
+  <si>
+    <t>['coating', 'coupling', 'fluorophenol', 'hydrophobicity', 'laccase', 'lignosulfonate', 'modification']</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Dissecting key residues of a C4-dicarboxylic acid transporter to accelerate malate export in Myceliophthora.</t>
+  </si>
+  <si>
+    <t>Efficient transporters are necessary for high concentration and purity of desired products during industrial production. In this study, we explored the mechanism of substrate transport and preference of the C4-dicarboxylic acid transporter AoMAE in the fungus Myceliophthora thermophila, and investigated the roles of 18 critical amino acid residues within this process. Among them, the residue Arg78, forming a hydrogen bond network with Arg23, Phe25, Thr74, Leu81, His82, and Glu94 to stabilize the protein conformation, is irreplaceable for the export function of AoMAE. Furthermore, varying the residue at position 100 resulted in changes to the size and shape of the substrate binding pocket, leading to alterations in transport efficiencies of both malic acid and succinic acid. We found that the mutation T100S increased malate production by 68%. Using these insights, we successfully generated an AoMAE variant with mutation T100S and deubiquitination, exhibiting an 81% increase in the selective export activity of malic acid. Simply introducing this version of AoMAE into M. thermophila wild-type strain increased production of malic acid from 1.22 to 54.88 g/L. These findings increase our understanding of the structure-function relationships of organic acid transporters and may accelerate the process of engineering dicarboxylic acid transporters with high efficiency. KEY POINTS: * This is the first systematical analysis of key residues of a malate transporter in fungi. * Protein engineering of AoMAE led to 81% increase of malate export activity. * Arg78 was essential for the normal function of AoMAE in M. thermophila. * Substitution of Thr100 affected export efficiency and substrate selectivity of AoMAE.</t>
+  </si>
+  <si>
+    <t>['C4-dicarboxylic acid;', 'Malate export', 'Myceliophthora;', 'Protein rewiring;']</t>
+  </si>
+  <si>
+    <t>2023 Feb</t>
+  </si>
+  <si>
+    <t>Green synthesis of glyco-phenol by enzymatic coupling between ferulic acid and glucosamine: An ecofriendly procedure.</t>
+  </si>
+  <si>
+    <t>A new glyco-phenol was produced by the coupling between glucosamine (Glu) and ferulic acid (FA) using Myceliophthora thermophila laccase as biocatalyst in mild conditions (distilled water and 30 degrees C) as an environmentally friendly process. Results indicated that the enzymatic reaction created a new derivative (FA-Glu), produced from coupling between Glu and FA by covalent bonds. By the high production of (FA-Glu) derivative and its stability, the optimal ratio of (FA:Glu) was of (1:1) at optimal time reaction of 6 h. Under these optimal conditions, almost 55% of -NH(2) groups on Glu were bound with FA oxidation products. The new derivative showed higher hydrophobic character than Glu due to the presence of FA in its structure. Liquid chromatography-mass spectrometry analysis showed that (FA-Glu) derivative exhibited a molecular mass at MM 713 g/mol containing one Glu molecule and three FA molecules after decarboxylation. Furthermore, the new derivative presented good antioxidant and antiproliferative activities in comparison with Glu and FA. These results suggest that the enzymatic conjugation between Glu and FA is a promising process to produce a new glyco-phenol having good functional properties for potential applications.</t>
+  </si>
+  <si>
+    <t>['ferulic acid', 'functional properties', 'glucosamine', 'glyco-phenol', 'laccase']</t>
+  </si>
+  <si>
+    <t>Biotechnology and applied biochemistry</t>
+  </si>
+  <si>
+    <t>2022 Aug</t>
+  </si>
+  <si>
+    <t>Laccase catalyzed elimination of morphine from aqueous systems.</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals contaminate the environment for several reasons, including metabolic excretion after intake, industrial waste and improper disposal. The narcotic drug morphine is commonly utilized for chronic pain management, and the distribution of morphine in aqueous systems and in waste waters is of high concern. Here, the removal of morphine by a laccase from Myceliophthora thermophila both in its free form as well as immobilized on Accurel MP1000 beads was investigated. Complete morphine elimination was achieved within 30 min for the free and the immobilized enzyme (70% bound protein) for concentrations between 1 and 1,000 mg L(-1) according to LC-TOF mass spectrometry analysis. Higher morphine concentrations up to 60 g L(-1) were also tested and total elimination was achieved within 6 h. Therefore, laccases are ideal candidates for removing morphine from aqueous systems.</t>
+  </si>
+  <si>
+    <t>['Aqueous systems', 'Elimination', 'Enzyme immobilization', 'Laccase', 'Morphine']</t>
+  </si>
+  <si>
+    <t>New biotechnology</t>
+  </si>
+  <si>
+    <t>2018 May 25</t>
+  </si>
+  <si>
+    <t>Development of a flow cytometry-based plating-free system for strain engineering in industrial fungi.</t>
+  </si>
+  <si>
+    <t>Recent technical advances regarding filamentous fungi have accelerated the engineering of fungal-based production and benefited basic science. However, challenges still remain and limit the speed of fungal applications. For example, high-throughput technologies tailored to filamentous fungi are not yet commonly available for genetic modification. The currently used fungal genetic manipulations are time-consuming and laborious. Here, we developed a flow cytometry-based plating-free system to directly screen and isolate the transformed protoplasts in industrial fungi Myceliophthora thermophila and Aspergillus niger. This system combines genetic engineering via the 2A peptide and the CRISPR-Cas9 system, strain screening by flow cytometry, and direct sorting of colonies for deep-well-plate incubation and phenotypic analysis while avoiding culturing transformed protoplasts in plates, colony picking, conidiation, and cultivation. As a proof of concept, we successfully applied this system to generate the glucoamylase-hyperproducing strains MtYM6 and AnLM3 in M. thermophila and A. niger, respectively. Notably, the protein secretion level and enzyme activities in MtYM6 were 17.3- and 25.1-fold higher than in the host strain. Overall, these findings suggest that the flow cytometry-based plating-free system can be a convenient and efficient tool for strain engineering in fungal biotechnology. We expect this system to facilitate improvements of filamentous fungal strains for industrial applications. KEY POINTS: * Development of a flow cytometry-based plating-free (FCPF) system is presented. * Application of FCPF system in M. thermophila and A. niger for glucoamylase platform. * Hyper-produced strains MtYM6 and AnLM3 for glucoamylase production are generated.</t>
+  </si>
+  <si>
+    <t>['Aspergillus niger', 'CRISPR-Cas9', 'Flow cytometry', 'Glucoamylase', 'Myceliophthora thermophila', 'Plating-free']</t>
+  </si>
+  <si>
+    <t>2022 Jan</t>
+  </si>
+  <si>
+    <t>Recombinant thermo-alkali-stable endoglucanase of Myceliopthora thermophila BJA (rMt-egl): Biochemical characteristics and applicability in enzymatic saccharification of agro-residues.</t>
+  </si>
+  <si>
+    <t>Codon adaptation index (CAI) of a 1263bp long endoglucanase encoding gene from the thermophilic mould Myceliopthora thermophile BJA has been improved from 0.44 to 0.76 by in vitro gene synthesis. The codon optimized endoglucanase gene (Mt-egl) has been constitutively expressed in Pichia pastoris under the regulation of GAP promoter. Recombinant endoglucanase (rMt-egl), purified by size exclusion chromatography, has been confirmed to be a monomeric protein of  approximately 47kDa. rMt-egl is optimally active at pH 10 and 50 degrees C, displaying stability in broad pH and temperature ranges, with a t(1/2) of 60 and 15min at 90 and 100 degrees C, respectively. This retained  approximately 70% of activity after 3h incubation at pH 5-12. The K(m), V(max), k(cat) and k(cat)/K(m) of rMt-egl were 5mgmL(-1), 20mumolesmin(-1)mg(-1), 1.02x10(3)s(-1) and 204s(-1)mg(-1)mL(-1), respectively. Homology modeling and bioinformatics analysis confirmed catalytically important role of glutamate 234 and 344. rMt-egl released high amounts of reducing sugars from wheat bran and corn cobs (421 and 382mgg(-1)), thus making it a useful biocatalyst for producing bioethanol and fine chemicals from agro-residues.</t>
+  </si>
+  <si>
+    <t>['Codon optimization', 'Constitutive expression', 'Enzymatic saccharification', 'Myceliophthora thermophila', 'Thermo-alkali-stable endoglucanase', 'Thermophilic mould']</t>
+  </si>
+  <si>
+    <t>A fatal case of pneumonia caused by Thermothelomycesthermophila.</t>
+  </si>
+  <si>
+    <t>Thermothelomyces thermophila (formerly Myceliophthora thermophila) is usually found in soil and specifically compost as an environmental dematiaceous fungus. Here, we report the first case of invasive pulmonary infection caused by T. thermophila in a pediatric patient with acute lymphoblastic leukemia. T. thermophila was serially cultured from bronchoalveolar lavage (BAL) fluid and sputum samples obtained from this patient with respiratory symptoms. The patient received antifungal treatment with liposomal amphotericin B (160 mg daily) and itraconazole (200 mg daily) combination therapy, but she died. By the antifungal susceptibility testing, low minimum inhibitory concentrations (MIC) were observed for itraconazole (MIC 0.06 mug/mL), voriconazole (MIC 0.12 mug/mL), and posaconazole (MIC 0.03 mug/mL) but high MIC was observed with amphotericin B (MIC 4.0 mug/mL). Since T. thermophila is usually found in the environment, it can be considered as a contaminant and may cause difficulties in diagnosis. Therefore, it is necessary to confirm the potential of pathogen through repeated culture and to conduct an antifungal susceptibility testing to find a suitable antifungal agent.</t>
+  </si>
+  <si>
+    <t>['Acute lymphoblastic leukemia', 'Antifungal susceptibility testing', 'Invasive pulmonary infection', 'Thermothelomyces thermophila']</t>
+  </si>
+  <si>
+    <t>Journal of infection and chemotherapy : official journal of the Japan Society of Chemotherapy</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>2023 Jan</t>
+  </si>
+  <si>
+    <t>Thermophilic Filamentous Fungus C1-Cell-Cloned SARS-CoV-2-Spike-RBD-Subunit-Vaccine Adjuvanted with Aldydrogel((R))85 Protects K18-hACE2 Mice against Lethal Virus Challenge.</t>
+  </si>
+  <si>
+    <t>SARS-CoV-2 is evolving with increased transmission, host range, pathogenicity, and virulence. The original and mutant viruses escape host innate (Interferon) immunity and adaptive (Antibody) immunity, emphasizing unmet needs for high-yield, commercial-scale manufacturing to produce inexpensive vaccines/boosters for global/equitable distribution. We developed DYAI-100A85, a SARS-CoV-2 spike receptor binding domain (RBD) subunit antigen vaccine expressed in genetically modified thermophilic filamentous fungus, Thermothelomyces heterothallica C1, and secreted at high levels into fermentation medium. The RBD-C-tag antigen strongly binds ACE2 receptors in vitro. Alhydrogel((R))'85'-adjuvanted RDB-C-tag-based vaccine candidate (DYAI-100A85) demonstrates strong immunogenicity, and antiviral efficacy, including in vivo protection against lethal intranasal SARS-CoV-2 (D614G) challenge in human ACE2-transgenic mice. No loss of body weight or adverse events occurred. DYAI-100A85 also demonstrates excellent safety profile in repeat-dose GLP toxicity study. In summary, subcutaneous prime/boost DYAI-100A85 inoculation induces high titers of RBD-specific neutralizing antibodies and protection of hACE2-transgenic mice against lethal challenge with SARS-CoV-2. Given its demonstrated safety, efficacy, and low production cost, vaccine candidate DYAI-100 received regulatory approval to initiate a Phase 1 clinical trial to demonstrate its safety and efficacy in humans.</t>
+  </si>
+  <si>
+    <t>['BALB/c mice', 'C-tag', 'CHO-cell', 'COVID-19', 'IgG', 'IgG1 and IgG2b', 'K18-hACE-2 mice', 'Myceliophthora thermophila', 'RBD', 'SARS-CoV-2', 'Thermothelomyces heterothallica', 'adjuvant', 'alum', 'aluminum-based vaccine adjuvants', 'antigen', 'baculovirus', 'biomanufacturing', 'dyadic', 'efficacy', 'glycans', 'glycoprotein', 'glycosylation', 'insect cells', 'intranasal challenge', 'neutralizing antibodies', 'pandemic', 'receptor binding domain', 'recombinant protein subunit vaccine', 'stability', 'toxicology', 'vaccine', 'variants of concern', 'virus', 'zoonotic']</t>
+  </si>
+  <si>
+    <t>Vaccines</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>2022 Dec 11</t>
+  </si>
+  <si>
+    <t>Evaluation of Antibacterial and Antifungal Properties of Low Molecular Weight Chitosan Extracted from Hermetia illucens Relative to Crab Chitosan.</t>
+  </si>
+  <si>
+    <t>This study shows the research on the depolymerisation of insect and crab chitosans using novel enzymes. Enzyme preparations containing recombinant chitinase Chi 418 from Trichoderma harzianum, chitinase Chi 403, and chitosanase Chi 402 from Myceliophthora thermophila, all belonging to the family GH18 of glycosyl hydrolases, were used to depolymerise a biopolymer, resulting in a range of chitosans with average molecular weights (M(w)) of 6-21 kDa. The depolymerised chitosans obtained from crustaceans and insects were studied, and their antibacterial and antifungal properties were evaluated. The results proved the significance of the chitosan's origin, showing the potential of Hermetia illucens as a new source of low molecular weight chitosan with an improved biological activity.</t>
+  </si>
+  <si>
+    <t>['Hermetia illucens', 'antibacterial activity', 'antifungal activity', 'chitosan', 'depolymerisation', 'insect']</t>
+  </si>
+  <si>
+    <t>2022 Jan 17</t>
+  </si>
+  <si>
+    <t>Bio-coloration of bacterial cellulose assisted by immobilized laccase.</t>
+  </si>
+  <si>
+    <t>In this work a process for the bio-coloration of bacterial cellulose (BC) membranes was developed. Laccase from Myceliophthora thermophila was immobilized onto BC membranes and retained up to 88% of residual activity after immobilization. Four compounds belonging to the flavonoids family were chosen to test the in situ polymerase activity of immobilized laccase. All the flavonoids were successfully polymerized by laccase giving rise to yellow, orange and dark brown oligomers which conferred color to the BC support. The optimal bio-coloration conditions were studied for two of the tested flavonoids, catechol and catechin, by varying the concentration and time of incubation. High color depth and resistance to washing were obtained for both compounds. The highly porous bacterial cellulose material demonstrated great performance as a bio-coloration support, in contrast to other materials cited in literature, like cotton or wool. The process developed is presented as an environmentally friendly alternative for bacterial cellulose bio-coloration and will contribute deeply for the development of new fashionable products within this material.</t>
+  </si>
+  <si>
+    <t>['Bacterial cellulose', 'Bio-coloration', 'Laccase', 'Polymerization']</t>
+  </si>
+  <si>
+    <t>2018 Feb 13</t>
+  </si>
+  <si>
+    <t>Enzymatic Oxidation of Ca-Lignosulfonate and Kraft Lignin in Different Lignin-Laccase-Mediator-Systems and MDF Production.</t>
+  </si>
+  <si>
+    <t>Laccase-mediator-oxidized lignin offers replacement for conventional chemical binders to produce fiberboards. Compared to the previously reported laccase-mediator system (LMS), a lignin-laccase-mediator-system (LLMS) has an advantage in that it requires much shorter fiber-enzyme incubation time due to significantly increased redox reactions. However, the cost of regularly applying laccase on an industrial scale is currently too high. We have employed CcLcc5 from cultures of the basidiomycete Coprinopsis cinerea as a novel basi-laccase (a CAZy subfamily AA1_1 laccase) in medium-density fiberboard (MDF) production, in comparison to the commercial formulation Novozym 51003 with recombinantly produced asco-laccase MtL (a CAZy subfamily AA1_3 laccase-like multicopper oxidase from the ascomycete Myceliophthora thermophila). With the best-performing natural mediator 2,6-dimethoxyphenol (DMP), unpurified CcLcc5 was almost as good as formulated Novozym 51003 in increasing the molecular weight (MW) of the technical lignins tested, the hydrophilic high-MW Ca-lignosulfonate and the hydrophobic low-MW kraft lignin (Indulin AT). Oxygen consumption rates of the two distantly related, poorly conserved enzymes (31% sequence identity) with different mediators and lignosulfonate were also comparable, but Indulin AT significantly reduced the oxidative activity of Novozym 51003 unlike CcLcc5, regardless of the mediator used, either DMP or guaiacol. Oxygen uptake by both laccases was much faster with both technical lignins with DMP than with guaiacol. In case of lignosulfonate and DMP, 20-30 min of incubation was sufficient for full oxygen consumption, which fits in well in time with the usual binder application steps in industrial MDF production processes. LLMS-bonded MDF was thus produced on a pilot-plant scale with either crude CcLcc5 or Novozym 51003 at reduced enzyme levels of 5 kU/kg absolutely dry wood fiber with lignosulfonate and mediator DMP. Boards produced with CcLcc5 were comparably good as those made with Novozym 51003. Boards reached nearly standard specifications in internal bond strength (IB) and modulus of rupture (MOR), while thickness swelling (TS) was less good based on the hydrophilic character of lignosulfonate. LLMS-bonded MDF with Indulin AT and DMP performed better in TS but showed reduced IB and MOR values.</t>
+  </si>
+  <si>
+    <t>['2,6-dimethoxyphenol', 'Ca-lignosulfonate', 'MDF', 'asco-laccase MtL', 'basi-laccase CcLcc5', 'guaiacol', 'kraft lignin', 'mediator']</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Laccase-Mediator System Using a Natural Mediator as a Whitening Agent for the Decolorization of Melanin.</t>
+  </si>
+  <si>
+    <t>In this study, a laccase-mediator system (LMS) using a natural mediator was developed as a whitening agent for melanin decolorization. Seven natural mediators were used to replace synthetic mediators and successfully overcome the low redox potential of laccase and limited access of melanin to the active site of laccase. The melanin decolorization activity of laccases from Trametes versicolor (lacT) and Myceliophthora thermophila (lacM) was significantly enhanced using natural mediators including acetosyringone, syringaldehyde, and acetovanillone, which showed low cytotoxicity. The methoxy and ketone groups of natural mediators play an important role in melanin decolorization. The specificity constants of lacT and lacM for melanin decolorization were enhanced by 247 and 334, respectively, when acetosyringone was used as a mediator. LMS using lacM and acetosyringone could also decolorize the melanin present in the cellulose hydrogel film, which mimics the skin condition. Furthermore, LMS could decolorize not only synthetic eumelanin analogs prepared by the oxidation of tyrosine but also natural melanin produced by melanoma cells.</t>
+  </si>
+  <si>
+    <t>['decolorization', 'laccase', 'melanin', 'natural mediators']</t>
+  </si>
+  <si>
+    <t>Korea</t>
+  </si>
+  <si>
+    <t>2021 Oct 25</t>
+  </si>
+  <si>
+    <t>Effect of mutations on the thermostability of Aspergillus aculeatus beta-1,4-galactanase.</t>
+  </si>
+  <si>
+    <t>New variants of beta-1,4-galactanase from the mesophilic organism Aspergillus aculeatus were designed using the structure of beta-1,4-galactanase from the thermophile organism Myceliophthora thermophila as a template. Some of the variants were generated using PROPKA 3.0, a validated pKa prediction tool, to test its usefulness as an enzyme design tool. The PROPKA designed variants were D182N and S185D/Q188T, G104D/A156R. Variants Y295F and G306A were designed by a consensus approach, as a complementary and validated design method. D58N was a stabilizing mutation predicted by both methods. The predictions were experimentally validated by measurements of the melting temperature (Tm ) by differential scanning calorimetry. We found that the Tm is elevated by 1.1  degrees C for G306A, slightly increased (in the range of 0.34 to 0.65  degrees C) for D182N, D58N, Y295F and unchanged or decreased for S185D/Q188T and G104D/A156R. The Tm changes were in the range predicted by PROPKA. Given the experimental errors, only the D58N and G306A show significant increase in thermodynamic stability. Given the practical importance of kinetic stability, the kinetics of the irreversible enzyme inactivation process were also investigated for the wild-type and three variants and found to be biphasic. The half-lives of thermal inactivation were approximately doubled in G306A, unchanged for D182N and, disappointingly, a lot lower for D58N. In conclusion, this study tests a new method for estimating Tm changes for mutants, adds to the available data on the effect of substitutions on protein thermostability and identifies an interesting thermostabilizing mutation, which may be beneficial also in other galactanases.</t>
+  </si>
+  <si>
+    <t>['AZCL-galactan, azurine-crosslinked galactan', 'AaGal, beta-1,4-galactanase from Aspergillus aculeatus', 'CAZY, carbohydrate active enzyme database', 'Computational prediction', 'DSC, differential scanning calorimetry', 'GH53', 'MtGal, beta-1,4-galactanase from Myceliophthora thermophila', 'Protein design', 'Thermostability', 'Tm, melting temperature', 'TsGal, Talaromyces stipitatus galactanase', 'WT, wild type', 'beta-1,4-galactanase']</t>
+  </si>
+  <si>
+    <t>Computational and structural biotechnology journal</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>Management of enzyme diversity in high-performance cellulolytic cocktails.</t>
+  </si>
+  <si>
+    <t>BACKGROUND: Modern biorefineries require enzymatic cocktails of improved efficiency to generate fermentable sugars from lignocellulosic biomass. Cellulolytic fungi, among other microorganisms, have demonstrated the highest potential in terms of enzymatic productivity, complexity and efficiency. On the other hand, under cellulolytic-inducing conditions, they often produce a considerable diversity of carbohydrate-active enzymes which allow them to adapt to changing environmental conditions. However, industrial conditions are fixed and adjusted to the optimum of the whole cocktail, resulting in underperformance of individual enzymes. RESULTS: One of these cellulolytic cocktails from Myceliophthora thermophila has been analyzed here by means of LC-MS/MS. Pure GH6 family members detected have been characterized, confirming previous studies, and added to whole cocktails to compare their contribution in the hydrolysis of industrial substrates. Finally, independent deletions of two GH6 family members, as an example of the enzymatic diversity management, led to the development of a strain producing a more efficient cellulolytic cocktail. CONCLUSIONS: These data indicate that the deletion of noncontributive cellulases (here EG VI) can increase the cellulolytic efficiency of the cocktail, validating the management of cellulase diversity as a strategy to obtain improved fungal cellulolytic cocktails.</t>
+  </si>
+  <si>
+    <t>['Bioethanol', 'Cellulolytic cocktail improvement', 'Enzymatic hydrolysis', 'Lignocellulosic biomass']</t>
+  </si>
+  <si>
+    <t>Modifying Surface Charges of a Thermophilic Laccase Toward Improving Activity and Stability in Ionic Liquid.</t>
+  </si>
+  <si>
+    <t>The multicopper oxidase enzyme laccase holds great potential to be used for biological lignin valorization alongside a biocompatible ionic liquid (IL). However, the IL concentrations required for biomass pretreatment severely inhibit laccase activity. Due to their ability to function in extreme conditions, many thermophilic enzymes have found use in industrial applications. The thermophilic fungal laccase from Myceliophthora thermophila was found to retain high levels of activity in the IL [C(2)C(1)Im][EtSO(4)], making it a desirable biocatalyst to be used for lignin valorization. In contrast to [C(2)C(1)Im][EtSO(4)], the biocompatibility of [C(2)C(1)Im][OAC] with the laccase was markedly lower. Severe inhibition of laccase activity was observed in 15% [C(2)C(1)Im][OAc]. In this study, the enzyme surface charges were modified via acetylation, succinylation, cationization, or neutralization. However, these modifications did not show significant improvement in laccase activity or stability in [C(2)C(1)Im][OAc]. Docking simulations show that the IL docks close to the T1 catalytic copper, likely interfering with substrate binding. Although additional docking locations for [OAc](-) are observed after making enzyme modifications, it does not appear that these locations play a role in the inhibition of enzyme activity. The results of this study could guide future enzyme engineering efforts by showing that the inhibition mechanism of [C(2)C(1)Im][OAc] toward M. thermophila laccase is likely not dependent upon the IL interacting with the enzyme surface.</t>
+  </si>
+  <si>
+    <t>['docking simulation', 'ionic liquid', 'lignin', 'lignin degrading enzymes', 'surface modifacation']</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Improved Production of Xylanase in Pichia pastoris and Its Application in Xylose Production From Xylan.</t>
+  </si>
+  <si>
+    <t>Xylanases with high specific activity has been focused with great interest as a useful enzyme in biomass utilization. The production of recombinant GH11 xylanase (MYCTH_56237) from Myceliophthora thermophila has been improved through N-terminal signal peptide engineering in P. pastoris. The production of newly recombinant xylanase (termed Mtxyn11C) was improved from 442.53 to 490.7 U/mL, through a replacement of alpha-factor signal peptide with the native xylanase signal peptide segment (MVSVKAVLLLGAAGTTLA) in P. pastoris. Scaling up of Mtxyn11C production in a 7.5 L fermentor was improved to the maximal production rate of 2503 U/mL. In this study, the degradation efficiency of Mtxyn11C was further examined. Analysis of the hydrolytic mode of action towards the birchwood xylan (BWX) revealed that Mtxyn11C was clearly more effective than commercial xylanase and degrades xylan into xylooligosaccharides (xylobiose, xylotriose, xylotetraose). More importantly, Mtxyn11C in combination with a single multifunctional xylanolytic enzyme, improved the hydrolysis of BWX into single xylose by 40%. Altogether, this study provided strategies for improved production of xylanase together with rapid conversion of xylose from BWX, which provides sustainable, cost-effective and environmental friendly approaches to produce xylose/XOSs for biomass energy or biofuels production.</t>
+  </si>
+  <si>
+    <t>['Myceliophthora thermophila', 'Pichia pastoris', 'hydrolytic activity', 'improved production', 'xylan', 'xylanase', 'xylose']</t>
+  </si>
+  <si>
+    <t>Quantification of the catalytic performance of C1-cellulose-specific lytic polysaccharide monooxygenases.</t>
+  </si>
+  <si>
+    <t>Lytic polysaccharide monooxygenases (LPMOs) have recently been shown to significantly enhance the degradation of recalcitrant polysaccharides and are of interest for the production of biochemicals and bioethanol from plant biomass. The copper-containing LPMOs utilize electrons, provided by reducing agents, to oxidatively cleave polysaccharides. Here, we report the development of a beta-glucosidase-assisted method to quantify the release of C1-oxidized gluco-oligosaccharides from cellulose by two C1-oxidizing LPMOs from Myceliophthora thermophila C1. Based on this quantification method, we demonstrate that the catalytic performance of both MtLPMOs is strongly dependent on pH and temperature. The obtained results indicate that the catalytic performance of LPMOs depends on the interaction of multiple factors, which are affected by both pH and temperature.</t>
+  </si>
+  <si>
+    <t>['Lignocellulose', 'Lytic polysaccharide monooxygenase', 'Plant biomass', 'Reducing agent', 'beta-Glucosidase']</t>
+  </si>
+  <si>
+    <t>Coupling the pretreatment and hydrolysis of lignocellulosic biomass by the expression of beta-xylosidases.</t>
+  </si>
+  <si>
+    <t>Thermochemical pretreatment and enzymatic hydrolysis are the areas contributing most to the operational costs of second generation ethanol in lignocellulosic biorefineries. The improvement of lignocellulosic enzyme cocktails has been significant in the recent years. Although the needs for the reduction of the energy intensity and chemical consumption in the pretreatment step are well known, the reduction of the severity of the process strongly affects the enzymatic hydrolysis yield. To explore the formulation requirements of the well known cellulolytic cocktail from Myceliophthora thermophila on mild pretreated raw materials, this cocktail was tested on steam exploded corn stover without acid impregnation. The low hemicellulose yield and significant accumulation of xylobiose compared with the standard pretreated material obtained with dilute acid impregnation evidenced a clear limitation in the conversion of xylan to xylose. In order to complement the beta-xylosidase limitation, a selection of enzymes was expressed and tested in this fungus. A controlled expression of xylosidases from Aspergillus nidulans, Aspergillus fumigatus, and Fusarium oxysporum allowed recovering hemicellulose yields reached with standard acid treated material. The results underline the need of parallel development of the pretreatment process with the optimization of the formulation of the enzymatic cocktails.</t>
+  </si>
+  <si>
+    <t>['beta-xylosidase', 'biofuels', 'biorefinery', 'enzymatic hydrolysis', 'lignocellulosic biomass']</t>
+  </si>
+  <si>
+    <t>The Highly Productive Thermothelomyces heterothallica C1 Expression System as a Host for Rapid Development of Influenza Vaccines.</t>
+  </si>
+  <si>
+    <t>(1) Influenza viruses constantly change and evade prior immune responses, forcing seasonal re-vaccinations with updated vaccines. Current FDA-approved vaccine manufacturing technologies are too slow and/or expensive to quickly adapt to mid-season changes in the virus or to the emergence of pandemic strains. Therefore, cost-effective vaccine technologies that can quickly adapt to newly emerged strains are desirable. (2) The filamentous fungal host Thermothelomyces heterothallica C1 (C1, formerly Myceliophthora thermophila) offers a highly efficient and cost-effective alternative to reliably produce immunogens of vaccine quality at large scale. (3) We showed the utility of the C1 system expressing hemagglutinin (HA) and a HA fusion protein from different H1N1 influenza A virus strains. Mice vaccinated with the C1-derived HA proteins elicited anti-HA immune responses similar, or stronger than mice vaccinated with HA products derived from prototypical expression systems. A challenge study demonstrated that vaccinated mice were protected against the aggressive homologous viral challenge. (4) The C1 expression system is proposed as part of a set of protein expression systems for plug-and-play vaccine manufacturing platforms. Upon the emergence of pathogens of concern these platforms could serve as a quick solution for producing enough vaccines for immunizing the world population in a much shorter time and more affordably than is possible with current platforms.</t>
+  </si>
+  <si>
+    <t>['Thermothelomyces heterothallica C1', 'filamentous fungi', 'influenza vaccine', 'recombinant protein expression', 'targeted influenza hemagglutinin', 'trimeric influenza hemagglutinin']</t>
+  </si>
+  <si>
+    <t>2022 Jan 20</t>
+  </si>
+  <si>
+    <t>Functionalization of pectin with laccase-mediated oxidation products of ferulic acid.</t>
+  </si>
+  <si>
+    <t>Pectin is a natural biopolymer extracted mostly from citrus peel, sugar beet and apple pomace. In order to improve its functional properties and then to enlarge the field of its potential applications, functionalization reaction of citrus pectin with ferulic acid (FA)-oxidation products was performed in aqueous medium, at 30 degrees C and pH7.5, in the presence of Myceliophthora thermophila laccase as biocatalyst. The conjugation between FA-oxidation products and pectin was confirmed using FTIR, UV-Vis and LC-MS analyses. The obtained results suggested that covalent bonds were between the pectin carboxyl groups and FA-oxidation products between the pectin carboxyl groups and FA-oxidation products. The determination of the total phenolic content showed that the modified pectin contained 5 times more phenols than the native pectin. In view of these results, this enzymatic procedure appears as a promising way to provide new pectin-based polymers that are expected to present new properties of interest.</t>
+  </si>
+  <si>
+    <t>['Ferulic acid', 'Functionalization', 'Laccase', 'Oxidation', 'Pectin']</t>
+  </si>
+  <si>
+    <t>Conductive Cotton by In Situ Laccase-Polymerization of Aniline.</t>
+  </si>
+  <si>
+    <t>Conductive cotton fabrics were obtained via in situ aniline polymerization by laccase from Myceliophthora thermophila under mild reaction conditions without the addition of strong proton acids. The reactions were conducted using two types of reactors, namely a water bath (WB) and an ultrasonic bath (US), and the role of a mediator, 1-hydroxybenzotriazol (HBT), on the laccase-assisted polymerization of aniline was investigated. A similar polymerization degree was obtained when using both reactors-however, the ultrasonic bath allowed the experiments to be conducted in shorter periods of time (24 h for WB vs. 2 h for US). The data obtained also revealed that the mediator (1-hydroxybenzotriazol-HBT) played a crucial role in aniline oxidation. A higher conversion yield and polymerization degree were obtained when the reaction was conducted in the presence of this compound, as confirmed by MALDI-TOF analysis. The cotton fabrics coated with polyaniline presented deep coloration and conductivity, especially when the mediator was included on the reactional system. The results obtained are a step forward in the enzymatic polymerization of aniline with the purpose of obtaining coloured conductive textile surfaces, with potential applications in wearable electronics.</t>
+  </si>
+  <si>
+    <t>['1-hydroxybenzotriazol (HBT)', 'coatings', 'conductive cotton', 'laccase', 'polyaniline']</t>
+  </si>
+  <si>
+    <t>2018 Sep 14</t>
+  </si>
+  <si>
+    <t>Functional Evolution in Orthologous Cell-encoded RNA-dependent RNA Polymerases.</t>
+  </si>
+  <si>
+    <t>Many eukaryotic organisms encode more than one RNA-dependent RNA polymerase (RdRP) that probably emerged as a result of gene duplication. Such RdRP paralogs often participate in distinct RNA silencing pathways and show characteristic repertoires of enzymatic activities in vitro However, to what extent members of individual paralogous groups can undergo functional changes during speciation remains an open question. We show that orthologs of QDE-1, an RdRP component of the quelling pathway in Neurospora crassa, have rapidly diverged in evolution at the amino acid sequence level. Analyses of purified QDE-1 polymerases from N. crassa (QDE-1(Ncr)) and related fungi, Thielavia terrestris (QDE-1(Tte)) and Myceliophthora thermophila (QDE-1(Mth)), show that all three enzymes can synthesize RNA, but the precise modes of their action differ considerably. Unlike their QDE-1(Ncr) counterpart favoring processive RNA synthesis, QDE-1(Tte) and QDE-1(Mth) produce predominantly short RNA copies via primer-independent initiation. Surprisingly, a 3.19 A resolution crystal structure of QDE-1(Tte) reveals a quasisymmetric dimer similar to QDE-1(Ncr) Further electron microscopy analyses confirm that QDE-1(Tte) occurs as a dimer in solution and retains this status upon interaction with a template. We conclude that divergence of orthologous RdRPs can result in functional innovation while retaining overall protein fold and quaternary structure.</t>
+  </si>
+  <si>
+    <t>['RNA interference (RNAi)', 'RNA polymerase', 'RNA-dependent RNA polymerase', 'electron microscopy (EM)', 'protein evolution', 'x-ray crystallography']</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>2016 Apr 22</t>
+  </si>
+  <si>
+    <t>Anti-inflammatory and anti-oxidant properties of laccase-synthesized phenolic-O-carboxymethyl chitosan hydrogels.</t>
+  </si>
+  <si>
+    <t>A bioactive O-carboxymethyl chitosan (CMCS) hydrogel crosslinked with natural phenolics with potential application in wound dressings was synthesized using a laccase from Myceliophthora thermophila (MTL). The highest degree of cross-linking (49.7%) was achieved with catechol. All the phenolic-CMCS hydrogels synthesized showed excellent anti-oxidant properties with a free radical scavenging activity up to 4-fold higher than in the absence of the phenolics, as quantified by the di(phenyl)-(2,4,6-trinitrophenyl)iminoazanium (DPPH) assay. In addition, the hydrogels produced showed an anti-inflammatory effect as evidenced by the inhibition of enzymes [myeloperoxidase (MPO), matrix-metalloproteinase-1 (MMP-1) and human neutrophil elastase (HNE)] over-expressed in chronic wounds. Sinapyl-CMCS hydrogels showed an MMP-1 inhibition of 37%. Further, the phenolic-CMCS hydrogels did not affect the viability of the NIH 3T3 mouse fibroblast cell line and were also able to slowly release human fibroblast growth factor 2, reaching 48.3% over a period of 28days. This study thus shows the possibility of synthesizing multifunctional bioactive chitosan based hydrogels with anti-oxidant and anti-inflammatory properties using natural occurring phenolics as crosslinkers.</t>
+  </si>
+  <si>
+    <t>['Anti-inflammatory', 'Anti-oxidant', 'Chitosan hydrogel', 'Laccase', 'Phenolics', 'Wound enzymes']</t>
+  </si>
+  <si>
+    <t>2018 Jan 25</t>
+  </si>
+  <si>
+    <t>Immobilization of laccase on epoxy-functionalized silica and its application in biodegradation of phenolic compounds.</t>
+  </si>
+  <si>
+    <t>A novel method of laccase immobilization on epoxy-functionalized silica particles was developed. Laccase from Myceliophthora thermophila was covalently immobilized onto epoxy-functionalized matrix by nucleophilic attack of amino groups of laccase to epoxy groups of the support. The enzyme loading on the support was about 30 mg/g under the optimum conditions (pH 4.5, 24 h). The effect of pH, temperature and organic solvent on immobilized enzyme activity was determined and compared with those of free enzyme. In general the immobilized enzyme was found to be stabilized compared to the free enzyme. Lineweaver-Burk plots were used to calculate kinetic parameters for ABTS oxidation. K(M) values were 24.0 and 25.3 muM while v(max) values were 10.0 and 1.6 muM min(-1) for free and immobilized laccase, respectively. The performance of the biocatalyst was evaluated by the degradation of phenolic compounds including phenol, p-chlorophenol and catechol. The removal efficiency of catechol by immobilized laccase was about 95% after 2 h.</t>
+  </si>
+  <si>
+    <t>['Immobilization', 'Laccase', 'Phenol biodegradation']</t>
+  </si>
+  <si>
+    <t>Iran. Electronic address: m.mohammadi@nigeb.ac.ir</t>
+  </si>
+  <si>
+    <t>2018 Apr 1</t>
+  </si>
+  <si>
+    <t>Enhanced production of bacterial xylanase and its utility in saccharification of sugarcane bagasse.</t>
+  </si>
+  <si>
+    <t>An investigation was carried out using sugarcane bagasse as the agricultural residue to study the optimization of xylanase production by solid-state fermentation. Maximum xylanase production (20.35 U/g substrate) was achieved by Bacillus substilis subsp. subtilis JJBS250 using 'one variable at a time approach' at pH 7.0, 40  degrees C after 48 h. After statistical optimization by response surface methodology (RSM) there was 4.82-fold improvement in xylanase production (98.16 U/g substrate). Further optimization of untreated and sodium carbonate pretreated sugarcane bagasse enzymatic hydrolysis was carried out using both bacterial (Bacillus substilis subsp. subtilis JJBS250) and fungal (Myceliophthora thermophila BJTLRMDU3) xylanases that showed high amount of reducing sugar liberation from untreated sugarcane bagasse (124.24 mg/g substrate) as compared to pretreated (76.23 mg/g substrate) biomass. Furthermore, biophysical characterization of untreated and sodium carbonate pretreated sugarcane bagasse using Fourier-transform infrared spectroscopy (FTIR), X-ray diffraction (XRD) and scanning electron microscopy (SEM), revealed the structural changes in the pretreated biomass.</t>
+  </si>
+  <si>
+    <t>['Bacillus subtilis subsp. subtilis JJBS250', 'Pretreatment', 'Response surface methodology', 'Solid-state fermentation', 'Sugarcane bagasse', 'Xylanase']</t>
+  </si>
+  <si>
+    <t>2020 Jun</t>
+  </si>
+  <si>
+    <t>Isolation and characterization of a new cytotoxic polyketide-amino acid hybrid from Thermothelomyces thermophilus ATCC 42464.</t>
+  </si>
+  <si>
+    <t>Fungi are a rich source of novel anticancer compounds. Bioassay-guided isolation has led to the isolation of four polyketide-amino acid hybrid compounds with trans-fused decalin system from the fungus Thermothelomyces thermophilus ATCC 42464 (=Myceliophthora thermophila ATCC 42464): myceliothermophins A, B, E and F (1-4). The structure of the new compound (myceliothermophin F, compound 4) was clearly determined by a combination of nuclear magnetic resonance (NMR) analysis and high-resolution electrospray ionisation mass spectroscopy (HRESIMS). The new compound exhibited promising cytotoxicity against some cell lines derived from colorectal carcinoma, hepatic carcinoma and gastric carcinoma, indicating that compounds with trans-fused decalin system would be promising in the course of developing novel anticancer drugs.</t>
+  </si>
+  <si>
+    <t>['Polyketide-amino acid', 'Thermothelomyces thermophilus', 'anticancer', 'decalin', 'hybrid']</t>
+  </si>
+  <si>
+    <t>Natural product research</t>
+  </si>
+  <si>
+    <t>2021 Jun</t>
+  </si>
+  <si>
+    <t>Influence of mediators on laccase catalyzed radical formation in lignin.</t>
+  </si>
+  <si>
+    <t>Laccases (EC 1.10.3.2) catalyze oxidation of phenolic groups in lignin to phenoxyl radicals during reduction of O(2) to H(2)O. Here, we examine the influence on this radical formation of mediators which are presumed to act by shuttling electrons between the laccase and the subunits in lignin that the enzyme cannot approach directly. Treatments of three different lignins with laccase-mediator-systems (LMS) including laccases derived from Trametes versicolor and Myceliophthora thermophila, respectively, and four individual mediators, 1-hydroxybenzotriazole (HBT), N-hydroxyphthalimide (HPI), 2,2,6,6-tetramethylpiperidin-1-yloxy (TEMPO), and 2,2'-azino-bis(3-ethylbenzothiazoline-6-sulphonic acid) (ABTS) were assessed by real time electron paramagnetic resonance measurements. Radical steady state concentrations and radical formation rates were quantified. LMS treatments with 500 muM N-OH type mediators (HPI or HBT) did not affect the lignin radical formation, but increased doses of those mediators (5 mM) surprisingly led to significantly decreased radical formation rates and lowered steady state radical concentrations. Laccase-TEMPO treatment at a 5 mM mediator dose was the only system that significantly increased steady state radical concentration and rate of radical formation in beech organosolv lignin. The data suggest that electron shuttling by mediators is not a significant general mechanism for enhancing laccase catalyzed oxidation of biorefinery lignin substrates, and the results thus provide a new view on laccase catalyzed lignin modification.</t>
+  </si>
+  <si>
+    <t>['ABTS', 'Electron paramagnetic resonance (EPR)', 'HBT', 'HPI', 'Laccase-mediator systems', 'Myceliophthora thermophila', 'TEMPO', 'Trametes versicolor']</t>
+  </si>
+  <si>
+    <t>Improving enzyme production by solid-state cultivation in packed-bed bioreactors by changing bed porosity and airflow distribution.</t>
+  </si>
+  <si>
+    <t>Enzymes production by solid-state cultivation in packed-bed bioreactor needs to be improved by mathematical modeling and also by experimentation. In this work, a mixture of sugarcane bagasse and wheat bran was used for the growth of the fungus Myceliophthora thermophila I-1D3b, able to secrete endoglucanase and xylanase, enzymes of interest in the second-generation ethanol production. Bench and pilot-scale bioreactors were used for the experiments, while critical parameters as bed porosity and airflow distribution were evaluated. Results showed enzymes with higher activities for the most porous medium, even though the less substrate amount to be cultivated. For the pilot-scale bioreactor, only the most porous medium was evaluated using different airflow distribution techniques. Using an inner tube for air supply resulted in more homogeneous enzyme production, with higher activities. The results here presented will be helpful for the scale-up of this class of bioreactor into industrial apparatuses.</t>
+  </si>
+  <si>
+    <t>['Cellulase', 'Fixed bioreactor', 'Packing density', 'Scale-up', 'Solid-state fermentation']</t>
+  </si>
+  <si>
+    <t>Brazil. lopesperezcaroline@gmail.com</t>
+  </si>
+  <si>
+    <t>2021 Mar</t>
+  </si>
+  <si>
+    <t>A novel fungal GH30 xylanase with xylobiohydrolase auxiliary activity.</t>
+  </si>
+  <si>
+    <t>BACKGROUND: The main representatives of hemicellulose are xylans, usually decorated beta-1,4-linked d-xylose polymers, which are hydrolyzed by xylanases. The efficient utilization and complete hydrolysis of xylans necessitate the understanding of the mode of action of xylan degrading enzymes. The glycoside hydrolase family 30 (GH30) xylanases comprise a less studied group of such enzymes, and differences regarding the substrate recognition have been reported between fungal and bacterial GH30 xylanases. Besides their role in the utilization of lignocellulosic biomass for bioenergy, such enzymes could be used for the tailored production of prebiotic xylooligosaccharides (XOS) due to their substrate specificity. RESULTS: The expression of a putative GH30_7 xylanase from the fungus Thermothelomyces thermophila (synonyms Myceliophthora thermophila, Sporotrichum thermophile) in Pichia pastoris resulted in the production and isolation of a novel xylanase with unique catalytic properties. The novel enzyme designated TtXyn30A, exhibited an endo- mode of action similar to that of bacterial GH30 xylanases that require 4-O-methyl-d-glucuronic acid (MeGlcA) decorations, in contrast to most characterized fungal ones. However, TtXyn30A also exhibited an exo-acting catalytic behavior by releasing the disaccharide xylobiose from the non-reducing end of XOS. The hydrolysis products from beechwood glucuronoxylan were MeGlcA substituted XOS, and xylobiose. The major uronic XOS (UXOS) were the aldotriuronic and aldotetrauronic acid after longer incubation indicating the ability of TtXyn30A to cleave linear parts of xylan and UXOS as well. CONCLUSIONS: Hereby, we reported the heterologous production and biochemical characterization of a novel fungal GH30 xylanase exhibiting endo- and exo-xylanase activity. To date, considering its novel catalytic properties, TtXyn30A shows differences with most characterized fungal and bacterial GH30 xylanases. The discovered xylobiohydrolase mode of action offers new insights into fungal enzymatic systems that are employed for the utilization of lignocellulosic biomass. The recombinant xylanase could be used for the production of X2 and UXOS from glucuronoxylan, which in turn would be utilized as prebiotics carrying manifold health benefits.</t>
+  </si>
+  <si>
+    <t>['GH30 xylanase', 'Glucuronoxylan', 'Thermothelomyces thermophila', 'Xylobiohydrolase', 'Xylooligosaccharides']</t>
+  </si>
+  <si>
+    <t>Greece. ISNI: 0000 0001 2185 9808. GRID: grid.4241.3</t>
+  </si>
+  <si>
+    <t>Polymer functionalization through an enzymatic process: Intermediate products characterization and their grafting onto gum Arabic.</t>
+  </si>
+  <si>
+    <t>The modification of gum Arabic with ferulic acid oxidation products was performed in aqueous medium, at 30  degrees C and pH 7.5, in the presence of Myceliophthora thermophila laccase as biocatalyst. First, this study aimed to investigate the structures of the oxidation products of ferulic acid that could possibly be covalently grafted onto gum Arabic. HPLC analyses revealed that this reaction produced several oxidation products, whose structures were investigated using LC-MS/MS analyses (liquid chromatography-mass spectrometry with mass fragmentation analyses) and NMR experiments. The chemical structure of one intermediate reaction product was fully elucidated as the 2-(4-hydroxy-3-methoxyphenyl)-4-[(4-hydroxy-3-methoxyphenyl) methylidene] cyclobutane-1, 3-dione, called by the authors cyclobutadiferulone. Secondly, this study aimed to locate the grafting of the oxidation products onto gum Arabic by performing several NMR experiments. This study did not determine how much and specifically which oxidation products were grafted but some of them were undeniably present onto modified gum Arabic, close to the glucuronic acid C5 carbon or close to the galactose C6 carbon.</t>
+  </si>
+  <si>
+    <t>['Ferulic acid', 'Functionalization', 'Gum Arabic', 'Oxidation product', 'Phenol grafting']</t>
+  </si>
+  <si>
+    <t>2021 Feb 1</t>
+  </si>
+  <si>
+    <t>N-Linked glycans are an important component of the processive machinery of cellobiohydrolases.</t>
+  </si>
+  <si>
+    <t>Cellobiohydrolases (CBHs), belonging to glycoside hydrolase families 6 and 7 (GH6 and GH7), are the major components of cellulase systems of filamentous fungi involved in biodegradation of cellulose in nature. Previous studies demonstrated that N-linked glycans in the catalytic domains of GH7 CBHs significantly affect the enzyme activity against cellulosic substrates. The influence of N-linked glycans on the activity and processivity of recombinant GH6 CBH II from Penicillium verruculosum (PvCel6A) was studied using site-directed mutagenesis of the respective Asn residues. Depending on the position of N-glycans on the surface of a protein globule, they affected the enzyme activity against cellulose either negatively or positively. The decrease or increase in the degree of processivity of recombinant forms of PvCel6A generally correlated with activity changes against Avicel. The mechanism of the N-glycan influence seems to be universal for GH6 and GH7 CBHs. The observed effects for CBHs from both families are explained in terms of a mechanistic model that also makes clear our previously published data on the highly active CBH IIb from Myceliophthora thermophila (MtCel6B). This study, together with data of other researchers, strongly suggests that the N-linked glycans in the catalytic domains of GH6 and GH7 CBHs are involved in processive catalytic machinery of these enzymes. Data obtained should be taken into account during development of new and more effective biocatalysts by protein engineering techniques.</t>
+  </si>
+  <si>
+    <t>['Cellobiohydrolase', 'Cloning', 'N-glycosylation', 'Processivity', 'Site-directed mutagenesis']</t>
+  </si>
+  <si>
+    <t>2017 Jan</t>
+  </si>
+  <si>
+    <t>Enzymatic versatility and thermostability of a new aryl-alcohol oxidase from Thermothelomyces thermophilus M77.</t>
+  </si>
+  <si>
+    <t>Background Fungal aryl-alcohol oxidases (AAOx) are extracellular flavoenzymes that belong to glucose-methanol-choline oxidoreductase family and are responsible for the selective conversion of primary aromatic alcohols into aldehydes and aromatic aldehydes to their corresponding acids, with concomitant production of hydrogen peroxide (H(2)O(2)) as by-product. The H(2)O(2) can be provided to lignin degradation pathway, a biotechnological property explored in biofuel production. In the thermophilic fungus Thermothelomyces thermophilus (formerly Myceliophthora thermophila), just one AAOx was identified in the exo-proteome. Methods The glycosylated and non-refolded crystal structure of an AAOx from T. thermophilus at 2.6 A resolution was elucidated by X-ray crystallography combined with small-angle X-ray scattering (SAXS) studies. Moreover, biochemical analyses were carried out to shed light on enzyme substrate specificity and thermostability. Results This flavoenzyme harbors a flavin adenine dinucleotide as a cofactor and is able to oxidize aromatic substrates and 5-HMF. Our results also show that the enzyme has similar oxidation rates for bulky or simple aromatic substrates such as cinnamyl and veratryl alcohols. Moreover, the crystal structure of MtAAOx reveals an open active site, which might explain observed specificity of the enzyme. Conclusions MtAAOx shows previously undescribed structural differences such as a fully accessible catalytic tunnel, heavy glycosylation and Ca(2+) binding site providing evidences for thermostability and activity of the enzymes from AA3_2 subfamily. General significance Structural and biochemical analyses of MtAAOx could be important for comprehension of aryl-alcohol oxidases structure-function relationships and provide additional molecular tools to be used in future biotechnological applications.</t>
+  </si>
+  <si>
+    <t>['AA3', 'AAOx', 'Aryl-alcohol oxidase', 'Thermostability', 'Thermothelomyces thermophilus', 'X-ray structure']</t>
+  </si>
+  <si>
+    <t>Brazil. Electronic address: marcokadowaki@gmail.com</t>
+  </si>
+  <si>
+    <t>2020 Oct</t>
+  </si>
+  <si>
+    <t>FTacV study of electroactive immobilized enzyme/free substrate reactions: Enzymatic catalysis of epinephrine by a multicopper oxidase from Thermothelomyces thermophila.</t>
+  </si>
+  <si>
+    <t>In the present work, a kinetic analysis is made concerning the reaction of an electroactive immobilized enzyme with a free substrate, based on a Michaelis-Menten scheme. The proposed kinetic equations are investigated numerically for conditions describing large amplitude fast Fourier transform alternating current voltammetry (FTacV), under different reaction states (transient or steady state for the reaction intermediate as well as quasi or complete reversibility of the electrochemical step). The dependence of two chief observables that occur from the analysis of the results of the method, that is, the maximum of the harmonics and the potential shift of the corresponding dominant peaks, on substrate concentration is presented. The FTacV method is applied experimentally for an immobilized laccase-like multicopper oxidase from Thermothelomyces thermophila, TtLMCO1, and its reaction with epinephrine. From the experimental findings it is shown that the intrinsic characteristics of the system do not lead to the extraction of the desired kinetic data although indications on the relation between the kinetic constants is revealed. Finally, the response of the third harmonic for the first additions of epinephrine at subnanomolarity range can be exploited for the detection of epinephrine at rather low concentrations.</t>
+  </si>
+  <si>
+    <t>['Direct electron transfer', 'Epinephrine', 'FTacV', 'Laccase', 'Multicopper oxidase', 'Thermothelomyces thermophila']</t>
+  </si>
+  <si>
+    <t>2020 Aug</t>
+  </si>
+  <si>
+    <t>Assessing the use of nanoimmobilized laccases to remove micropollutants from wastewater.</t>
+  </si>
+  <si>
+    <t>Enzymes immobilization is a useful way to allow enzyme reuse and increase their stability. A high redox potential laccase from Trametes versicolor (TvL) and a low redox potential, but commercially available low-cost laccase from Myceliophthora thermophila (MtL), were successfully immobilized and co-immobilized onto fumed silica nanoparticles (fsNP). Enzyme loads of 1.78 +/- 0.07, 0.69 +/- 0.03, and 1.10 +/- 0.01 U/mg fsNP were attained for the optimal doses of TvL, MtL, and co-immobilized laccases, respectively. In general, the laccase-fsNP conjugates showed a higher resistance against an acidic pH value (i.e., pH 3), and a higher storage stability than free enzymes. In addition, immobilized enzymes exhibited a superior long-term stability than free laccases when incubated in a secondary effluent from a municipal wastewater treatment plant (WWTP). For instance, the residual activity after 2 weeks for the co-immobilized laccases and the mixture of free laccases were 40.2 +/- 2.5% and 16.8 +/- 1.0%, respectively. The ability of the laccase-fsNP to remove a mixture of (14)C-bisphenol A (BPA) and (14)C-sodium diclofenac (DCF) from spiked secondary effluents was assessed in batch experiments. The catalytic efficiency was highly dependent on both the microbial source and state of the biocatalyst. The high redox potential TvL in free form attained a four-fold higher percentage of BPA transformation than the free MtL. Compared to free laccases, immobilized enzymes led to much slower rates of BPA transformation. For instance, after 24 h, the percentages of BPA transformation by 1000 U/L of a mixture of free laccases or co-immobilized enzymes were 67.8 +/- 5.2 and 27.0 +/- 3.9%, respectively. Nevertheless, the use of 8000 U/L of co-immobilized laccase led to a nearly complete removal of BPA, despite the unfavorable conditions for laccase catalysis (pH ~ 8.4). DCF transformation was not observed for any of the enzymatic systems, showing that this compound is highly recalcitrant toward laccase oxidation under realistic conditions.</t>
+  </si>
+  <si>
+    <t>['Enzyme immobilization', 'Fumed silica nanoparticles', 'Laccase', 'Micropollutants', 'Secondary effluent']</t>
+  </si>
+  <si>
+    <t>Environmental science and pollution research international</t>
+  </si>
+  <si>
+    <t>Spain. adriana.arca@rai.usc.es</t>
+  </si>
+  <si>
+    <t>2016 Feb</t>
+  </si>
+  <si>
+    <t>Membraneless glucose/oxygen enzymatic fuel cells using redox hydrogel films containing carbon nanotubes.</t>
+  </si>
+  <si>
+    <t>Co-immobilisation of three separate multiple blue copper oxygenases, a Myceliophthora thermophila laccase, a Streptomyces coelicolor laccase and a Myrothecium verrucaria bilirubin oxidase, with an [Os(2,2'-bipyridine)2 (polyvinylimidazole)10Cl](+/2+) redox polymer in the presence of multi-walled carbon nanotubes (MWCNTs) on graphite electrodes results in enzyme electrodes that produce current densities above 0.5 mA cm(-2) for oxygen reduction at an applied potential of 0 V versus Ag/AgCl. Fully enzymatic membraneless fuel cells are assembled with the oxygen-reducing enzyme electrodes connected to glucose-oxidising anodes based on co-immobilisation of glucose oxidase or a flavin adenine dinucleotide-dependent glucose dehydrogenase with an [Os(4,4'-dimethyl-2,2'-bipyridine)2(polyvinylimidazole)10Cl](+/2+) redox polymer in the presence of MWCNTs on graphite electrodes. These fuel cells can produce power densities of up to 145 muW cm(-2) on operation in pH 7.4 phosphate buffer solution at 37  degrees C containing 150 mM NaCl, 5 mM glucose and 0.12 mM O2. The fuel cells based on Myceliophthora thermophila laccase enzyme electrodes produce the highest power density if combined with glucose oxidase-based anodes. Although the maximum power density of a fuel cell of glucose dehydrogenase and Myceliophthora thermophila laccase enzyme electrodes decreases from 110 muW cm(-2) in buffer to 60 muW cm(-2) on testing in artificial plasma, it provides the highest power output reported to date for a fully enzymatic glucose-oxidising, oxygen-reducing fuel cell in artificial plasma.</t>
+  </si>
+  <si>
+    <t>['enzyme electrodes', 'fuel cells', 'glucose oxidation', 'oxygen reduction', 'redox chemistry']</t>
+  </si>
+  <si>
+    <t>Chemphyschem : a European journal of chemical physics and physical chemistry</t>
   </si>
   <si>
     <t>Ireland</t>
   </si>
   <si>
-    <t>2010 May 5</t>
-  </si>
-  <si>
-    <t>Breeding of a thermostable xylanase-producing strain of Myceliophthora thermophila by atmospheric room temperature plasma (ARTP) mutagenesis.</t>
-  </si>
-  <si>
-    <t>Introduction: Hemicellulose is an important component in lignocellulose materials, which is second only to cellulose, accounting for 15%-35% of the dry weight of plants. In the current situation of energy shortage, making full use of lignocellulose materials to produce fuel ethanol has become an important way to solve the energy problem. Xylanase plays a crucial role in the utilization of hemicellulose. It is a necessary means to reduce the cost of hemicellulose utilization by improving the activity of xylanase. Moreover, most naturally xylanases are mesophilic enzymes, which limits their industrial application. Methods:In this study, Myceliophthora thermophila was used to produce xylanases and a thermostable mutant M 2103 was obtained by atmospheric room temperature plasma (ARTP) mutagenesis. The research work started with exploring the effects of ARTP mutagenesis on the antioxidase system [superoxide dismutase (SOD), catalase (CAT), peroxidase (POD), polyphenol oxidase (PPO), and antioxidant capacity (AOC)] of M. thermophile, and found that superoxide dismutase activity increased by 221.13%, and polyphenol oxidase activity increased by 486.04% as compared with the original strain when the implantation time was 300 s. So as to determine the conditions for subsequent mutagenesis. Results and Discussion:For the mutant M 2103, the reaction temperature for xylanase production remained stable in the range of 70 degrees C-85 degrees C. Its optimum temperature was 75 degrees C, which was 15 degrees C higher than that of the original strain. And its xylanase activity increased by 21.71% as compared with the original strain. M 2103 displayed a significantly higher relative xylanase activity than the original strain in the acidic (pH 4.0-7.0) range, and the xylanase activity was relatively stable in the pH range of 6.0-8.5. These results provide an alternative biocatalyst for the production of xylooligosaccharide, and a potential usage of ARTP in the mutagenesis of thermostable mutant.</t>
-  </si>
-  <si>
-    <t>['ARTP', 'Myceliophthora thermophila', 'antioxidase', 'thermotolerant mutant', 'xylanase']</t>
-  </si>
-  <si>
-    <t>Stability and kinetic behavior of immobilized laccase from Myceliophthora thermophila in the presence of the ionic liquid 1-ethyl-3-methylimidazolium ethylsulfate.</t>
-  </si>
-  <si>
-    <t>The use of ionic liquids (ILs) as reaction media for enzymatic reactions has increased their potential because they can improve enzyme activity and stability. Kinetic and stability properties of immobilized commercial laccase from Myceliophthora thermophila in the water-soluble IL 1-ethyl-3-methylimidazolium ethylsulfate ([emim][EtSO4 ]) have been studied and compared with free laccase. Laccase immobilization was carried out by covalent binding on glyoxyl-agarose beads. The immobilization yield was 100%, and the activity was totally recovered. The Michaelis-Menten model fitted well to the kinetic data of enzymatic oxidation of a model substrate in the presence of the IL [emim][EtSO4 ]. When concentration of the IL was augmented, the values of Vmax for free and immobilized laccases showed an increase and slight decrease, respectively. The laccase-glyoxyl-agarose derivative improved the laccase stability in comparison with the free laccase regarding the enzymatic inactivation in [emim][EtSO4 ]. The stability of both free and immobilized laccase was slightly affected by small amounts of IL (&lt;50%). A high concentration of the IL (75%) produced a large inactivation of free laccase. However, immobilization prevented deactivation beyond 50%. Free and immobilized laccase showed a first-order thermal inactivation profile between 55 and 70 degrees C in the presence of the IL [emim][EtSO4 ]. Finally, thermal stability was scarcely affected by the presence of the IL.</t>
-  </si>
-  <si>
-    <t>['1-ethyl-3-methylimidazolium ethylsulfate', 'agarose', 'immobilization', 'ionic liquid', 'laccase', 'stability']</t>
-  </si>
-  <si>
-    <t>Biotechnology progress</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>2014 Jul-Aug</t>
-  </si>
-  <si>
-    <t>Optimized synthesis of novel prenyl ferulate performed by feruloyl esterases from Myceliophthora thermophila in microemulsions.</t>
-  </si>
-  <si>
-    <t>Five feruloyl esterases (FAEs; EC 3.1.1.73), FaeA1, FaeA2, FaeB1, and FaeB2 from Myceliophthora thermophila C1 and MtFae1a from M. thermophila ATCC 42464, were tested for their ability to catalyze the transesterification of vinyl ferulate (VFA) with prenol in detergentless microemulsions. Reaction conditions were optimized investigating parameters such as the medium composition, the substrate concentration, the enzyme load, the pH, the temperature, and agitation. FaeB2 offered the highest transesterification yield (71.5 +/- 0.2%) after 24 h of incubation at 30  degrees C using 60 mM VFA, 1 M prenol, and 0.02 mg FAE/mL in a mixture comprising of 53.4:43.4:3.2 v/v/v n-hexane:t-butanol:100 mM MOPS-NaOH, pH 6.0. At these conditions, the competitive side hydrolysis of VFA was 4.7-fold minimized. The ability of prenyl ferulate (PFA) and its corresponding ferulic acid (FA) to scavenge 1,1-diphenyl-2-picrylhydrazyl (DPPH) radicals was significant and similar (IC(50) 423.39 muM for PFA, 329.9 muM for FA). PFA was not cytotoxic at 0.8-100 muM (IC(50) 220.23 muM) and reduced intracellular reactive oxygen species (ROS) in human skin fibroblasts at concentrations ranging between 4 and 20 muM as determined with the dichloro-dihydro-fluorescein diacetate (DCFH-DA) assay.</t>
-  </si>
-  <si>
-    <t>['Antioxidant', 'DCFH-DA', 'DPPH', 'Feruloyl esterase', 'Myceliophthora thermophila', 'Prenyl ferulate', 'Transesterification']</t>
-  </si>
-  <si>
-    <t>2017 Apr</t>
-  </si>
-  <si>
-    <t>Characterization and application of a novel class II thermophilic peroxidase from Myceliophthora thermophila in biosynthesis of polycatechol.</t>
-  </si>
-  <si>
-    <t>A peroxidase from the thermophilic fungus Myceliophthora thermophila that belongs to ascomycete Class II based on PeroxiBase classification was functionally expressed in methylotrophic yeast Pichia pastoris. The putative peroxidase from the genomic DNA was successfully cloned in P. pastoris X-33 under the transcriptional control of the alcohol oxidase (AOX1) promoter. The heterologous production was greatly enhanced by the addition of hemin with a titer of 0.41 U mL(-1) peroxidase activity at the second day of incubation. The recombinant enzyme was purified to homogeneity (50 kDa) and characterized using a series of phenolic substrates that indicated similar characteristics with those of generic peroxidases. In addition, the enzyme was found thermostable, retaining its activity for temperatures up to 60  degrees C after eight hours incubation. Moreover, the enzyme displayed remarkable H2O2 stability, retaining more than 80% of its initial activity after 24h incubation in 5000-fold molar excess of H2O2. The ability of the peroxidase to polymerize catechol at high superoxide concentrations, together with its high thermostability and substrate specificity, indicate a potential commercial significance of the enzyme.</t>
-  </si>
-  <si>
-    <t>['Class II peroxidase', 'Heterologous production', 'Myceliophthora thermophila', 'Pichia pastoris', 'Polycatechol', 'Thermostability']</t>
-  </si>
-  <si>
-    <t>2015 Jul-Aug</t>
-  </si>
-  <si>
-    <t>Immobilisation on mesoporous silica and solvent rinsing improve the transesterification abilities of feruloyl esterases from Myceliophthora thermophila.</t>
-  </si>
-  <si>
-    <t>The immobilisation of four feruloyl esterases (FAEs) (FaeA1, FaeA2, FaeB1, FaeB2) from the thermophilic fungus Myceliophthora thermophila C1 was studied and optimised via physical adsorption onto various mesoporous silica particles with pore diameters varying from 6.6nm to 10.9nm. Using crude enzyme preparations, enrichment of immobilised FAEs was observed, depending on pore diameter and protein size. The immobilised enzymes were successfully used for the synthesis of butyl ferulate through transesterification of methyl ferulate with 1-butanol. Although the highest butyl ferulate yields were obtained with free enzyme, the synthesis-to-hydrolysis ratio was higher when using immobilised enzymes. Over 90% of the initial activity was observed in a reusability experiment after nine reaction cycles, each lasting 24h. Rinsing with solvent to remove water from the immobilised enzymes further improved their activity. This study demonstrates the suitability of immobilised crude enzyme preparations in the development of biocatalysts for esterification reactions.</t>
-  </si>
-  <si>
-    <t>['Biocatalysis', 'Butyl ferulate', 'Enzyme immobilisation', 'Esterification', 'SBA-15']</t>
-  </si>
-  <si>
-    <t>Sweden. Electronic address: huttner@chalmers.se</t>
-  </si>
-  <si>
-    <t>2017 Sep</t>
-  </si>
-  <si>
-    <t>Efficacy and safety of itraconazole use in infants.</t>
-  </si>
-  <si>
-    <t>BACKGROUND: Itraconazole has been used to treat fungal infections, in particular invasive fungal infections in infants or neonates in many countries. DATA SOURCES: Literature search was conducted through Ovid EMBASE, PubMed, ISI Web of Science, CNKI and Google scholarship using the following key words: "pediatric" or "infant" or "neonate" and "fungal infection" in combination with "itraconazole". Based on the literature and our clinical experience, we outline the administration of itraconazole in infants in order to develop evidence-based pharmacotherapy. RESULTS: Of 45 articles on the use of itraconazole in infancy, 13 are related to superficial fungal infections including tinea capitis, sporotrichosis, mucosal fungal infections and opportunistic infections. The other 32 articles are related to systemic fungal infections including candidiasis, aspergillosis, histoplasmosis, zygomycosis, trichosporonosis and opportunistic infections as caused by Myceliophthora thermophila. CONCLUSION: Itraconazole is safe and effective at a dose of 5 mg/kg per day in a short duration of therapy for superficial fungal infections and 10 mg/kg per day for systemic fungal infections in infants. With a good compliance, it is cost-effective in treating infantile fungal infections. The profiles of adverse events induced by itraconazole in infants are similar to those in adults and children.</t>
-  </si>
-  <si>
-    <t>['infant', 'itraconazole', 'prophylaxis', 'superficial fungal infections', 'systemic fungal infections']</t>
-  </si>
-  <si>
-    <t>World journal of pediatrics : WJP</t>
-  </si>
-  <si>
-    <t>2016 Nov</t>
-  </si>
-  <si>
-    <t>Engineered Fungus Thermothelomyces thermophilus Producing Plant Storage Proteins.</t>
-  </si>
-  <si>
-    <t>An efficient Agrobacterium-mediated genetic transformation based on the plant binary vector pPZP-RCS2 was carried out for the multiple heterologous protein production in filamentous fungus Thermothelomyces&amp;nbsp;thermophilus F-859 (formerly Myceliophthora&amp;nbsp;thermophila F-859). The engineered fungus Th.&amp;nbsp;thermophilus was able to produce plant storage proteins of Zea&amp;nbsp;mays (alpha-zein Z19) and Amaranthus&amp;nbsp;hypochondriacus (albumin A1) to enrich fungal biomass by valuable nutritional proteins and improved amino acid content. The mRNA levels of z19 and a1 genes were significantly dependent on their driving promoters: the promoter of tryptophan synthase (PtrpC) was more efficient to express a1, while the promoter of translation elongation factor (Ptef) provided much higher levels of z19 transcript abundance. In general, the total recombinant proteins and amino acid contents were higher in the Ptef-containing clones. This work describes a new strategy to improve mycoprotein nutritive value by overexpression of plant storage proteins.</t>
-  </si>
-  <si>
-    <t>['Myceliophthora thermophila', 'amaranth albumin A1', 'filamentous fungi', 'maize alpha-zein', 'mycoprotein', 'recombinant protein']</t>
-  </si>
-  <si>
-    <t>Journal of fungi (Basel, Switzerland)</t>
-  </si>
-  <si>
-    <t>2022 Jan 26</t>
-  </si>
-  <si>
-    <t>Increasing the lignin yield of the Alkaline Polyol Pulping process by treating black liquor with laccases of Myceliophthora thermophila.</t>
-  </si>
-  <si>
-    <t>The Alkaline Polyol Pulping process separates cellulose from lignocellulosic biomass by dissolving lignin to a great extent. Due to the pulping conditions the dissolved lignin depolymerises and only 75% can be precipitated. To increase this amount, a 24 h reaction of laccases of Myceliophthora thermophila with lignin dissolved in black liquor of the AlkaPolP process was investigated. The influence of pH, temperature, enzyme concentration and partial oxygen pressure was examined in a batch stirred tank reactor using a Box-Behnken factorial design. Due to the enzymatic reaction the lignin polymerises which results in an enhanced lignin precipitation. The addition of a mediator improves the polymerisation but decreases the amount of precipitable lignin. The influence of the parameters on precipitation yield and molecular mass can sufficiently be described with a second-order model and optimum conditions can be assessed. FT-IR spectra of the obtained lignins revealed that its typical phenolic structure is preserved.</t>
-  </si>
-  <si>
-    <t>['Biorefinery', 'Laccase', 'Lignin', 'Lignocellulose', 'Polymerisation']</t>
-  </si>
-  <si>
-    <t>Germany. Electronic address: norman.engel@b-tu.de</t>
-  </si>
-  <si>
-    <t>Ultrasound-assisted swelling of bacterial cellulose.</t>
-  </si>
-  <si>
-    <t>Bacterial cellulose (BC) was obtained by static cultivation using commercial BC gel from scoby. BC membranes (oven dried and freeze-dried) were swelled with 8% NaOH, in the absence and in the presence of ultrasound (US), for 30, 60, and 90 min. The influence of swelling conditions on both physico-chemical properties and molecules entrapment was evaluated. Considering the highest levels of entrapment, an optimum swelling procedure was established: 8% NaOH for 30 min at room temperature in the presence of US. Native and PEGylated laccase from Myceliophthora thermophila was immobilized on BC membranes and a different catalytic behaviour was observed after immobilization. Native laccase presented activity values similar to published reports (5-7 U/gBC) after immobilization whereas PEGylated enzymes showed much lower activity (1-2 U/gBC). BC swelled membranes are presented herein as a potential support for the preparation of immobilized enzymes for industrial applications, like phenolics polymerization.</t>
-  </si>
-  <si>
-    <t>['Bacterial cellulose', 'PEG-FITC', 'Polymerization', 'Swelling', 'Ultrasound']</t>
-  </si>
-  <si>
-    <t>Engineering in life sciences</t>
-  </si>
-  <si>
-    <t>Department of Clothing and Textiles Sookmyung Women's University Seoul South Korea</t>
-  </si>
-  <si>
-    <t>2017 Oct</t>
-  </si>
-  <si>
-    <t>Substrate selectivity in starch polysaccharide monooxygenases.</t>
-  </si>
-  <si>
-    <t>Degradation of polysaccharides is central to numerous biological and industrial processes. Starch-active polysaccharide monooxygenases (AA13 PMOs) oxidatively degrade starch and can potentially be used with industrial amylases to convert starch into a fermentable carbohydrate. The oxidative activities of the starch-active PMOs from the fungi Neurospora crassa and Myceliophthora thermophila, NcAA13 and MtAA13, respectively, on three different starch substrates are reported here. Using high-performance anion-exchange chromatography coupled with pulsed amperometry detection, we observed that both enzymes have significantly higher oxidative activity on amylose than on amylopectin and cornstarch. Analysis of the product distribution revealed that NcAA13 and MtAA13 more frequently oxidize glycosidic linkages separated by multiples of a helical turn consisting of six glucose units on the same amylose helix. Docking studies identified important residues that are involved in amylose binding and suggest that the shallow groove that spans the active-site surface of AA13 PMOs favors the binding of helical amylose substrates over nonhelical substrates. Truncations of NcAA13 that removed its native carbohydrate-binding module resulted in diminished binding to amylose, but truncated NcAA13 still favored amylose oxidation over other starch substrates. These findings establish that AA13 PMOs preferentially bind and oxidize the helical starch substrate amylose. Moreover, the product distributions of these two enzymes suggest a unique interaction with starch substrates.</t>
-  </si>
-  <si>
-    <t>['amylose', 'auxiliary activity (AA) enzyme', 'carbohydrate-binding protein', 'copper', 'copper monooxygenase', 'metalloprotein', 'oxygenase', 'polysaccharide', 'polysaccharide monooxygenase', 'starch']</t>
-  </si>
-  <si>
-    <t>Vietnam. Electronic address: vanvu@ntt.edu.vn</t>
-  </si>
-  <si>
-    <t>2019 Aug 9</t>
-  </si>
-  <si>
-    <t>Development of a genome-editing CRISPR/Cas9 system in thermophilic fungal Myceliophthora species and its application to hyper-cellulase production strain engineering.</t>
-  </si>
-  <si>
-    <t>BACKGROUND: Over the past 3 years, the CRISPR/Cas9 system has revolutionized the field of genome engineering. However, its application has not yet been validated in thermophilic fungi. Myceliophthora thermophila, an important thermophilic biomass-degrading fungus, has attracted industrial interest for the production of efficient thermostable enzymes. Genetic manipulation of Myceliophthora is crucial for metabolic engineering and to unravel the mechanism of lignocellulose deconstruction. The lack of a powerful, versatile genome-editing tool has impeded the broader exploitation of M. thermophila in biotechnology. RESULTS: In this study, a CRISPR/Cas9 system for efficient multiplexed genome engineering was successfully developed in the thermophilic species M. thermophila and M. heterothallica. This CRISPR/Cas9 system could efficiently mutate the imported amdS gene in the genome via NHEJ-mediated events. As a proof of principle, the genes of the cellulase production pathway, including cre-1, res-1, gh1-1, and alp-1, were chosen as editing targets. Simultaneous multigene disruptions of up to four of these different loci were accomplished with neomycin selection marker integration via a single transformation using the CRISPR/Cas9 system. Using this genome-engineering tool, multiple strains exhibiting pronounced hyper-cellulase production were generated, in which the extracellular secreted protein and lignocellulase activities were significantly increased (up to 5- and 13-fold, respectively) compared with the parental strain. CONCLUSIONS: A genome-wide engineering system for thermophilic fungi was established based on CRISPR/Cas9. Successful expansion of this system without modification to M. heterothallica indicates it has wide adaptability and flexibility for use in other Myceliophthora species. This system could greatly accelerate strain engineering of thermophilic fungi for production of industrial enzymes, such as cellulases as shown in this study and possibly bio-based fuels and chemicals in the future.</t>
-  </si>
-  <si>
-    <t>['CRISPR/Cas9 system', 'Cellulases', 'Myceliophthora', 'Thermophilic fungi']</t>
-  </si>
-  <si>
-    <t>300308 China</t>
-  </si>
-  <si>
-    <t>Designing and Constructing a Novel Artificial Pathway for Malonic Acid Production Biologically.</t>
-  </si>
-  <si>
-    <t>Malonic acid is used as a common component of many products and processes in the pharmaceutical and cosmetic industries. Here, we designed a novel artificial synthetic pathway of malonic acid, in which oxaloacetate, an intermediate of cytoplasmic reductive tricarboxylic acid (rTCA) pathway, is converted to malonic semialdehyde and then to malonic acid, sequentially catalyzed by a-keto decarboxylase and malonic semialdehyde dehydrogenase. After the systematic screening, we discovered the enzyme oxaloacetate decarboxylase Mdc, catalyzing the first step of the artificially designed pathway in vitro. Then, this synthetic pathway was functionally constructed in cellulolytic thermophilic fungus Myceliophthora thermophila. After enhancement of glucose uptake, the titer of malonic acid achieved 42.5 mg/L. This study presents a novel biological pathway for producing malonic acid from renewable resources in the future.</t>
-  </si>
-  <si>
-    <t>['Myceliophthora thermophila', 'a-keto decarboxylase', 'malonic acid', 'metabolic engineering', 'oxaloacetic acid']</t>
-  </si>
-  <si>
-    <t>Additives enhancing enzymatic hydrolysis of lignocellulosic biomass.</t>
-  </si>
-  <si>
-    <t>Linked to the development of cellulolytic enzyme cocktails from Myceliophthora thermophila, we studied the effect of different additives on the enzymatic hydrolysis yield. The hydrolysis of pretreated corn stover (PCS), sugar cane straw (PSCS) and microcrystalline cellulose (Avicel) was performed under industrial conditions using high solid loadings, limited mixing, and low enzyme dosages. The addition of polyethylene glycol (PEG4000) allowed to increase the glucose yields by 10%, 7.5%, and 32%, respectively in the three materials. PEG4000 did not have significant effect on the stability of the main individual enzymes but increased beta-glucosidase and endoglucanase activity by 20% and 60% respectively. Moreover, the presence of PEG4000 accelerated cellulase-catalyzed hydrolysis reducing up to 25% the liquefaction time. However, a preliminary economical assessment concludes that even with these improvements, a lower contribution of PEG4000 to the 2G bioethanol production costs would be needed to reach commercial feasibility.</t>
-  </si>
-  <si>
-    <t>['Additives', 'Enzymatic hydrolysis', 'Lignocellulose', 'Myceliophthora thermophila']</t>
-  </si>
-  <si>
-    <t>2017 Nov</t>
-  </si>
-  <si>
-    <t>Enzymatic Oxidation of Ferulic Acid as a Way of Preparing New Derivatives.</t>
-  </si>
-  <si>
-    <t>The ferulic acid (FA)-oxidation by Myceliophthora thermophila laccase was performed in phosphate buffer at 30  degrees C and pH 7.5 as an eco-friendly procedure. LC-MS analysis showed that oxidation products were four dehydrodimers (P1, P2, P3, P5) at MM = 386 g/mol, two dehydrotetramers (P6, P7) at MM = 770 g/mol and one decarboxylated dehydrodimer (P4) at MM = 340 g/mol. Structural characterization showed that FA-dehydrodimers were symmetric for P1 and P5 while asymmetric for P2, P3 and P4. Physicochemical characterization showed that oxidation products presented a higher lipophilicity than that of FA. Moreover, symmetric dimers and tetra dimers had a higher melting point compared to FA and its asymmetric dimers. Antioxidant and anti-proliferative assessments indicated that enzymatic oligomerization increased antioxidant and anti-proliferative properties of oxidation products for P2, P3 and P6 compared to FA. Finally, this enzymatic process in water could produce new molecules, having good antiradical and anti-proliferative activities.</t>
-  </si>
-  <si>
-    <t>['LC-MS', 'RMN', 'anti-proliferative', 'antioxidant', 'enzymatic oxidation']</t>
-  </si>
-  <si>
-    <t>Biotech (Basel (Switzerland))</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>2022 Dec 5</t>
-  </si>
-  <si>
-    <t>Polymers from Bamboo Extracts Produced by Laccase.</t>
-  </si>
-  <si>
-    <t>A green methodology for the production of polymers from bamboo powder was investigated. The optimal conditions for the extraction of components from bamboo were defined by incubating the powder in an acetate buffer (pH 5) under boiling for 2 h. Native laccase from Myceliophthora thermophila was used afterwards to oxidize the extracts from the final resulting extraction liquid. The reduction of the free OH content after enzymatic oxidation, as well as the (1)H NMR data, confirmed the efficient polymerization of the extracts. The bamboo powder samples were also subjected to high compression and curing, in the absence and in the presence of laccase, to evaluate the hardness of the tablets formed by enzymatic bonding events. The results revealed a higher hardness when the tablets were produced in the presence of laccase, confirming the role of the catalyst on the precipitation of colloidal lignin and phenolic extractives. Herein we produce new oligomers/polymers by laccase oxidation of the extracts resulting from a clean method boiling. At the same time, the data open up new routes for the exploitation of new lignocellulosic materials by the direct application of the enzyme on the bamboo powder material.</t>
-  </si>
-  <si>
-    <t>['bamboo powder', 'bamboo tablets', 'laccase', 'oxidation', 'phenolic compound extraction']</t>
-  </si>
-  <si>
-    <t>China. jingsu@ceb.uminho.pt</t>
-  </si>
-  <si>
-    <t>2018 Oct 12</t>
-  </si>
-  <si>
-    <t>Unique features of the bifunctional GH30 from Thermothelomyces thermophila revealed by structural and mutational studies.</t>
-  </si>
-  <si>
-    <t>Fungal xylanases belonging to family GH30_7, initially categorized as endo-glucuronoxylanases, are now known to differ both in terms of substrate specificity, as well as mode of action. Recently, TtXyn30A, a GH30_7 xylanase from Thermothelomyces thermophila, was shown to possess dual activity, acting on the xylan backbone in both an endo- and an exo- manner. Here, in an effort to identify the structural characteristics that append these functional properties to the enzyme, we present the biochemical characterization of various TtXyn30A mutants as well as its crystal structure, alone, and in complex with the reaction product. An auxiliary catalytic amino acid has been identified, while it is also shown that glucuronic acid recognition is not mediated by a conserved arginine residue, as shown by previously determined GH30 structures.</t>
-  </si>
-  <si>
-    <t>['Acidic xylooligosaccharides', 'GH30 xylanase', 'Glucuronic acid recognition', 'Protein engineering', 'X-ray structure', 'Xylobiohydrolase']</t>
-  </si>
-  <si>
-    <t>2021 Dec 1</t>
-  </si>
-  <si>
-    <t>Enzyme Catalyzed Copolymerization of Lignosulfonates for Hydrophobic Coatings.</t>
-  </si>
-  <si>
-    <t>Enzymatic polymerization of lignin can generate a variety of value-added products concomitantly replacing fossil-based resources. In line with this approach, a laccase from the thermophilic fungus Myceliophthora thermophila (MtL) was used to couple a hydrophobicity enhancing fluorophenol (FP) molecule, namely 4-[4-(trifluoromethyl)phenoxy]phenol (4,4-F3MPP), as a model substrate onto lignosulfonate (LS). During the coupling reaction changes in fluorescence, phenol content, viscosity and molecular weight (size exclusion chromatography; SEC) were monitored. The effects of enzymatic coupling of FP onto LS on hydrophobicity were investigated by the means of water contact angle (WCA) measurement and determination of swelling capacity. Full polymerization of LS resulting in the production of water-insoluble polymers was achieved at a pH of 7 and 33 degrees C. Incorporation of 2% (w/v) of FP led to an increase in WCA by 59.2% while the swelling capacity showed a decrease by 216.8%. Further, Fourier transform infrared spectroscopy (FTIR) and X-ray photoelectron spectroscopy (XPS) analysis indicated successful covalent coupling of the FP molecule onto LS by an emerging peak at 1,320 cm(-1) in the FTIR spectrum and the evidence of Fluor in the XPS spectrum. This study shows the ability of laccase to mediate the tailoring of LS properties to produce functional polymers.</t>
-  </si>
-  <si>
-    <t>['coating', 'coupling', 'fluorophenol', 'hydrophobicity', 'laccase', 'lignosulfonate', 'modification']</t>
-  </si>
-  <si>
-    <t>Austria</t>
-  </si>
-  <si>
-    <t>Dissecting key residues of a C4-dicarboxylic acid transporter to accelerate malate export in Myceliophthora.</t>
-  </si>
-  <si>
-    <t>Efficient transporters are necessary for high concentration and purity of desired products during industrial production. In this study, we explored the mechanism of substrate transport and preference of the C4-dicarboxylic acid transporter AoMAE in the fungus Myceliophthora thermophila, and investigated the roles of 18 critical amino acid residues within this process. Among them, the residue Arg78, forming a hydrogen bond network with Arg23, Phe25, Thr74, Leu81, His82, and Glu94 to stabilize the protein conformation, is irreplaceable for the export function of AoMAE. Furthermore, varying the residue at position 100 resulted in changes to the size and shape of the substrate binding pocket, leading to alterations in transport efficiencies of both malic acid and succinic acid. We found that the mutation T100S increased malate production by 68%. Using these insights, we successfully generated an AoMAE variant with mutation T100S and deubiquitination, exhibiting an 81% increase in the selective export activity of malic acid. Simply introducing this version of AoMAE into M. thermophila wild-type strain increased production of malic acid from 1.22 to 54.88 g/L. These findings increase our understanding of the structure-function relationships of organic acid transporters and may accelerate the process of engineering dicarboxylic acid transporters with high efficiency. KEY POINTS: * This is the first systematical analysis of key residues of a malate transporter in fungi. * Protein engineering of AoMAE led to 81% increase of malate export activity. * Arg78 was essential for the normal function of AoMAE in M. thermophila. * Substitution of Thr100 affected export efficiency and substrate selectivity of AoMAE.</t>
-  </si>
-  <si>
-    <t>['C4-dicarboxylic acid;', 'Malate export', 'Myceliophthora;', 'Protein rewiring;']</t>
-  </si>
-  <si>
-    <t>2023 Feb</t>
-  </si>
-  <si>
-    <t>Green synthesis of glyco-phenol by enzymatic coupling between ferulic acid and glucosamine: An ecofriendly procedure.</t>
-  </si>
-  <si>
-    <t>A new glyco-phenol was produced by the coupling between glucosamine (Glu) and ferulic acid (FA) using Myceliophthora thermophila laccase as biocatalyst in mild conditions (distilled water and 30 degrees C) as an environmentally friendly process. Results indicated that the enzymatic reaction created a new derivative (FA-Glu), produced from coupling between Glu and FA by covalent bonds. By the high production of (FA-Glu) derivative and its stability, the optimal ratio of (FA:Glu) was of (1:1) at optimal time reaction of 6 h. Under these optimal conditions, almost 55% of -NH(2) groups on Glu were bound with FA oxidation products. The new derivative showed higher hydrophobic character than Glu due to the presence of FA in its structure. Liquid chromatography-mass spectrometry analysis showed that (FA-Glu) derivative exhibited a molecular mass at MM 713 g/mol containing one Glu molecule and three FA molecules after decarboxylation. Furthermore, the new derivative presented good antioxidant and antiproliferative activities in comparison with Glu and FA. These results suggest that the enzymatic conjugation between Glu and FA is a promising process to produce a new glyco-phenol having good functional properties for potential applications.</t>
-  </si>
-  <si>
-    <t>['ferulic acid', 'functional properties', 'glucosamine', 'glyco-phenol', 'laccase']</t>
-  </si>
-  <si>
-    <t>Biotechnology and applied biochemistry</t>
-  </si>
-  <si>
-    <t>2022 Aug</t>
-  </si>
-  <si>
-    <t>Laccase catalyzed elimination of morphine from aqueous systems.</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals contaminate the environment for several reasons, including metabolic excretion after intake, industrial waste and improper disposal. The narcotic drug morphine is commonly utilized for chronic pain management, and the distribution of morphine in aqueous systems and in waste waters is of high concern. Here, the removal of morphine by a laccase from Myceliophthora thermophila both in its free form as well as immobilized on Accurel MP1000 beads was investigated. Complete morphine elimination was achieved within 30 min for the free and the immobilized enzyme (70% bound protein) for concentrations between 1 and 1,000 mg L(-1) according to LC-TOF mass spectrometry analysis. Higher morphine concentrations up to 60 g L(-1) were also tested and total elimination was achieved within 6 h. Therefore, laccases are ideal candidates for removing morphine from aqueous systems.</t>
-  </si>
-  <si>
-    <t>['Aqueous systems', 'Elimination', 'Enzyme immobilization', 'Laccase', 'Morphine']</t>
-  </si>
-  <si>
-    <t>New biotechnology</t>
-  </si>
-  <si>
-    <t>2018 May 25</t>
-  </si>
-  <si>
-    <t>Development of a flow cytometry-based plating-free system for strain engineering in industrial fungi.</t>
-  </si>
-  <si>
-    <t>Recent technical advances regarding filamentous fungi have accelerated the engineering of fungal-based production and benefited basic science. However, challenges still remain and limit the speed of fungal applications. For example, high-throughput technologies tailored to filamentous fungi are not yet commonly available for genetic modification. The currently used fungal genetic manipulations are time-consuming and laborious. Here, we developed a flow cytometry-based plating-free system to directly screen and isolate the transformed protoplasts in industrial fungi Myceliophthora thermophila and Aspergillus niger. This system combines genetic engineering via the 2A peptide and the CRISPR-Cas9 system, strain screening by flow cytometry, and direct sorting of colonies for deep-well-plate incubation and phenotypic analysis while avoiding culturing transformed protoplasts in plates, colony picking, conidiation, and cultivation. As a proof of concept, we successfully applied this system to generate the glucoamylase-hyperproducing strains MtYM6 and AnLM3 in M. thermophila and A. niger, respectively. Notably, the protein secretion level and enzyme activities in MtYM6 were 17.3- and 25.1-fold higher than in the host strain. Overall, these findings suggest that the flow cytometry-based plating-free system can be a convenient and efficient tool for strain engineering in fungal biotechnology. We expect this system to facilitate improvements of filamentous fungal strains for industrial applications. KEY POINTS: * Development of a flow cytometry-based plating-free (FCPF) system is presented. * Application of FCPF system in M. thermophila and A. niger for glucoamylase platform. * Hyper-produced strains MtYM6 and AnLM3 for glucoamylase production are generated.</t>
-  </si>
-  <si>
-    <t>['Aspergillus niger', 'CRISPR-Cas9', 'Flow cytometry', 'Glucoamylase', 'Myceliophthora thermophila', 'Plating-free']</t>
-  </si>
-  <si>
-    <t>2022 Jan</t>
-  </si>
-  <si>
-    <t>Recombinant thermo-alkali-stable endoglucanase of Myceliopthora thermophila BJA (rMt-egl): Biochemical characteristics and applicability in enzymatic saccharification of agro-residues.</t>
-  </si>
-  <si>
-    <t>Codon adaptation index (CAI) of a 1263bp long endoglucanase encoding gene from the thermophilic mould Myceliopthora thermophile BJA has been improved from 0.44 to 0.76 by in vitro gene synthesis. The codon optimized endoglucanase gene (Mt-egl) has been constitutively expressed in Pichia pastoris under the regulation of GAP promoter. Recombinant endoglucanase (rMt-egl), purified by size exclusion chromatography, has been confirmed to be a monomeric protein of  approximately 47kDa. rMt-egl is optimally active at pH 10 and 50 degrees C, displaying stability in broad pH and temperature ranges, with a t(1/2) of 60 and 15min at 90 and 100 degrees C, respectively. This retained  approximately 70% of activity after 3h incubation at pH 5-12. The K(m), V(max), k(cat) and k(cat)/K(m) of rMt-egl were 5mgmL(-1), 20mumolesmin(-1)mg(-1), 1.02x10(3)s(-1) and 204s(-1)mg(-1)mL(-1), respectively. Homology modeling and bioinformatics analysis confirmed catalytically important role of glutamate 234 and 344. rMt-egl released high amounts of reducing sugars from wheat bran and corn cobs (421 and 382mgg(-1)), thus making it a useful biocatalyst for producing bioethanol and fine chemicals from agro-residues.</t>
-  </si>
-  <si>
-    <t>['Codon optimization', 'Constitutive expression', 'Enzymatic saccharification', 'Myceliophthora thermophila', 'Thermo-alkali-stable endoglucanase', 'Thermophilic mould']</t>
-  </si>
-  <si>
-    <t>A fatal case of pneumonia caused by Thermothelomycesthermophila.</t>
-  </si>
-  <si>
-    <t>Thermothelomyces thermophila (formerly Myceliophthora thermophila) is usually found in soil and specifically compost as an environmental dematiaceous fungus. Here, we report the first case of invasive pulmonary infection caused by T. thermophila in a pediatric patient with acute lymphoblastic leukemia. T. thermophila was serially cultured from bronchoalveolar lavage (BAL) fluid and sputum samples obtained from this patient with respiratory symptoms. The patient received antifungal treatment with liposomal amphotericin B (160 mg daily) and itraconazole (200 mg daily) combination therapy, but she died. By the antifungal susceptibility testing, low minimum inhibitory concentrations (MIC) were observed for itraconazole (MIC 0.06 mug/mL), voriconazole (MIC 0.12 mug/mL), and posaconazole (MIC 0.03 mug/mL) but high MIC was observed with amphotericin B (MIC 4.0 mug/mL). Since T. thermophila is usually found in the environment, it can be considered as a contaminant and may cause difficulties in diagnosis. Therefore, it is necessary to confirm the potential of pathogen through repeated culture and to conduct an antifungal susceptibility testing to find a suitable antifungal agent.</t>
-  </si>
-  <si>
-    <t>['Acute lymphoblastic leukemia', 'Antifungal susceptibility testing', 'Invasive pulmonary infection', 'Thermothelomyces thermophila']</t>
-  </si>
-  <si>
-    <t>Journal of infection and chemotherapy : official journal of the Japan Society of Chemotherapy</t>
-  </si>
-  <si>
-    <t>South Korea</t>
-  </si>
-  <si>
-    <t>2023 Jan</t>
-  </si>
-  <si>
-    <t>Thermophilic Filamentous Fungus C1-Cell-Cloned SARS-CoV-2-Spike-RBD-Subunit-Vaccine Adjuvanted with Aldydrogel((R))85 Protects K18-hACE2 Mice against Lethal Virus Challenge.</t>
-  </si>
-  <si>
-    <t>SARS-CoV-2 is evolving with increased transmission, host range, pathogenicity, and virulence. The original and mutant viruses escape host innate (Interferon) immunity and adaptive (Antibody) immunity, emphasizing unmet needs for high-yield, commercial-scale manufacturing to produce inexpensive vaccines/boosters for global/equitable distribution. We developed DYAI-100A85, a SARS-CoV-2 spike receptor binding domain (RBD) subunit antigen vaccine expressed in genetically modified thermophilic filamentous fungus, Thermothelomyces heterothallica C1, and secreted at high levels into fermentation medium. The RBD-C-tag antigen strongly binds ACE2 receptors in vitro. Alhydrogel((R))'85'-adjuvanted RDB-C-tag-based vaccine candidate (DYAI-100A85) demonstrates strong immunogenicity, and antiviral efficacy, including in vivo protection against lethal intranasal SARS-CoV-2 (D614G) challenge in human ACE2-transgenic mice. No loss of body weight or adverse events occurred. DYAI-100A85 also demonstrates excellent safety profile in repeat-dose GLP toxicity study. In summary, subcutaneous prime/boost DYAI-100A85 inoculation induces high titers of RBD-specific neutralizing antibodies and protection of hACE2-transgenic mice against lethal challenge with SARS-CoV-2. Given its demonstrated safety, efficacy, and low production cost, vaccine candidate DYAI-100 received regulatory approval to initiate a Phase 1 clinical trial to demonstrate its safety and efficacy in humans.</t>
-  </si>
-  <si>
-    <t>['BALB/c mice', 'C-tag', 'CHO-cell', 'COVID-19', 'IgG', 'IgG1 and IgG2b', 'K18-hACE-2 mice', 'Myceliophthora thermophila', 'RBD', 'SARS-CoV-2', 'Thermothelomyces heterothallica', 'adjuvant', 'alum', 'aluminum-based vaccine adjuvants', 'antigen', 'baculovirus', 'biomanufacturing', 'dyadic', 'efficacy', 'glycans', 'glycoprotein', 'glycosylation', 'insect cells', 'intranasal challenge', 'neutralizing antibodies', 'pandemic', 'receptor binding domain', 'recombinant protein subunit vaccine', 'stability', 'toxicology', 'vaccine', 'variants of concern', 'virus', 'zoonotic']</t>
-  </si>
-  <si>
-    <t>Vaccines</t>
-  </si>
-  <si>
-    <t>Israel</t>
-  </si>
-  <si>
-    <t>2022 Dec 11</t>
-  </si>
-  <si>
-    <t>Evaluation of Antibacterial and Antifungal Properties of Low Molecular Weight Chitosan Extracted from Hermetia illucens Relative to Crab Chitosan.</t>
-  </si>
-  <si>
-    <t>This study shows the research on the depolymerisation of insect and crab chitosans using novel enzymes. Enzyme preparations containing recombinant chitinase Chi 418 from Trichoderma harzianum, chitinase Chi 403, and chitosanase Chi 402 from Myceliophthora thermophila, all belonging to the family GH18 of glycosyl hydrolases, were used to depolymerise a biopolymer, resulting in a range of chitosans with average molecular weights (M(w)) of 6-21 kDa. The depolymerised chitosans obtained from crustaceans and insects were studied, and their antibacterial and antifungal properties were evaluated. The results proved the significance of the chitosan's origin, showing the potential of Hermetia illucens as a new source of low molecular weight chitosan with an improved biological activity.</t>
-  </si>
-  <si>
-    <t>['Hermetia illucens', 'antibacterial activity', 'antifungal activity', 'chitosan', 'depolymerisation', 'insect']</t>
-  </si>
-  <si>
-    <t>2022 Jan 17</t>
-  </si>
-  <si>
-    <t>Bio-coloration of bacterial cellulose assisted by immobilized laccase.</t>
-  </si>
-  <si>
-    <t>In this work a process for the bio-coloration of bacterial cellulose (BC) membranes was developed. Laccase from Myceliophthora thermophila was immobilized onto BC membranes and retained up to 88% of residual activity after immobilization. Four compounds belonging to the flavonoids family were chosen to test the in situ polymerase activity of immobilized laccase. All the flavonoids were successfully polymerized by laccase giving rise to yellow, orange and dark brown oligomers which conferred color to the BC support. The optimal bio-coloration conditions were studied for two of the tested flavonoids, catechol and catechin, by varying the concentration and time of incubation. High color depth and resistance to washing were obtained for both compounds. The highly porous bacterial cellulose material demonstrated great performance as a bio-coloration support, in contrast to other materials cited in literature, like cotton or wool. The process developed is presented as an environmentally friendly alternative for bacterial cellulose bio-coloration and will contribute deeply for the development of new fashionable products within this material.</t>
-  </si>
-  <si>
-    <t>['Bacterial cellulose', 'Bio-coloration', 'Laccase', 'Polymerization']</t>
-  </si>
-  <si>
-    <t>2018 Feb 13</t>
-  </si>
-  <si>
-    <t>Enzymatic Oxidation of Ca-Lignosulfonate and Kraft Lignin in Different Lignin-Laccase-Mediator-Systems and MDF Production.</t>
-  </si>
-  <si>
-    <t>Laccase-mediator-oxidized lignin offers replacement for conventional chemical binders to produce fiberboards. Compared to the previously reported laccase-mediator system (LMS), a lignin-laccase-mediator-system (LLMS) has an advantage in that it requires much shorter fiber-enzyme incubation time due to significantly increased redox reactions. However, the cost of regularly applying laccase on an industrial scale is currently too high. We have employed CcLcc5 from cultures of the basidiomycete Coprinopsis cinerea as a novel basi-laccase (a CAZy subfamily AA1_1 laccase) in medium-density fiberboard (MDF) production, in comparison to the commercial formulation Novozym 51003 with recombinantly produced asco-laccase MtL (a CAZy subfamily AA1_3 laccase-like multicopper oxidase from the ascomycete Myceliophthora thermophila). With the best-performing natural mediator 2,6-dimethoxyphenol (DMP), unpurified CcLcc5 was almost as good as formulated Novozym 51003 in increasing the molecular weight (MW) of the technical lignins tested, the hydrophilic high-MW Ca-lignosulfonate and the hydrophobic low-MW kraft lignin (Indulin AT). Oxygen consumption rates of the two distantly related, poorly conserved enzymes (31% sequence identity) with different mediators and lignosulfonate were also comparable, but Indulin AT significantly reduced the oxidative activity of Novozym 51003 unlike CcLcc5, regardless of the mediator used, either DMP or guaiacol. Oxygen uptake by both laccases was much faster with both technical lignins with DMP than with guaiacol. In case of lignosulfonate and DMP, 20-30 min of incubation was sufficient for full oxygen consumption, which fits in well in time with the usual binder application steps in industrial MDF production processes. LLMS-bonded MDF was thus produced on a pilot-plant scale with either crude CcLcc5 or Novozym 51003 at reduced enzyme levels of 5 kU/kg absolutely dry wood fiber with lignosulfonate and mediator DMP. Boards produced with CcLcc5 were comparably good as those made with Novozym 51003. Boards reached nearly standard specifications in internal bond strength (IB) and modulus of rupture (MOR), while thickness swelling (TS) was less good based on the hydrophilic character of lignosulfonate. LLMS-bonded MDF with Indulin AT and DMP performed better in TS but showed reduced IB and MOR values.</t>
-  </si>
-  <si>
-    <t>['2,6-dimethoxyphenol', 'Ca-lignosulfonate', 'MDF', 'asco-laccase MtL', 'basi-laccase CcLcc5', 'guaiacol', 'kraft lignin', 'mediator']</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Laccase-Mediator System Using a Natural Mediator as a Whitening Agent for the Decolorization of Melanin.</t>
-  </si>
-  <si>
-    <t>In this study, a laccase-mediator system (LMS) using a natural mediator was developed as a whitening agent for melanin decolorization. Seven natural mediators were used to replace synthetic mediators and successfully overcome the low redox potential of laccase and limited access of melanin to the active site of laccase. The melanin decolorization activity of laccases from Trametes versicolor (lacT) and Myceliophthora thermophila (lacM) was significantly enhanced using natural mediators including acetosyringone, syringaldehyde, and acetovanillone, which showed low cytotoxicity. The methoxy and ketone groups of natural mediators play an important role in melanin decolorization. The specificity constants of lacT and lacM for melanin decolorization were enhanced by 247 and 334, respectively, when acetosyringone was used as a mediator. LMS using lacM and acetosyringone could also decolorize the melanin present in the cellulose hydrogel film, which mimics the skin condition. Furthermore, LMS could decolorize not only synthetic eumelanin analogs prepared by the oxidation of tyrosine but also natural melanin produced by melanoma cells.</t>
-  </si>
-  <si>
-    <t>['decolorization', 'laccase', 'melanin', 'natural mediators']</t>
-  </si>
-  <si>
-    <t>Korea</t>
-  </si>
-  <si>
-    <t>2021 Oct 25</t>
-  </si>
-  <si>
-    <t>Effect of mutations on the thermostability of Aspergillus aculeatus beta-1,4-galactanase.</t>
-  </si>
-  <si>
-    <t>New variants of beta-1,4-galactanase from the mesophilic organism Aspergillus aculeatus were designed using the structure of beta-1,4-galactanase from the thermophile organism Myceliophthora thermophila as a template. Some of the variants were generated using PROPKA 3.0, a validated pKa prediction tool, to test its usefulness as an enzyme design tool. The PROPKA designed variants were D182N and S185D/Q188T, G104D/A156R. Variants Y295F and G306A were designed by a consensus approach, as a complementary and validated design method. D58N was a stabilizing mutation predicted by both methods. The predictions were experimentally validated by measurements of the melting temperature (Tm ) by differential scanning calorimetry. We found that the Tm is elevated by 1.1  degrees C for G306A, slightly increased (in the range of 0.34 to 0.65  degrees C) for D182N, D58N, Y295F and unchanged or decreased for S185D/Q188T and G104D/A156R. The Tm changes were in the range predicted by PROPKA. Given the experimental errors, only the D58N and G306A show significant increase in thermodynamic stability. Given the practical importance of kinetic stability, the kinetics of the irreversible enzyme inactivation process were also investigated for the wild-type and three variants and found to be biphasic. The half-lives of thermal inactivation were approximately doubled in G306A, unchanged for D182N and, disappointingly, a lot lower for D58N. In conclusion, this study tests a new method for estimating Tm changes for mutants, adds to the available data on the effect of substitutions on protein thermostability and identifies an interesting thermostabilizing mutation, which may be beneficial also in other galactanases.</t>
-  </si>
-  <si>
-    <t>['AZCL-galactan, azurine-crosslinked galactan', 'AaGal, beta-1,4-galactanase from Aspergillus aculeatus', 'CAZY, carbohydrate active enzyme database', 'Computational prediction', 'DSC, differential scanning calorimetry', 'GH53', 'MtGal, beta-1,4-galactanase from Myceliophthora thermophila', 'Protein design', 'Thermostability', 'Tm, melting temperature', 'TsGal, Talaromyces stipitatus galactanase', 'WT, wild type', 'beta-1,4-galactanase']</t>
-  </si>
-  <si>
-    <t>Computational and structural biotechnology journal</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>Management of enzyme diversity in high-performance cellulolytic cocktails.</t>
-  </si>
-  <si>
-    <t>BACKGROUND: Modern biorefineries require enzymatic cocktails of improved efficiency to generate fermentable sugars from lignocellulosic biomass. Cellulolytic fungi, among other microorganisms, have demonstrated the highest potential in terms of enzymatic productivity, complexity and efficiency. On the other hand, under cellulolytic-inducing conditions, they often produce a considerable diversity of carbohydrate-active enzymes which allow them to adapt to changing environmental conditions. However, industrial conditions are fixed and adjusted to the optimum of the whole cocktail, resulting in underperformance of individual enzymes. RESULTS: One of these cellulolytic cocktails from Myceliophthora thermophila has been analyzed here by means of LC-MS/MS. Pure GH6 family members detected have been characterized, confirming previous studies, and added to whole cocktails to compare their contribution in the hydrolysis of industrial substrates. Finally, independent deletions of two GH6 family members, as an example of the enzymatic diversity management, led to the development of a strain producing a more efficient cellulolytic cocktail. CONCLUSIONS: These data indicate that the deletion of noncontributive cellulases (here EG VI) can increase the cellulolytic efficiency of the cocktail, validating the management of cellulase diversity as a strategy to obtain improved fungal cellulolytic cocktails.</t>
-  </si>
-  <si>
-    <t>['Bioethanol', 'Cellulolytic cocktail improvement', 'Enzymatic hydrolysis', 'Lignocellulosic biomass']</t>
-  </si>
-  <si>
-    <t>Modifying Surface Charges of a Thermophilic Laccase Toward Improving Activity and Stability in Ionic Liquid.</t>
-  </si>
-  <si>
-    <t>The multicopper oxidase enzyme laccase holds great potential to be used for biological lignin valorization alongside a biocompatible ionic liquid (IL). However, the IL concentrations required for biomass pretreatment severely inhibit laccase activity. Due to their ability to function in extreme conditions, many thermophilic enzymes have found use in industrial applications. The thermophilic fungal laccase from Myceliophthora thermophila was found to retain high levels of activity in the IL [C(2)C(1)Im][EtSO(4)], making it a desirable biocatalyst to be used for lignin valorization. In contrast to [C(2)C(1)Im][EtSO(4)], the biocompatibility of [C(2)C(1)Im][OAC] with the laccase was markedly lower. Severe inhibition of laccase activity was observed in 15% [C(2)C(1)Im][OAc]. In this study, the enzyme surface charges were modified via acetylation, succinylation, cationization, or neutralization. However, these modifications did not show significant improvement in laccase activity or stability in [C(2)C(1)Im][OAc]. Docking simulations show that the IL docks close to the T1 catalytic copper, likely interfering with substrate binding. Although additional docking locations for [OAc](-) are observed after making enzyme modifications, it does not appear that these locations play a role in the inhibition of enzyme activity. The results of this study could guide future enzyme engineering efforts by showing that the inhibition mechanism of [C(2)C(1)Im][OAc] toward M. thermophila laccase is likely not dependent upon the IL interacting with the enzyme surface.</t>
-  </si>
-  <si>
-    <t>['docking simulation', 'ionic liquid', 'lignin', 'lignin degrading enzymes', 'surface modifacation']</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Improved Production of Xylanase in Pichia pastoris and Its Application in Xylose Production From Xylan.</t>
-  </si>
-  <si>
-    <t>Xylanases with high specific activity has been focused with great interest as a useful enzyme in biomass utilization. The production of recombinant GH11 xylanase (MYCTH_56237) from Myceliophthora thermophila has been improved through N-terminal signal peptide engineering in P. pastoris. The production of newly recombinant xylanase (termed Mtxyn11C) was improved from 442.53 to 490.7 U/mL, through a replacement of alpha-factor signal peptide with the native xylanase signal peptide segment (MVSVKAVLLLGAAGTTLA) in P. pastoris. Scaling up of Mtxyn11C production in a 7.5 L fermentor was improved to the maximal production rate of 2503 U/mL. In this study, the degradation efficiency of Mtxyn11C was further examined. Analysis of the hydrolytic mode of action towards the birchwood xylan (BWX) revealed that Mtxyn11C was clearly more effective than commercial xylanase and degrades xylan into xylooligosaccharides (xylobiose, xylotriose, xylotetraose). More importantly, Mtxyn11C in combination with a single multifunctional xylanolytic enzyme, improved the hydrolysis of BWX into single xylose by 40%. Altogether, this study provided strategies for improved production of xylanase together with rapid conversion of xylose from BWX, which provides sustainable, cost-effective and environmental friendly approaches to produce xylose/XOSs for biomass energy or biofuels production.</t>
-  </si>
-  <si>
-    <t>['Myceliophthora thermophila', 'Pichia pastoris', 'hydrolytic activity', 'improved production', 'xylan', 'xylanase', 'xylose']</t>
-  </si>
-  <si>
-    <t>Quantification of the catalytic performance of C1-cellulose-specific lytic polysaccharide monooxygenases.</t>
-  </si>
-  <si>
-    <t>Lytic polysaccharide monooxygenases (LPMOs) have recently been shown to significantly enhance the degradation of recalcitrant polysaccharides and are of interest for the production of biochemicals and bioethanol from plant biomass. The copper-containing LPMOs utilize electrons, provided by reducing agents, to oxidatively cleave polysaccharides. Here, we report the development of a beta-glucosidase-assisted method to quantify the release of C1-oxidized gluco-oligosaccharides from cellulose by two C1-oxidizing LPMOs from Myceliophthora thermophila C1. Based on this quantification method, we demonstrate that the catalytic performance of both MtLPMOs is strongly dependent on pH and temperature. The obtained results indicate that the catalytic performance of LPMOs depends on the interaction of multiple factors, which are affected by both pH and temperature.</t>
-  </si>
-  <si>
-    <t>['Lignocellulose', 'Lytic polysaccharide monooxygenase', 'Plant biomass', 'Reducing agent', 'beta-Glucosidase']</t>
-  </si>
-  <si>
-    <t>Coupling the pretreatment and hydrolysis of lignocellulosic biomass by the expression of beta-xylosidases.</t>
-  </si>
-  <si>
-    <t>Thermochemical pretreatment and enzymatic hydrolysis are the areas contributing most to the operational costs of second generation ethanol in lignocellulosic biorefineries. The improvement of lignocellulosic enzyme cocktails has been significant in the recent years. Although the needs for the reduction of the energy intensity and chemical consumption in the pretreatment step are well known, the reduction of the severity of the process strongly affects the enzymatic hydrolysis yield. To explore the formulation requirements of the well known cellulolytic cocktail from Myceliophthora thermophila on mild pretreated raw materials, this cocktail was tested on steam exploded corn stover without acid impregnation. The low hemicellulose yield and significant accumulation of xylobiose compared with the standard pretreated material obtained with dilute acid impregnation evidenced a clear limitation in the conversion of xylan to xylose. In order to complement the beta-xylosidase limitation, a selection of enzymes was expressed and tested in this fungus. A controlled expression of xylosidases from Aspergillus nidulans, Aspergillus fumigatus, and Fusarium oxysporum allowed recovering hemicellulose yields reached with standard acid treated material. The results underline the need of parallel development of the pretreatment process with the optimization of the formulation of the enzymatic cocktails.</t>
-  </si>
-  <si>
-    <t>['beta-xylosidase', 'biofuels', 'biorefinery', 'enzymatic hydrolysis', 'lignocellulosic biomass']</t>
-  </si>
-  <si>
-    <t>The Highly Productive Thermothelomyces heterothallica C1 Expression System as a Host for Rapid Development of Influenza Vaccines.</t>
-  </si>
-  <si>
-    <t>(1) Influenza viruses constantly change and evade prior immune responses, forcing seasonal re-vaccinations with updated vaccines. Current FDA-approved vaccine manufacturing technologies are too slow and/or expensive to quickly adapt to mid-season changes in the virus or to the emergence of pandemic strains. Therefore, cost-effective vaccine technologies that can quickly adapt to newly emerged strains are desirable. (2) The filamentous fungal host Thermothelomyces heterothallica C1 (C1, formerly Myceliophthora thermophila) offers a highly efficient and cost-effective alternative to reliably produce immunogens of vaccine quality at large scale. (3) We showed the utility of the C1 system expressing hemagglutinin (HA) and a HA fusion protein from different H1N1 influenza A virus strains. Mice vaccinated with the C1-derived HA proteins elicited anti-HA immune responses similar, or stronger than mice vaccinated with HA products derived from prototypical expression systems. A challenge study demonstrated that vaccinated mice were protected against the aggressive homologous viral challenge. (4) The C1 expression system is proposed as part of a set of protein expression systems for plug-and-play vaccine manufacturing platforms. Upon the emergence of pathogens of concern these platforms could serve as a quick solution for producing enough vaccines for immunizing the world population in a much shorter time and more affordably than is possible with current platforms.</t>
-  </si>
-  <si>
-    <t>['Thermothelomyces heterothallica C1', 'filamentous fungi', 'influenza vaccine', 'recombinant protein expression', 'targeted influenza hemagglutinin', 'trimeric influenza hemagglutinin']</t>
-  </si>
-  <si>
-    <t>2022 Jan 20</t>
-  </si>
-  <si>
-    <t>Functionalization of pectin with laccase-mediated oxidation products of ferulic acid.</t>
-  </si>
-  <si>
-    <t>Pectin is a natural biopolymer extracted mostly from citrus peel, sugar beet and apple pomace. In order to improve its functional properties and then to enlarge the field of its potential applications, functionalization reaction of citrus pectin with ferulic acid (FA)-oxidation products was performed in aqueous medium, at 30 degrees C and pH7.5, in the presence of Myceliophthora thermophila laccase as biocatalyst. The conjugation between FA-oxidation products and pectin was confirmed using FTIR, UV-Vis and LC-MS analyses. The obtained results suggested that covalent bonds were between the pectin carboxyl groups and FA-oxidation products between the pectin carboxyl groups and FA-oxidation products. The determination of the total phenolic content showed that the modified pectin contained 5 times more phenols than the native pectin. In view of these results, this enzymatic procedure appears as a promising way to provide new pectin-based polymers that are expected to present new properties of interest.</t>
-  </si>
-  <si>
-    <t>['Ferulic acid', 'Functionalization', 'Laccase', 'Oxidation', 'Pectin']</t>
-  </si>
-  <si>
-    <t>Conductive Cotton by In Situ Laccase-Polymerization of Aniline.</t>
-  </si>
-  <si>
-    <t>Conductive cotton fabrics were obtained via in situ aniline polymerization by laccase from Myceliophthora thermophila under mild reaction conditions without the addition of strong proton acids. The reactions were conducted using two types of reactors, namely a water bath (WB) and an ultrasonic bath (US), and the role of a mediator, 1-hydroxybenzotriazol (HBT), on the laccase-assisted polymerization of aniline was investigated. A similar polymerization degree was obtained when using both reactors-however, the ultrasonic bath allowed the experiments to be conducted in shorter periods of time (24 h for WB vs. 2 h for US). The data obtained also revealed that the mediator (1-hydroxybenzotriazol-HBT) played a crucial role in aniline oxidation. A higher conversion yield and polymerization degree were obtained when the reaction was conducted in the presence of this compound, as confirmed by MALDI-TOF analysis. The cotton fabrics coated with polyaniline presented deep coloration and conductivity, especially when the mediator was included on the reactional system. The results obtained are a step forward in the enzymatic polymerization of aniline with the purpose of obtaining coloured conductive textile surfaces, with potential applications in wearable electronics.</t>
-  </si>
-  <si>
-    <t>['1-hydroxybenzotriazol (HBT)', 'coatings', 'conductive cotton', 'laccase', 'polyaniline']</t>
-  </si>
-  <si>
-    <t>2018 Sep 14</t>
-  </si>
-  <si>
-    <t>Functional Evolution in Orthologous Cell-encoded RNA-dependent RNA Polymerases.</t>
-  </si>
-  <si>
-    <t>Many eukaryotic organisms encode more than one RNA-dependent RNA polymerase (RdRP) that probably emerged as a result of gene duplication. Such RdRP paralogs often participate in distinct RNA silencing pathways and show characteristic repertoires of enzymatic activities in vitro However, to what extent members of individual paralogous groups can undergo functional changes during speciation remains an open question. We show that orthologs of QDE-1, an RdRP component of the quelling pathway in Neurospora crassa, have rapidly diverged in evolution at the amino acid sequence level. Analyses of purified QDE-1 polymerases from N. crassa (QDE-1(Ncr)) and related fungi, Thielavia terrestris (QDE-1(Tte)) and Myceliophthora thermophila (QDE-1(Mth)), show that all three enzymes can synthesize RNA, but the precise modes of their action differ considerably. Unlike their QDE-1(Ncr) counterpart favoring processive RNA synthesis, QDE-1(Tte) and QDE-1(Mth) produce predominantly short RNA copies via primer-independent initiation. Surprisingly, a 3.19 A resolution crystal structure of QDE-1(Tte) reveals a quasisymmetric dimer similar to QDE-1(Ncr) Further electron microscopy analyses confirm that QDE-1(Tte) occurs as a dimer in solution and retains this status upon interaction with a template. We conclude that divergence of orthologous RdRPs can result in functional innovation while retaining overall protein fold and quaternary structure.</t>
-  </si>
-  <si>
-    <t>['RNA interference (RNAi)', 'RNA polymerase', 'RNA-dependent RNA polymerase', 'electron microscopy (EM)', 'protein evolution', 'x-ray crystallography']</t>
-  </si>
-  <si>
-    <t>Singapore</t>
-  </si>
-  <si>
-    <t>2016 Apr 22</t>
-  </si>
-  <si>
-    <t>Anti-inflammatory and anti-oxidant properties of laccase-synthesized phenolic-O-carboxymethyl chitosan hydrogels.</t>
-  </si>
-  <si>
-    <t>A bioactive O-carboxymethyl chitosan (CMCS) hydrogel crosslinked with natural phenolics with potential application in wound dressings was synthesized using a laccase from Myceliophthora thermophila (MTL). The highest degree of cross-linking (49.7%) was achieved with catechol. All the phenolic-CMCS hydrogels synthesized showed excellent anti-oxidant properties with a free radical scavenging activity up to 4-fold higher than in the absence of the phenolics, as quantified by the di(phenyl)-(2,4,6-trinitrophenyl)iminoazanium (DPPH) assay. In addition, the hydrogels produced showed an anti-inflammatory effect as evidenced by the inhibition of enzymes [myeloperoxidase (MPO), matrix-metalloproteinase-1 (MMP-1) and human neutrophil elastase (HNE)] over-expressed in chronic wounds. Sinapyl-CMCS hydrogels showed an MMP-1 inhibition of 37%. Further, the phenolic-CMCS hydrogels did not affect the viability of the NIH 3T3 mouse fibroblast cell line and were also able to slowly release human fibroblast growth factor 2, reaching 48.3% over a period of 28days. This study thus shows the possibility of synthesizing multifunctional bioactive chitosan based hydrogels with anti-oxidant and anti-inflammatory properties using natural occurring phenolics as crosslinkers.</t>
-  </si>
-  <si>
-    <t>['Anti-inflammatory', 'Anti-oxidant', 'Chitosan hydrogel', 'Laccase', 'Phenolics', 'Wound enzymes']</t>
-  </si>
-  <si>
-    <t>2018 Jan 25</t>
-  </si>
-  <si>
-    <t>Immobilization of laccase on epoxy-functionalized silica and its application in biodegradation of phenolic compounds.</t>
-  </si>
-  <si>
-    <t>A novel method of laccase immobilization on epoxy-functionalized silica particles was developed. Laccase from Myceliophthora thermophila was covalently immobilized onto epoxy-functionalized matrix by nucleophilic attack of amino groups of laccase to epoxy groups of the support. The enzyme loading on the support was about 30 mg/g under the optimum conditions (pH 4.5, 24 h). The effect of pH, temperature and organic solvent on immobilized enzyme activity was determined and compared with those of free enzyme. In general the immobilized enzyme was found to be stabilized compared to the free enzyme. Lineweaver-Burk plots were used to calculate kinetic parameters for ABTS oxidation. K(M) values were 24.0 and 25.3 muM while v(max) values were 10.0 and 1.6 muM min(-1) for free and immobilized laccase, respectively. The performance of the biocatalyst was evaluated by the degradation of phenolic compounds including phenol, p-chlorophenol and catechol. The removal efficiency of catechol by immobilized laccase was about 95% after 2 h.</t>
-  </si>
-  <si>
-    <t>['Immobilization', 'Laccase', 'Phenol biodegradation']</t>
-  </si>
-  <si>
-    <t>Iran. Electronic address: m.mohammadi@nigeb.ac.ir</t>
-  </si>
-  <si>
-    <t>2018 Apr 1</t>
-  </si>
-  <si>
-    <t>Enhanced production of bacterial xylanase and its utility in saccharification of sugarcane bagasse.</t>
-  </si>
-  <si>
-    <t>An investigation was carried out using sugarcane bagasse as the agricultural residue to study the optimization of xylanase production by solid-state fermentation. Maximum xylanase production (20.35 U/g substrate) was achieved by Bacillus substilis subsp. subtilis JJBS250 using 'one variable at a time approach' at pH 7.0, 40  degrees C after 48 h. After statistical optimization by response surface methodology (RSM) there was 4.82-fold improvement in xylanase production (98.16 U/g substrate). Further optimization of untreated and sodium carbonate pretreated sugarcane bagasse enzymatic hydrolysis was carried out using both bacterial (Bacillus substilis subsp. subtilis JJBS250) and fungal (Myceliophthora thermophila BJTLRMDU3) xylanases that showed high amount of reducing sugar liberation from untreated sugarcane bagasse (124.24 mg/g substrate) as compared to pretreated (76.23 mg/g substrate) biomass. Furthermore, biophysical characterization of untreated and sodium carbonate pretreated sugarcane bagasse using Fourier-transform infrared spectroscopy (FTIR), X-ray diffraction (XRD) and scanning electron microscopy (SEM), revealed the structural changes in the pretreated biomass.</t>
-  </si>
-  <si>
-    <t>['Bacillus subtilis subsp. subtilis JJBS250', 'Pretreatment', 'Response surface methodology', 'Solid-state fermentation', 'Sugarcane bagasse', 'Xylanase']</t>
-  </si>
-  <si>
-    <t>2020 Jun</t>
-  </si>
-  <si>
-    <t>Isolation and characterization of a new cytotoxic polyketide-amino acid hybrid from Thermothelomyces thermophilus ATCC 42464.</t>
-  </si>
-  <si>
-    <t>Fungi are a rich source of novel anticancer compounds. Bioassay-guided isolation has led to the isolation of four polyketide-amino acid hybrid compounds with trans-fused decalin system from the fungus Thermothelomyces thermophilus ATCC 42464 (=Myceliophthora thermophila ATCC 42464): myceliothermophins A, B, E and F (1-4). The structure of the new compound (myceliothermophin F, compound 4) was clearly determined by a combination of nuclear magnetic resonance (NMR) analysis and high-resolution electrospray ionisation mass spectroscopy (HRESIMS). The new compound exhibited promising cytotoxicity against some cell lines derived from colorectal carcinoma, hepatic carcinoma and gastric carcinoma, indicating that compounds with trans-fused decalin system would be promising in the course of developing novel anticancer drugs.</t>
-  </si>
-  <si>
-    <t>['Polyketide-amino acid', 'Thermothelomyces thermophilus', 'anticancer', 'decalin', 'hybrid']</t>
-  </si>
-  <si>
-    <t>Natural product research</t>
-  </si>
-  <si>
-    <t>2021 Jun</t>
-  </si>
-  <si>
-    <t>Influence of mediators on laccase catalyzed radical formation in lignin.</t>
-  </si>
-  <si>
-    <t>Laccases (EC 1.10.3.2) catalyze oxidation of phenolic groups in lignin to phenoxyl radicals during reduction of O(2) to H(2)O. Here, we examine the influence on this radical formation of mediators which are presumed to act by shuttling electrons between the laccase and the subunits in lignin that the enzyme cannot approach directly. Treatments of three different lignins with laccase-mediator-systems (LMS) including laccases derived from Trametes versicolor and Myceliophthora thermophila, respectively, and four individual mediators, 1-hydroxybenzotriazole (HBT), N-hydroxyphthalimide (HPI), 2,2,6,6-tetramethylpiperidin-1-yloxy (TEMPO), and 2,2'-azino-bis(3-ethylbenzothiazoline-6-sulphonic acid) (ABTS) were assessed by real time electron paramagnetic resonance measurements. Radical steady state concentrations and radical formation rates were quantified. LMS treatments with 500 muM N-OH type mediators (HPI or HBT) did not affect the lignin radical formation, but increased doses of those mediators (5 mM) surprisingly led to significantly decreased radical formation rates and lowered steady state radical concentrations. Laccase-TEMPO treatment at a 5 mM mediator dose was the only system that significantly increased steady state radical concentration and rate of radical formation in beech organosolv lignin. The data suggest that electron shuttling by mediators is not a significant general mechanism for enhancing laccase catalyzed oxidation of biorefinery lignin substrates, and the results thus provide a new view on laccase catalyzed lignin modification.</t>
-  </si>
-  <si>
-    <t>['ABTS', 'Electron paramagnetic resonance (EPR)', 'HBT', 'HPI', 'Laccase-mediator systems', 'Myceliophthora thermophila', 'TEMPO', 'Trametes versicolor']</t>
-  </si>
-  <si>
-    <t>Selection of thermophilic and thermotolerant fungi for the production of cellulases and xylanases under solid-state fermentation.</t>
-  </si>
-  <si>
-    <t>Twenty-seven thermophilic and thermotolerant fungal strains were isolated from soil, decaying organic matter and sugarcane piles based on their ability to grow at 45 degrees C on medium containing corn straw and cardboard as carbon sources. These fungi were identified in the genera Aspergillus, Thermomyces, Myceliophthora, Thermomucor and Candida. The majority of the isolated strains produced xylanase and cellulases under solid state fermentation (SSF). The highest cellulase and xylanase productions were obtained by the cultivation of the strains identified as Aspergillus fumigatus M.7.1 and Myceliophthora thermophila M.7.7. The enzymes from these strains exhibited maximum activity at pH 5.0 and at 60 and 70 masculineC. The endo-glucanase from A. fumigatus was stable from 40 degrees C to 65 degrees C and both endo-glucanase and xylanase from M. thermophila were stable in this temperature range when in absence of substrate. The enzymes were stable from pH 4.0 to 9.0.</t>
-  </si>
-  <si>
-    <t>['Thermophilic fungi', 'cellulase', 'solid-state fermentation', 'xylanase']</t>
+    <t>2013 Jul 22</t>
+  </si>
+  <si>
+    <t>Boosting LPMO-driven lignocellulose degradation by polyphenol oxidase-activated lignin building blocks.</t>
+  </si>
+  <si>
+    <t>BACKGROUND: Many fungi boost the deconstruction of lignocellulosic plant biomass via oxidation using lytic polysaccharide monooxygenases (LPMOs). The application of LPMOs is expected to contribute to ecologically friendly conversion of biomass into fuels and chemicals. Moreover, applications of LPMO-modified cellulose-based products may be envisaged within the food or material industry. RESULTS: Here, we show an up to 75-fold improvement in LPMO-driven cellulose degradation using polyphenol oxidase-activated lignin building blocks. This concerted enzymatic process involves the initial conversion of monophenols into diphenols by the polyphenol oxidase MtPPO7 from Myceliophthora thermophila C1 and the subsequent oxidation of cellulose by MtLPMO9B. Interestingly, MtPPO7 shows preference towards lignin-derived methoxylated monophenols. Sequence analysis of genomes of 336 Ascomycota and 208 Basidiomycota reveals a high correlation between MtPPO7 and AA9 LPMO genes. CONCLUSIONS: The activity towards methoxylated phenolic compounds distinguishes MtPPO7 from well-known PPOs, such as tyrosinases, and ensures that MtPPO7 is an excellent redox partner of LPMOs. The correlation between MtPPO7 and AA9 LPMO genes is indicative for the importance of the coupled action of different monooxygenases in the concerted degradation of lignocellulosic biomass. These results will contribute to a better understanding in both lignin deconstruction and enzymatic lignocellulose oxidation and potentially improve the exploration of eco-friendly routes for biomass utilization in a circular economy.</t>
+  </si>
+  <si>
+    <t>['Agaricus bisporus', 'Ascomycota', 'Basidiomycota', 'Catechol oxidase', 'LPMO', 'Lignocellulose', 'Myceliophthora thermophila C1', 'PPO', 'Phenols', 'Polyphenol oxidase', 'Tyrosinase']</t>
+  </si>
+  <si>
+    <t>The Netherlands. ISNI: 0000 0001 0791 5666. GRID: grid.4818.5</t>
+  </si>
+  <si>
+    <t>Laccase multi-point covalent immobilization: characterization, kinetics, and its hydrophobicity applications.</t>
+  </si>
+  <si>
+    <t>Laccase from Myceliophthora thermophila was immobilized using one-point and multi-point covalent attachment on both a native and a modified new commercial epoxy carrier (Immobead 150P). After 10 cycles of operation at pH 3.0 and temperature 70  degrees C, the multi-point covalently immobilized laccase on the modified Immobead 150P performed best in terms of immobilization characteristics, retaining 95% of its initial activity. Thermodynamic parameters of thermal inactivation emphasized the positive impact of the immobilization procedure. At 50  degrees C, the immobilized and free enzyme activity levels dropped by 27 and 73%, respectively, after 48 h of incubation. The immobilized enzyme enhanced its stability in alkaline conditions, resuming 95% of its original activity after 3 h at pH 9.0. Immobilization reduced substrate affinity because the free laccase's K(m) value was lower than that of the immobilized laccase. Finally, the application of immobilized laccase in an innovative wood treatment process was tested by grafting lauryl gallate (LG) in order to provide hydrophobic properties to the wood. The results showed a relative water contact angle of 85.7% for treated wood, whereas the control showed only 26.6%, after 4 min of contact between water and beechwood surface. KEY POINTS: * Multi-point covalent immobilization of a commercial laccase on a commercial support. * Enzymatic parameters generally improved by immobilization process. * New application of immobilized laccase: enzymatic-assisted wood hydrophobization.</t>
+  </si>
+  <si>
+    <t>['Covalent immobilization', 'Grafting', 'Immobead 150P', 'Laccase', 'Thermodynamics', 'Wood hydrophobization']</t>
+  </si>
+  <si>
+    <t>Egypt. othmanam_nrc@yahoo.com</t>
+  </si>
+  <si>
+    <t>The influence of the primary and secondary xanthan structure on the enzymatic hydrolysis of the xanthan backbone.</t>
+  </si>
+  <si>
+    <t>Differently modified xanthans, varying in degree of acetylation and/or pyruvylation were incubated with the experimental cellulase mixture C1-G1 from Myceliophthora thermophila C1. The ionic strength and/or temperature of the xanthan solutions were varied, to obtain different xanthan conformations. The exact conformation at the selected incubation conditions was determined by circular dichroism. The xanthan degradation was analyzed by size exclusion chromatography. It was shown that at a fixed xanthan conformation, the backbone degradation by cellulases is equal for each type of xanthan. Complete backbone degradation is only obtained at a fully disordered conformation, indicating that only the secondary xanthan structure influences the final degree of hydrolysis by cellulases. It is thereby shown that, independently on the degree of substitution, xanthan can be completely hydrolyzed to oligosaccharides. These oligosaccharides can be used to further investigate the primary structure of different xanthans and to correlate the molecular structure to the xanthan functionalities.</t>
+  </si>
+  <si>
+    <t>['Cellulases', 'Circular dichroism', 'Conformation', 'Degree of substitution', 'HPSEC', 'Renatured xanthan']</t>
+  </si>
+  <si>
+    <t>2013 Sep 12</t>
+  </si>
+  <si>
+    <t>Effect of Metal Ions on the Activity of Ten NAD-Dependent Formate Dehydrogenases.</t>
+  </si>
+  <si>
+    <t>NAD-dependent formate dehydrogenase (FDH) enzymes are frequently used in industrial and scientific applications. FDH is a reversible enzyme that reduces the NAD molecule to NADH and produces CO(2) by oxidation of the formate ion, whereas it causes CO(2) reduction in the reverse reaction. Some transition metal elements - Fe(3+), Mo(6+) and W(6 +) - can be found in the FDH structure of anaerobic and archaeal microorganisms, and these enzymes require cations and other redox-active cofactors for their FDH activity. While NAD-dependent FDHs do not necessarily require any metal cations, the presence of various metal cations can still affect FDH activities. To study the effect of 11 different metal ions, NAD-dependent FDH enzymes from ten different microorganisms were tested: Ancylobacter aquaticus (AaFDH), Candida boidinii (CboFDH), Candida methylica (CmFDH), Ceriporiopsis subvermispora (CsFDH), Chaetomium thermophilum (CtFDH), Moraxella sp. (MsFDH), Myceliophthora thermophila (MtFDH), Paracoccus sp. (PsFDH), Saccharomyces cerevisiae (ScFDH) and Thiobacillus sp. (TsFDH). It was found that metal ions (mainly Cu(2+) and Zn(2+)) could have quite strong inhibition effects on several enzymes in the forward reaction, whereas several cations (Li(+), Mg(2+), Mn(2+), Fe(3+) and W(6+)) could increase the forward reaction of two FDHs. The highest activity increase (1.97 fold) was caused by Fe(3+) in AaFDH. The effect on the reverse reaction was minimal. The modelled structures of ten FDHs showed that the active site is formed by 15 highly conserved amino acid residues spatially settling around the formate binding site in a conserved way. However, the residue differences at some of the sites close to the substrate do not explain the activity differences. The active site space is very tight, excluding water molecules, as observed in earlier studies. Structural examination indicated that smaller metal ions might be spaced close to the active site to affect the reaction. Metal ion size showed partial correlation to the effect on inhibition or activation. Affinity of the substrate may also affect the sensitivity to the metal's effect. In addition, amino acid differences on the protein surface may also be important for the metal ion effect.</t>
+  </si>
+  <si>
+    <t>['Metal ion effect', 'NAD-dependent FDH', 'Reaction kinetics', 'Structural analysis']</t>
+  </si>
+  <si>
+    <t>The protein journal</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Autochthonous ascomycetes in depollution of polychlorinated biphenyls contaminated soil and sediment.</t>
+  </si>
+  <si>
+    <t>We investigated the capacity of a consortium of ascomycetous strains, Doratomyces nanus, Doratomyces purpureofuscus, Doratomyces verrucisporus, Myceliophthora thermophila, Phoma eupyrena and Thermoascus crustaceus in the mycoremediation of historically contaminated soil and sediment by polychlorinated biphenyls (PCBs). Analyses of 15 PCB concentrations in three mesocosms containing soil from which the fungal strains had previously been isolated, revealed significant PCB depletions of 16.9% for the 6 indicator PCBs (i-PCBs) and 18.7% for the total 15 PCBs analyzed after 6months treatment. The degradation rate did not statistically vary whether the soil had been treated with non-inoculated straw or colonized straw or without straw and inoculated with the consortium of the six strains. Concerning the sediment, we evidenced significant depletions of 31.8% for the 6 i-PCBs and 33.3% for the 15 PCB congeners. The PCB depletions affected most of the 15 PCBs analyzed without preference for lower chlorinated congeners. Bioaugmented strains were evidenced in different mesocosms, but their reintroduction, after six months treatment, did not improve the rate of PCB degradation, suggesting that the biodegradation could affect the bioavailable PCB fraction. Our results demonstrate that the ascomycetous strains potentially adapted to PCBs may be propitious to the remediation of PCB contaminated sites.</t>
+  </si>
+  <si>
+    <t>['Ascomycetous strains', 'Bioaugmentation', 'Mycoremediation', 'PCBs']</t>
+  </si>
+  <si>
+    <t>Chemosphere</t>
+  </si>
+  <si>
+    <t>2014 Sep</t>
+  </si>
+  <si>
+    <t>Filamentous fungi and media for cellulase production in solid state cultures.</t>
+  </si>
+  <si>
+    <t>Cellulase production was evaluated in two reference strains (T. reesei Rut-C30 and T. reesei QM9414), two strains isolated from a sugarcane cultivation area (Trichoderma sp. IPT778 and T. harzianum rifai IPT821) and one strain isolated in a program for biodiversity preservation in Sao Paulo state (Myceliophthora thermophila M77). Solid state cultures were performed using sugarcane bagasse (C), wheat bran (W) and/or soybean bran (S). The highest FPA was 10.6 U/gdm for M77 in SC (10:90) at 80% moisture, which was 4.4 times higher than production in pure W. C was a strong inducer of cellulase production, given that the production level of 6.1 U/gdm in WC (40:60) was 2.5 times higher than in pure W for strain M77; T. reesei Rut-C30 did not respond as strongly with about 1.6-fold surplus production. S advantageously replaced W, as the surplus production on SC (20:80) was 2.3 times relative to WC (20:80) for M77.</t>
+  </si>
+  <si>
+    <t>['Myceliophtora sp', 'cellulase', 'productivity', 'solid media', 'sugarcane bagasse']</t>
   </si>
   <si>
     <t>Brazilian journal of microbiology : [publication of the Brazilian Society for Microbiology]</t>
-  </si>
-  <si>
-    <t>Brasil</t>
-  </si>
-  <si>
-    <t>2012 Jul</t>
-  </si>
-  <si>
-    <t>Improving enzyme production by solid-state cultivation in packed-bed bioreactors by changing bed porosity and airflow distribution.</t>
-  </si>
-  <si>
-    <t>Enzymes production by solid-state cultivation in packed-bed bioreactor needs to be improved by mathematical modeling and also by experimentation. In this work, a mixture of sugarcane bagasse and wheat bran was used for the growth of the fungus Myceliophthora thermophila I-1D3b, able to secrete endoglucanase and xylanase, enzymes of interest in the second-generation ethanol production. Bench and pilot-scale bioreactors were used for the experiments, while critical parameters as bed porosity and airflow distribution were evaluated. Results showed enzymes with higher activities for the most porous medium, even though the less substrate amount to be cultivated. For the pilot-scale bioreactor, only the most porous medium was evaluated using different airflow distribution techniques. Using an inner tube for air supply resulted in more homogeneous enzyme production, with higher activities. The results here presented will be helpful for the scale-up of this class of bioreactor into industrial apparatuses.</t>
-  </si>
-  <si>
-    <t>['Cellulase', 'Fixed bioreactor', 'Packing density', 'Scale-up', 'Solid-state fermentation']</t>
-  </si>
-  <si>
-    <t>Brazil. lopesperezcaroline@gmail.com</t>
-  </si>
-  <si>
-    <t>2021 Mar</t>
-  </si>
-  <si>
-    <t>A novel fungal GH30 xylanase with xylobiohydrolase auxiliary activity.</t>
-  </si>
-  <si>
-    <t>BACKGROUND: The main representatives of hemicellulose are xylans, usually decorated beta-1,4-linked d-xylose polymers, which are hydrolyzed by xylanases. The efficient utilization and complete hydrolysis of xylans necessitate the understanding of the mode of action of xylan degrading enzymes. The glycoside hydrolase family 30 (GH30) xylanases comprise a less studied group of such enzymes, and differences regarding the substrate recognition have been reported between fungal and bacterial GH30 xylanases. Besides their role in the utilization of lignocellulosic biomass for bioenergy, such enzymes could be used for the tailored production of prebiotic xylooligosaccharides (XOS) due to their substrate specificity. RESULTS: The expression of a putative GH30_7 xylanase from the fungus Thermothelomyces thermophila (synonyms Myceliophthora thermophila, Sporotrichum thermophile) in Pichia pastoris resulted in the production and isolation of a novel xylanase with unique catalytic properties. The novel enzyme designated TtXyn30A, exhibited an endo- mode of action similar to that of bacterial GH30 xylanases that require 4-O-methyl-d-glucuronic acid (MeGlcA) decorations, in contrast to most characterized fungal ones. However, TtXyn30A also exhibited an exo-acting catalytic behavior by releasing the disaccharide xylobiose from the non-reducing end of XOS. The hydrolysis products from beechwood glucuronoxylan were MeGlcA substituted XOS, and xylobiose. The major uronic XOS (UXOS) were the aldotriuronic and aldotetrauronic acid after longer incubation indicating the ability of TtXyn30A to cleave linear parts of xylan and UXOS as well. CONCLUSIONS: Hereby, we reported the heterologous production and biochemical characterization of a novel fungal GH30 xylanase exhibiting endo- and exo-xylanase activity. To date, considering its novel catalytic properties, TtXyn30A shows differences with most characterized fungal and bacterial GH30 xylanases. The discovered xylobiohydrolase mode of action offers new insights into fungal enzymatic systems that are employed for the utilization of lignocellulosic biomass. The recombinant xylanase could be used for the production of X2 and UXOS from glucuronoxylan, which in turn would be utilized as prebiotics carrying manifold health benefits.</t>
-  </si>
-  <si>
-    <t>['GH30 xylanase', 'Glucuronoxylan', 'Thermothelomyces thermophila', 'Xylobiohydrolase', 'Xylooligosaccharides']</t>
-  </si>
-  <si>
-    <t>Greece. ISNI: 0000 0001 2185 9808. GRID: grid.4241.3</t>
-  </si>
-  <si>
-    <t>Polymer functionalization through an enzymatic process: Intermediate products characterization and their grafting onto gum Arabic.</t>
-  </si>
-  <si>
-    <t>The modification of gum Arabic with ferulic acid oxidation products was performed in aqueous medium, at 30  degrees C and pH 7.5, in the presence of Myceliophthora thermophila laccase as biocatalyst. First, this study aimed to investigate the structures of the oxidation products of ferulic acid that could possibly be covalently grafted onto gum Arabic. HPLC analyses revealed that this reaction produced several oxidation products, whose structures were investigated using LC-MS/MS analyses (liquid chromatography-mass spectrometry with mass fragmentation analyses) and NMR experiments. The chemical structure of one intermediate reaction product was fully elucidated as the 2-(4-hydroxy-3-methoxyphenyl)-4-[(4-hydroxy-3-methoxyphenyl) methylidene] cyclobutane-1, 3-dione, called by the authors cyclobutadiferulone. Secondly, this study aimed to locate the grafting of the oxidation products onto gum Arabic by performing several NMR experiments. This study did not determine how much and specifically which oxidation products were grafted but some of them were undeniably present onto modified gum Arabic, close to the glucuronic acid C5 carbon or close to the galactose C6 carbon.</t>
-  </si>
-  <si>
-    <t>['Ferulic acid', 'Functionalization', 'Gum Arabic', 'Oxidation product', 'Phenol grafting']</t>
-  </si>
-  <si>
-    <t>2021 Feb 1</t>
-  </si>
-  <si>
-    <t>N-Linked glycans are an important component of the processive machinery of cellobiohydrolases.</t>
-  </si>
-  <si>
-    <t>Cellobiohydrolases (CBHs), belonging to glycoside hydrolase families 6 and 7 (GH6 and GH7), are the major components of cellulase systems of filamentous fungi involved in biodegradation of cellulose in nature. Previous studies demonstrated that N-linked glycans in the catalytic domains of GH7 CBHs significantly affect the enzyme activity against cellulosic substrates. The influence of N-linked glycans on the activity and processivity of recombinant GH6 CBH II from Penicillium verruculosum (PvCel6A) was studied using site-directed mutagenesis of the respective Asn residues. Depending on the position of N-glycans on the surface of a protein globule, they affected the enzyme activity against cellulose either negatively or positively. The decrease or increase in the degree of processivity of recombinant forms of PvCel6A generally correlated with activity changes against Avicel. The mechanism of the N-glycan influence seems to be universal for GH6 and GH7 CBHs. The observed effects for CBHs from both families are explained in terms of a mechanistic model that also makes clear our previously published data on the highly active CBH IIb from Myceliophthora thermophila (MtCel6B). This study, together with data of other researchers, strongly suggests that the N-linked glycans in the catalytic domains of GH6 and GH7 CBHs are involved in processive catalytic machinery of these enzymes. Data obtained should be taken into account during development of new and more effective biocatalysts by protein engineering techniques.</t>
-  </si>
-  <si>
-    <t>['Cellobiohydrolase', 'Cloning', 'N-glycosylation', 'Processivity', 'Site-directed mutagenesis']</t>
-  </si>
-  <si>
-    <t>2017 Jan</t>
-  </si>
-  <si>
-    <t>Enzymatic versatility and thermostability of a new aryl-alcohol oxidase from Thermothelomyces thermophilus M77.</t>
-  </si>
-  <si>
-    <t>Background Fungal aryl-alcohol oxidases (AAOx) are extracellular flavoenzymes that belong to glucose-methanol-choline oxidoreductase family and are responsible for the selective conversion of primary aromatic alcohols into aldehydes and aromatic aldehydes to their corresponding acids, with concomitant production of hydrogen peroxide (H(2)O(2)) as by-product. The H(2)O(2) can be provided to lignin degradation pathway, a biotechnological property explored in biofuel production. In the thermophilic fungus Thermothelomyces thermophilus (formerly Myceliophthora thermophila), just one AAOx was identified in the exo-proteome. Methods The glycosylated and non-refolded crystal structure of an AAOx from T. thermophilus at 2.6 A resolution was elucidated by X-ray crystallography combined with small-angle X-ray scattering (SAXS) studies. Moreover, biochemical analyses were carried out to shed light on enzyme substrate specificity and thermostability. Results This flavoenzyme harbors a flavin adenine dinucleotide as a cofactor and is able to oxidize aromatic substrates and 5-HMF. Our results also show that the enzyme has similar oxidation rates for bulky or simple aromatic substrates such as cinnamyl and veratryl alcohols. Moreover, the crystal structure of MtAAOx reveals an open active site, which might explain observed specificity of the enzyme. Conclusions MtAAOx shows previously undescribed structural differences such as a fully accessible catalytic tunnel, heavy glycosylation and Ca(2+) binding site providing evidences for thermostability and activity of the enzymes from AA3_2 subfamily. General significance Structural and biochemical analyses of MtAAOx could be important for comprehension of aryl-alcohol oxidases structure-function relationships and provide additional molecular tools to be used in future biotechnological applications.</t>
-  </si>
-  <si>
-    <t>['AA3', 'AAOx', 'Aryl-alcohol oxidase', 'Thermostability', 'Thermothelomyces thermophilus', 'X-ray structure']</t>
-  </si>
-  <si>
-    <t>Brazil. Electronic address: marcokadowaki@gmail.com</t>
-  </si>
-  <si>
-    <t>2020 Oct</t>
-  </si>
-  <si>
-    <t>FTacV study of electroactive immobilized enzyme/free substrate reactions: Enzymatic catalysis of epinephrine by a multicopper oxidase from Thermothelomyces thermophila.</t>
-  </si>
-  <si>
-    <t>In the present work, a kinetic analysis is made concerning the reaction of an electroactive immobilized enzyme with a free substrate, based on a Michaelis-Menten scheme. The proposed kinetic equations are investigated numerically for conditions describing large amplitude fast Fourier transform alternating current voltammetry (FTacV), under different reaction states (transient or steady state for the reaction intermediate as well as quasi or complete reversibility of the electrochemical step). The dependence of two chief observables that occur from the analysis of the results of the method, that is, the maximum of the harmonics and the potential shift of the corresponding dominant peaks, on substrate concentration is presented. The FTacV method is applied experimentally for an immobilized laccase-like multicopper oxidase from Thermothelomyces thermophila, TtLMCO1, and its reaction with epinephrine. From the experimental findings it is shown that the intrinsic characteristics of the system do not lead to the extraction of the desired kinetic data although indications on the relation between the kinetic constants is revealed. Finally, the response of the third harmonic for the first additions of epinephrine at subnanomolarity range can be exploited for the detection of epinephrine at rather low concentrations.</t>
-  </si>
-  <si>
-    <t>['Direct electron transfer', 'Epinephrine', 'FTacV', 'Laccase', 'Multicopper oxidase', 'Thermothelomyces thermophila']</t>
-  </si>
-  <si>
-    <t>2020 Aug</t>
-  </si>
-  <si>
-    <t>Assessing the use of nanoimmobilized laccases to remove micropollutants from wastewater.</t>
-  </si>
-  <si>
-    <t>Enzymes immobilization is a useful way to allow enzyme reuse and increase their stability. A high redox potential laccase from Trametes versicolor (TvL) and a low redox potential, but commercially available low-cost laccase from Myceliophthora thermophila (MtL), were successfully immobilized and co-immobilized onto fumed silica nanoparticles (fsNP). Enzyme loads of 1.78 +/- 0.07, 0.69 +/- 0.03, and 1.10 +/- 0.01 U/mg fsNP were attained for the optimal doses of TvL, MtL, and co-immobilized laccases, respectively. In general, the laccase-fsNP conjugates showed a higher resistance against an acidic pH value (i.e., pH 3), and a higher storage stability than free enzymes. In addition, immobilized enzymes exhibited a superior long-term stability than free laccases when incubated in a secondary effluent from a municipal wastewater treatment plant (WWTP). For instance, the residual activity after 2 weeks for the co-immobilized laccases and the mixture of free laccases were 40.2 +/- 2.5% and 16.8 +/- 1.0%, respectively. The ability of the laccase-fsNP to remove a mixture of (14)C-bisphenol A (BPA) and (14)C-sodium diclofenac (DCF) from spiked secondary effluents was assessed in batch experiments. The catalytic efficiency was highly dependent on both the microbial source and state of the biocatalyst. The high redox potential TvL in free form attained a four-fold higher percentage of BPA transformation than the free MtL. Compared to free laccases, immobilized enzymes led to much slower rates of BPA transformation. For instance, after 24 h, the percentages of BPA transformation by 1000 U/L of a mixture of free laccases or co-immobilized enzymes were 67.8 +/- 5.2 and 27.0 +/- 3.9%, respectively. Nevertheless, the use of 8000 U/L of co-immobilized laccase led to a nearly complete removal of BPA, despite the unfavorable conditions for laccase catalysis (pH ~ 8.4). DCF transformation was not observed for any of the enzymatic systems, showing that this compound is highly recalcitrant toward laccase oxidation under realistic conditions.</t>
-  </si>
-  <si>
-    <t>['Enzyme immobilization', 'Fumed silica nanoparticles', 'Laccase', 'Micropollutants', 'Secondary effluent']</t>
-  </si>
-  <si>
-    <t>Environmental science and pollution research international</t>
-  </si>
-  <si>
-    <t>Spain. adriana.arca@rai.usc.es</t>
-  </si>
-  <si>
-    <t>2016 Feb</t>
-  </si>
-  <si>
-    <t>Membraneless glucose/oxygen enzymatic fuel cells using redox hydrogel films containing carbon nanotubes.</t>
-  </si>
-  <si>
-    <t>Co-immobilisation of three separate multiple blue copper oxygenases, a Myceliophthora thermophila laccase, a Streptomyces coelicolor laccase and a Myrothecium verrucaria bilirubin oxidase, with an [Os(2,2'-bipyridine)2 (polyvinylimidazole)10Cl](+/2+) redox polymer in the presence of multi-walled carbon nanotubes (MWCNTs) on graphite electrodes results in enzyme electrodes that produce current densities above 0.5 mA cm(-2) for oxygen reduction at an applied potential of 0 V versus Ag/AgCl. Fully enzymatic membraneless fuel cells are assembled with the oxygen-reducing enzyme electrodes connected to glucose-oxidising anodes based on co-immobilisation of glucose oxidase or a flavin adenine dinucleotide-dependent glucose dehydrogenase with an [Os(4,4'-dimethyl-2,2'-bipyridine)2(polyvinylimidazole)10Cl](+/2+) redox polymer in the presence of MWCNTs on graphite electrodes. These fuel cells can produce power densities of up to 145 muW cm(-2) on operation in pH 7.4 phosphate buffer solution at 37  degrees C containing 150 mM NaCl, 5 mM glucose and 0.12 mM O2. The fuel cells based on Myceliophthora thermophila laccase enzyme electrodes produce the highest power density if combined with glucose oxidase-based anodes. Although the maximum power density of a fuel cell of glucose dehydrogenase and Myceliophthora thermophila laccase enzyme electrodes decreases from 110 muW cm(-2) in buffer to 60 muW cm(-2) on testing in artificial plasma, it provides the highest power output reported to date for a fully enzymatic glucose-oxidising, oxygen-reducing fuel cell in artificial plasma.</t>
-  </si>
-  <si>
-    <t>['enzyme electrodes', 'fuel cells', 'glucose oxidation', 'oxygen reduction', 'redox chemistry']</t>
-  </si>
-  <si>
-    <t>Chemphyschem : a European journal of chemical physics and physical chemistry</t>
-  </si>
-  <si>
-    <t>2013 Jul 22</t>
-  </si>
-  <si>
-    <t>Boosting LPMO-driven lignocellulose degradation by polyphenol oxidase-activated lignin building blocks.</t>
-  </si>
-  <si>
-    <t>BACKGROUND: Many fungi boost the deconstruction of lignocellulosic plant biomass via oxidation using lytic polysaccharide monooxygenases (LPMOs). The application of LPMOs is expected to contribute to ecologically friendly conversion of biomass into fuels and chemicals. Moreover, applications of LPMO-modified cellulose-based products may be envisaged within the food or material industry. RESULTS: Here, we show an up to 75-fold improvement in LPMO-driven cellulose degradation using polyphenol oxidase-activated lignin building blocks. This concerted enzymatic process involves the initial conversion of monophenols into diphenols by the polyphenol oxidase MtPPO7 from Myceliophthora thermophila C1 and the subsequent oxidation of cellulose by MtLPMO9B. Interestingly, MtPPO7 shows preference towards lignin-derived methoxylated monophenols. Sequence analysis of genomes of 336 Ascomycota and 208 Basidiomycota reveals a high correlation between MtPPO7 and AA9 LPMO genes. CONCLUSIONS: The activity towards methoxylated phenolic compounds distinguishes MtPPO7 from well-known PPOs, such as tyrosinases, and ensures that MtPPO7 is an excellent redox partner of LPMOs. The correlation between MtPPO7 and AA9 LPMO genes is indicative for the importance of the coupled action of different monooxygenases in the concerted degradation of lignocellulosic biomass. These results will contribute to a better understanding in both lignin deconstruction and enzymatic lignocellulose oxidation and potentially improve the exploration of eco-friendly routes for biomass utilization in a circular economy.</t>
-  </si>
-  <si>
-    <t>['Agaricus bisporus', 'Ascomycota', 'Basidiomycota', 'Catechol oxidase', 'LPMO', 'Lignocellulose', 'Myceliophthora thermophila C1', 'PPO', 'Phenols', 'Polyphenol oxidase', 'Tyrosinase']</t>
-  </si>
-  <si>
-    <t>The Netherlands. ISNI: 0000 0001 0791 5666. GRID: grid.4818.5</t>
-  </si>
-  <si>
-    <t>Laccase multi-point covalent immobilization: characterization, kinetics, and its hydrophobicity applications.</t>
-  </si>
-  <si>
-    <t>Laccase from Myceliophthora thermophila was immobilized using one-point and multi-point covalent attachment on both a native and a modified new commercial epoxy carrier (Immobead 150P). After 10 cycles of operation at pH 3.0 and temperature 70  degrees C, the multi-point covalently immobilized laccase on the modified Immobead 150P performed best in terms of immobilization characteristics, retaining 95% of its initial activity. Thermodynamic parameters of thermal inactivation emphasized the positive impact of the immobilization procedure. At 50  degrees C, the immobilized and free enzyme activity levels dropped by 27 and 73%, respectively, after 48 h of incubation. The immobilized enzyme enhanced its stability in alkaline conditions, resuming 95% of its original activity after 3 h at pH 9.0. Immobilization reduced substrate affinity because the free laccase's K(m) value was lower than that of the immobilized laccase. Finally, the application of immobilized laccase in an innovative wood treatment process was tested by grafting lauryl gallate (LG) in order to provide hydrophobic properties to the wood. The results showed a relative water contact angle of 85.7% for treated wood, whereas the control showed only 26.6%, after 4 min of contact between water and beechwood surface. KEY POINTS: * Multi-point covalent immobilization of a commercial laccase on a commercial support. * Enzymatic parameters generally improved by immobilization process. * New application of immobilized laccase: enzymatic-assisted wood hydrophobization.</t>
-  </si>
-  <si>
-    <t>['Covalent immobilization', 'Grafting', 'Immobead 150P', 'Laccase', 'Thermodynamics', 'Wood hydrophobization']</t>
-  </si>
-  <si>
-    <t>Egypt. othmanam_nrc@yahoo.com</t>
-  </si>
-  <si>
-    <t>The influence of the primary and secondary xanthan structure on the enzymatic hydrolysis of the xanthan backbone.</t>
-  </si>
-  <si>
-    <t>Differently modified xanthans, varying in degree of acetylation and/or pyruvylation were incubated with the experimental cellulase mixture C1-G1 from Myceliophthora thermophila C1. The ionic strength and/or temperature of the xanthan solutions were varied, to obtain different xanthan conformations. The exact conformation at the selected incubation conditions was determined by circular dichroism. The xanthan degradation was analyzed by size exclusion chromatography. It was shown that at a fixed xanthan conformation, the backbone degradation by cellulases is equal for each type of xanthan. Complete backbone degradation is only obtained at a fully disordered conformation, indicating that only the secondary xanthan structure influences the final degree of hydrolysis by cellulases. It is thereby shown that, independently on the degree of substitution, xanthan can be completely hydrolyzed to oligosaccharides. These oligosaccharides can be used to further investigate the primary structure of different xanthans and to correlate the molecular structure to the xanthan functionalities.</t>
-  </si>
-  <si>
-    <t>['Cellulases', 'Circular dichroism', 'Conformation', 'Degree of substitution', 'HPSEC', 'Renatured xanthan']</t>
-  </si>
-  <si>
-    <t>2013 Sep 12</t>
-  </si>
-  <si>
-    <t>Effect of Metal Ions on the Activity of Ten NAD-Dependent Formate Dehydrogenases.</t>
-  </si>
-  <si>
-    <t>NAD-dependent formate dehydrogenase (FDH) enzymes are frequently used in industrial and scientific applications. FDH is a reversible enzyme that reduces the NAD molecule to NADH and produces CO(2) by oxidation of the formate ion, whereas it causes CO(2) reduction in the reverse reaction. Some transition metal elements - Fe(3+), Mo(6+) and W(6 +) - can be found in the FDH structure of anaerobic and archaeal microorganisms, and these enzymes require cations and other redox-active cofactors for their FDH activity. While NAD-dependent FDHs do not necessarily require any metal cations, the presence of various metal cations can still affect FDH activities. To study the effect of 11 different metal ions, NAD-dependent FDH enzymes from ten different microorganisms were tested: Ancylobacter aquaticus (AaFDH), Candida boidinii (CboFDH), Candida methylica (CmFDH), Ceriporiopsis subvermispora (CsFDH), Chaetomium thermophilum (CtFDH), Moraxella sp. (MsFDH), Myceliophthora thermophila (MtFDH), Paracoccus sp. (PsFDH), Saccharomyces cerevisiae (ScFDH) and Thiobacillus sp. (TsFDH). It was found that metal ions (mainly Cu(2+) and Zn(2+)) could have quite strong inhibition effects on several enzymes in the forward reaction, whereas several cations (Li(+), Mg(2+), Mn(2+), Fe(3+) and W(6+)) could increase the forward reaction of two FDHs. The highest activity increase (1.97 fold) was caused by Fe(3+) in AaFDH. The effect on the reverse reaction was minimal. The modelled structures of ten FDHs showed that the active site is formed by 15 highly conserved amino acid residues spatially settling around the formate binding site in a conserved way. However, the residue differences at some of the sites close to the substrate do not explain the activity differences. The active site space is very tight, excluding water molecules, as observed in earlier studies. Structural examination indicated that smaller metal ions might be spaced close to the active site to affect the reaction. Metal ion size showed partial correlation to the effect on inhibition or activation. Affinity of the substrate may also affect the sensitivity to the metal's effect. In addition, amino acid differences on the protein surface may also be important for the metal ion effect.</t>
-  </si>
-  <si>
-    <t>['Metal ion effect', 'NAD-dependent FDH', 'Reaction kinetics', 'Structural analysis']</t>
-  </si>
-  <si>
-    <t>The protein journal</t>
-  </si>
-  <si>
-    <t>Turkey</t>
-  </si>
-  <si>
-    <t>Autochthonous ascomycetes in depollution of polychlorinated biphenyls contaminated soil and sediment.</t>
-  </si>
-  <si>
-    <t>We investigated the capacity of a consortium of ascomycetous strains, Doratomyces nanus, Doratomyces purpureofuscus, Doratomyces verrucisporus, Myceliophthora thermophila, Phoma eupyrena and Thermoascus crustaceus in the mycoremediation of historically contaminated soil and sediment by polychlorinated biphenyls (PCBs). Analyses of 15 PCB concentrations in three mesocosms containing soil from which the fungal strains had previously been isolated, revealed significant PCB depletions of 16.9% for the 6 indicator PCBs (i-PCBs) and 18.7% for the total 15 PCBs analyzed after 6months treatment. The degradation rate did not statistically vary whether the soil had been treated with non-inoculated straw or colonized straw or without straw and inoculated with the consortium of the six strains. Concerning the sediment, we evidenced significant depletions of 31.8% for the 6 i-PCBs and 33.3% for the 15 PCB congeners. The PCB depletions affected most of the 15 PCBs analyzed without preference for lower chlorinated congeners. Bioaugmented strains were evidenced in different mesocosms, but their reintroduction, after six months treatment, did not improve the rate of PCB degradation, suggesting that the biodegradation could affect the bioavailable PCB fraction. Our results demonstrate that the ascomycetous strains potentially adapted to PCBs may be propitious to the remediation of PCB contaminated sites.</t>
-  </si>
-  <si>
-    <t>['Ascomycetous strains', 'Bioaugmentation', 'Mycoremediation', 'PCBs']</t>
-  </si>
-  <si>
-    <t>Chemosphere</t>
-  </si>
-  <si>
-    <t>2014 Sep</t>
-  </si>
-  <si>
-    <t>Filamentous fungi and media for cellulase production in solid state cultures.</t>
-  </si>
-  <si>
-    <t>Cellulase production was evaluated in two reference strains (T. reesei Rut-C30 and T. reesei QM9414), two strains isolated from a sugarcane cultivation area (Trichoderma sp. IPT778 and T. harzianum rifai IPT821) and one strain isolated in a program for biodiversity preservation in Sao Paulo state (Myceliophthora thermophila M77). Solid state cultures were performed using sugarcane bagasse (C), wheat bran (W) and/or soybean bran (S). The highest FPA was 10.6 U/gdm for M77 in SC (10:90) at 80% moisture, which was 4.4 times higher than production in pure W. C was a strong inducer of cellulase production, given that the production level of 6.1 U/gdm in WC (40:60) was 2.5 times higher than in pure W for strain M77; T. reesei Rut-C30 did not respond as strongly with about 1.6-fold surplus production. S advantageously replaced W, as the surplus production on SC (20:80) was 2.3 times relative to WC (20:80) for M77.</t>
-  </si>
-  <si>
-    <t>['Myceliophtora sp', 'cellulase', 'productivity', 'solid media', 'sugarcane bagasse']</t>
   </si>
   <si>
     <t>Departamento de Engenharia Quimica Universidade de Sao Paulo Sao PauloSP Brazil</t>
@@ -2112,7 +2070,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2122,13 +2080,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2183,7 +2135,7 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -2497,19 +2449,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="35.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="444.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2532,7 +2484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
         <v>25025273</v>
       </c>
@@ -2555,7 +2507,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3">
         <v>32640074</v>
       </c>
@@ -2578,7 +2530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3">
         <v>35450635</v>
       </c>
@@ -2601,7 +2553,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3">
         <v>24995002</v>
       </c>
@@ -2624,7 +2576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3">
         <v>31534479</v>
       </c>
@@ -2647,7 +2599,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3">
         <v>34735642</v>
       </c>
@@ -2670,7 +2622,7 @@
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3">
         <v>35257374</v>
       </c>
@@ -2693,7 +2645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3">
         <v>27807811</v>
       </c>
@@ -2716,7 +2668,7 @@
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3">
         <v>34489043</v>
       </c>
@@ -2739,7 +2691,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3">
         <v>31078793</v>
       </c>
@@ -2762,7 +2714,7 @@
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3">
         <v>33413029</v>
       </c>
@@ -2785,7 +2737,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3">
         <v>36478865</v>
       </c>
@@ -2808,7 +2760,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3">
         <v>31802333</v>
       </c>
@@ -2831,7 +2783,7 @@
         <v>75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3">
         <v>33995328</v>
       </c>
@@ -2854,7 +2806,7 @@
         <v>79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3">
         <v>36238990</v>
       </c>
@@ -2877,7 +2829,7 @@
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3">
         <v>36174898</v>
       </c>
@@ -2900,7 +2852,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3">
         <v>36165620</v>
       </c>
@@ -2923,7 +2875,7 @@
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3">
         <v>35608343</v>
       </c>
@@ -2946,7 +2898,7 @@
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3">
         <v>36799667</v>
       </c>
@@ -2969,7 +2921,7 @@
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3">
         <v>31114738</v>
       </c>
@@ -2992,7 +2944,7 @@
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3">
         <v>36691040</v>
       </c>
@@ -3015,7 +2967,7 @@
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3">
         <v>30974557</v>
       </c>
@@ -3038,7 +2990,7 @@
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3">
         <v>27629413</v>
       </c>
@@ -3061,7 +3013,7 @@
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3">
         <v>29359934</v>
       </c>
@@ -3084,7 +3036,7 @@
         <v>133</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3">
         <v>31381927</v>
       </c>
@@ -3107,7 +3059,7 @@
         <v>138</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3">
         <v>27128897</v>
       </c>
@@ -3130,7 +3082,7 @@
         <v>144</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3">
         <v>29303991</v>
       </c>
@@ -3153,7 +3105,7 @@
         <v>149</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3">
         <v>29222836</v>
       </c>
@@ -3176,7 +3128,7 @@
         <v>154</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3">
         <v>33765291</v>
       </c>
@@ -3199,7 +3151,7 @@
         <v>159</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3">
         <v>32984289</v>
       </c>
@@ -3222,7 +3174,7 @@
         <v>164</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3">
         <v>29943052</v>
       </c>
@@ -3245,7 +3197,7 @@
         <v>169</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3">
         <v>29843921</v>
       </c>
@@ -3268,7 +3220,7 @@
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="3">
         <v>30534201</v>
       </c>
@@ -3291,7 +3243,7 @@
         <v>178</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="3">
         <v>32253539</v>
       </c>
@@ -3314,7 +3266,7 @@
         <v>182</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="3">
         <v>31911243</v>
       </c>
@@ -3337,7 +3289,7 @@
         <v>188</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="3">
         <v>27193267</v>
       </c>
@@ -3360,7 +3312,7 @@
         <v>193</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="3">
         <v>29527447</v>
       </c>
@@ -3383,7 +3335,7 @@
         <v>198</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="3">
         <v>32021654</v>
       </c>
@@ -3406,7 +3358,7 @@
         <v>164</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="3">
         <v>29687143</v>
       </c>
@@ -3429,7 +3381,7 @@
         <v>207</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="3">
         <v>25824435</v>
       </c>
@@ -3452,7 +3404,7 @@
         <v>213</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="3">
         <v>31890021</v>
       </c>
@@ -3475,7 +3427,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="3">
         <v>31754437</v>
       </c>
@@ -3498,7 +3450,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="3">
         <v>25541341</v>
       </c>
@@ -3521,7 +3473,7 @@
         <v>227</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="3">
         <v>28278111</v>
       </c>
@@ -3544,7 +3496,7 @@
         <v>231</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="3">
         <v>34556173</v>
       </c>
@@ -3567,7 +3519,7 @@
         <v>235</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="3">
         <v>31407106</v>
       </c>
@@ -3590,7 +3542,7 @@
         <v>239</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3">
         <v>24881579</v>
       </c>
@@ -3613,7 +3565,7 @@
         <v>245</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="3">
         <v>28477154</v>
       </c>
@@ -3636,7 +3588,7 @@
         <v>250</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
       <c r="A50" s="3">
         <v>31786675</v>
       </c>
@@ -3822,7 +3774,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3">
-        <v>23638383</v>
+        <v>36966330</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>285</v>
@@ -3834,33 +3786,33 @@
         <v>287</v>
       </c>
       <c r="E58" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>289</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="3">
-        <v>36966330</v>
+        <v>28515785</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="D59" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>293</v>
@@ -3868,7 +3820,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3">
-        <v>28515785</v>
+        <v>36686237</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>294</v>
@@ -3880,64 +3832,64 @@
         <v>296</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>297</v>
+        <v>46</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>298</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3">
-        <v>25919617</v>
+        <v>24692305</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="F61" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3">
-        <v>36686237</v>
+        <v>28078397</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="D62" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3">
-        <v>24692305</v>
+        <v>26047916</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>307</v>
@@ -3949,56 +3901,56 @@
         <v>309</v>
       </c>
       <c r="E63" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>312</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3">
-        <v>28078397</v>
+        <v>28501686</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="E64" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>316</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3">
-        <v>26047916</v>
+        <v>27286691</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="D65" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="F65" s="4" t="s">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>320</v>
@@ -4006,7 +3958,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3">
-        <v>28501686</v>
+        <v>35205873</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>321</v>
@@ -4018,10 +3970,10 @@
         <v>323</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>87</v>
+        <v>324</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>324</v>
+        <v>226</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>325</v>
@@ -4029,7 +3981,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3">
-        <v>27286691</v>
+        <v>26722808</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>326</v>
@@ -4041,33 +3993,33 @@
         <v>328</v>
       </c>
       <c r="E67" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="G67" s="4" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3">
-        <v>35205873</v>
+        <v>32624738</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="D68" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="E68" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="F68" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>335</v>
@@ -4075,7 +4027,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="3">
-        <v>26722808</v>
+        <v>31235519</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>336</v>
@@ -4087,110 +4039,110 @@
         <v>338</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>339</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3">
-        <v>32624738</v>
+        <v>28053662</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>343</v>
+        <v>34</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>344</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3">
-        <v>31235519</v>
+        <v>35127677</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="D71" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>348</v>
-      </c>
       <c r="E71" s="4" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>349</v>
+        <v>46</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>350</v>
+        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3">
-        <v>28053662</v>
+        <v>28777990</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>298</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3">
-        <v>35127677</v>
+        <v>36546909</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="F73" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="G73" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3">
-        <v>28777990</v>
+        <v>30961066</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>358</v>
@@ -4202,125 +4154,125 @@
         <v>360</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="3">
-        <v>36546909</v>
+        <v>34560965</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>365</v>
+        <v>22</v>
       </c>
       <c r="F75" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3">
-        <v>30961066</v>
+        <v>34336809</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="D76" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>371</v>
-      </c>
       <c r="G76" s="4" t="s">
-        <v>372</v>
+        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3">
-        <v>34560965</v>
+        <v>36542100</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="E77" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>374</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>376</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3">
-        <v>34336809</v>
+        <v>34155677</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="E78" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="F78" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3">
-        <v>36542100</v>
+        <v>29317354</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="F79" s="4" t="s">
-        <v>46</v>
+        <v>370</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>384</v>
@@ -4328,7 +4280,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="3">
-        <v>34155677</v>
+        <v>34921331</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>385</v>
@@ -4340,102 +4292,102 @@
         <v>387</v>
       </c>
       <c r="E80" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3">
-        <v>29317354</v>
+        <v>28591592</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="D81" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>392</v>
-      </c>
       <c r="E81" s="4" t="s">
-        <v>393</v>
+        <v>137</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>380</v>
+        <v>11</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>394</v>
+        <v>351</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3">
-        <v>34921331</v>
+        <v>36162644</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E82" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="F82" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="G82" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>398</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3">
-        <v>28591592</v>
+        <v>36560529</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="E83" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="E83" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="F83" s="4" t="s">
-        <v>11</v>
+        <v>402</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>361</v>
+        <v>403</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3">
-        <v>36162644</v>
+        <v>35056890</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>405</v>
+        <v>142</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>406</v>
+        <v>226</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>407</v>
@@ -4443,7 +4395,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3">
-        <v>36560529</v>
+        <v>29435681</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>408</v>
@@ -4455,582 +4407,582 @@
         <v>410</v>
       </c>
       <c r="E85" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3">
-        <v>35056890</v>
+        <v>35155404</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="E86" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>226</v>
-      </c>
       <c r="G86" s="4" t="s">
-        <v>417</v>
+        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3">
-        <v>29435681</v>
+        <v>34771228</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="E87" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="G87" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3">
-        <v>35155404</v>
+        <v>25941560</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="D88" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="E88" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>425</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>79</v>
+        <v>426</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3">
-        <v>34771228</v>
+        <v>28649275</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>429</v>
+        <v>301</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>430</v>
+        <v>293</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3">
-        <v>25941560</v>
+        <v>35757805</v>
       </c>
       <c r="B90" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="D90" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="E90" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F90" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="G90" s="4" t="s">
-        <v>436</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3">
-        <v>28649275</v>
+        <v>34513809</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>311</v>
+        <v>46</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>298</v>
+        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3">
-        <v>35757805</v>
+        <v>29196788</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>443</v>
+        <v>132</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3">
-        <v>34513809</v>
+        <v>28710860</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>46</v>
+        <v>301</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>79</v>
+        <v>351</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3">
-        <v>29196788</v>
+        <v>35214607</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>168</v>
+        <v>401</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>154</v>
+        <v>446</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="3">
-        <v>28710860</v>
+        <v>28648174</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="3">
-        <v>35214607</v>
+        <v>30960948</v>
       </c>
       <c r="B96" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G96" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="3">
-        <v>28648174</v>
+        <v>26907693</v>
       </c>
       <c r="B97" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="G97" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>325</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="3">
-        <v>30960948</v>
+        <v>28935560</v>
       </c>
       <c r="B98" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="D98" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="G98" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>463</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="3">
-        <v>26907693</v>
+        <v>29274421</v>
       </c>
       <c r="B99" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="D99" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="E99" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F99" s="4" t="s">
+      <c r="G99" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>468</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="3">
-        <v>28935560</v>
+        <v>32065289</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C100" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="D100" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="E100" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>472</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="3">
-        <v>29274421</v>
+        <v>31309856</v>
       </c>
       <c r="B101" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="D101" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="E101" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="E101" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="F101" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G101" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>477</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="3">
-        <v>32065289</v>
+        <v>29887016</v>
       </c>
       <c r="B102" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="D102" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D102" s="4" t="s">
-        <v>480</v>
-      </c>
       <c r="E102" s="4" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>11</v>
+        <v>425</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>481</v>
+        <v>169</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="3">
-        <v>31309856</v>
+        <v>33222033</v>
       </c>
       <c r="B103" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="E103" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="G103" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>486</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="3">
-        <v>29887016</v>
+        <v>31110561</v>
       </c>
       <c r="B104" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="E104" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F104" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="G104" s="4" t="s">
-        <v>169</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="3">
-        <v>24031929</v>
+        <v>33352160</v>
       </c>
       <c r="B105" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="D105" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="E105" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G105" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>495</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="3">
-        <v>33222033</v>
+        <v>27856189</v>
       </c>
       <c r="B106" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G106" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="3">
-        <v>31110561</v>
+        <v>32653619</v>
       </c>
       <c r="B107" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="G107" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="3">
-        <v>33352160</v>
+        <v>32380451</v>
       </c>
       <c r="B108" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G108" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>508</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="3">
-        <v>27856189</v>
+        <v>26490891</v>
       </c>
       <c r="B109" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="F109" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="G109" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>512</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="3">
-        <v>32653619</v>
+        <v>23788272</v>
       </c>
       <c r="B110" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="D110" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="E110" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>516</v>
@@ -5041,7 +4993,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="3">
-        <v>32380451</v>
+        <v>28491137</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>518</v>
@@ -5053,18 +5005,18 @@
         <v>520</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>267</v>
+        <v>34</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>192</v>
+        <v>521</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>521</v>
+        <v>293</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="3">
-        <v>26490891</v>
+        <v>36602562</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>522</v>
@@ -5076,110 +5028,110 @@
         <v>524</v>
       </c>
       <c r="E112" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="F112" s="4" t="s">
-        <v>526</v>
-      </c>
       <c r="G112" s="4" t="s">
-        <v>527</v>
+        <v>374</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="3">
-        <v>23788272</v>
+        <v>23911459</v>
       </c>
       <c r="B113" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="E113" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="3">
-        <v>28491137</v>
+        <v>33043425</v>
       </c>
       <c r="B114" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E114" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="F114" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>536</v>
-      </c>
       <c r="G114" s="4" t="s">
-        <v>298</v>
+        <v>501</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="3">
-        <v>36602562</v>
+        <v>24880600</v>
       </c>
       <c r="B115" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="F115" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G115" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="3">
-        <v>23911459</v>
+        <v>24948946</v>
       </c>
       <c r="B116" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="D116" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="E116" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="F116" s="4" t="s">
-        <v>132</v>
+        <v>544</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>544</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="3">
-        <v>33043425</v>
+        <v>33712158</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>545</v>
@@ -5191,110 +5143,110 @@
         <v>547</v>
       </c>
       <c r="E117" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G117" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>517</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="3">
-        <v>24880600</v>
+        <v>31641526</v>
       </c>
       <c r="B118" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C118" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="D118" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="E118" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F118" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="E118" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>366</v>
-      </c>
       <c r="G118" s="4" t="s">
-        <v>554</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="3">
-        <v>24948946</v>
+        <v>23795296</v>
       </c>
       <c r="B119" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="E119" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="F119" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="G119" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="3">
-        <v>33712158</v>
+        <v>32300998</v>
       </c>
       <c r="B120" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="D120" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="D120" s="4" t="s">
-        <v>561</v>
-      </c>
       <c r="E120" s="4" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>562</v>
+        <v>182</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="3">
-        <v>31641526</v>
+        <v>34153346</v>
       </c>
       <c r="B121" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="E121" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="F121" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F121" s="4" t="s">
+      <c r="G121" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="3">
-        <v>23795296</v>
+        <v>26909078</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>567</v>
@@ -5306,87 +5258,87 @@
         <v>569</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>570</v>
+        <v>28</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>443</v>
+        <v>29</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>571</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="3">
-        <v>32300998</v>
+        <v>30125627</v>
       </c>
       <c r="B123" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="E123" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F123" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="D123" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="G123" s="4" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="3">
-        <v>34153346</v>
+        <v>28576392</v>
       </c>
       <c r="B124" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="D124" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="E124" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="E124" s="4" t="s">
+      <c r="F124" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G124" s="4" t="s">
         <v>578</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>580</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="3">
-        <v>26909078</v>
+        <v>30966676</v>
       </c>
       <c r="B125" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="E125" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F125" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="G125" s="4" t="s">
         <v>583</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="3">
-        <v>30125627</v>
+        <v>32866595</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>584</v>
@@ -5398,18 +5350,18 @@
         <v>586</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="F126" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G126" s="4" t="s">
         <v>587</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>260</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="3">
-        <v>28576392</v>
+        <v>30465791</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>588</v>
@@ -5424,7 +5376,7 @@
         <v>591</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="G127" s="4" t="s">
         <v>592</v>
@@ -5432,7 +5384,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="3">
-        <v>30966676</v>
+        <v>33521846</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>593</v>
@@ -5444,102 +5396,102 @@
         <v>595</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="F128" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G128" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>597</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="3">
-        <v>32866595</v>
+        <v>25644433</v>
       </c>
       <c r="B129" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="C129" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="D129" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="E129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G129" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>601</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="3">
-        <v>30465791</v>
+        <v>31131710</v>
       </c>
       <c r="B130" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="D130" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="D130" s="4" t="s">
-        <v>604</v>
-      </c>
       <c r="E130" s="4" t="s">
-        <v>605</v>
+        <v>103</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>226</v>
+        <v>17</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>606</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="3">
-        <v>33521846</v>
+        <v>34168079</v>
       </c>
       <c r="B131" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E131" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="F131" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="G131" s="4" t="s">
         <v>609</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="G131" s="4" t="s">
-        <v>610</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="3">
-        <v>25644433</v>
+        <v>33292403</v>
       </c>
       <c r="B132" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="C132" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="D132" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="E132" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F132" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>614</v>
@@ -5547,7 +5499,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="3">
-        <v>31131710</v>
+        <v>36771814</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>615</v>
@@ -5559,30 +5511,30 @@
         <v>617</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>17</v>
+        <v>301</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>36</v>
+        <v>618</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="3">
-        <v>34168079</v>
+        <v>34771293</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>621</v>
+        <v>119</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>622</v>
@@ -5593,7 +5545,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="3">
-        <v>33292403</v>
+        <v>29100178</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>624</v>
@@ -5605,10 +5557,10 @@
         <v>626</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>34</v>
+        <v>627</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>627</v>
+        <v>187</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>628</v>
@@ -5616,7 +5568,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="3">
-        <v>36771814</v>
+        <v>28859815</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>629</v>
@@ -5628,179 +5580,179 @@
         <v>631</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>311</v>
+        <v>425</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>632</v>
+        <v>351</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="3">
-        <v>34771293</v>
+        <v>32871114</v>
       </c>
       <c r="B137" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="D137" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="E137" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="E137" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="F137" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>636</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="3">
-        <v>29100178</v>
+        <v>28750348</v>
       </c>
       <c r="B138" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C138" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="D138" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="D138" s="4" t="s">
+      <c r="E138" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="F138" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="E138" s="4" t="s">
+      <c r="G138" s="4" t="s">
         <v>641</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>642</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="3">
-        <v>28859815</v>
+        <v>26185526</v>
       </c>
       <c r="B139" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="C139" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="D139" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="D139" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="E139" s="4" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>435</v>
+        <v>132</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>361</v>
+        <v>426</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
       <c r="A140" s="3">
-        <v>32871114</v>
+        <v>30396396</v>
       </c>
       <c r="B140" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="D140" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="D140" s="4" t="s">
-        <v>648</v>
-      </c>
       <c r="E140" s="4" t="s">
-        <v>649</v>
+        <v>55</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>650</v>
+        <v>592</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="3">
-        <v>28750348</v>
+        <v>33905799</v>
       </c>
       <c r="B141" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G141" s="4" t="s">
         <v>651</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="G141" s="4" t="s">
-        <v>655</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="3">
-        <v>26185526</v>
+        <v>28884503</v>
       </c>
       <c r="B142" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="G142" s="4" t="s">
         <v>656</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>436</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="3">
-        <v>30396396</v>
+        <v>24128582</v>
       </c>
       <c r="B143" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="D143" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="E143" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="D143" s="4" t="s">
+      <c r="F143" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G143" s="4" t="s">
         <v>661</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>606</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="3">
-        <v>33905799</v>
+        <v>34489024</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>662</v>
@@ -5812,18 +5764,18 @@
         <v>664</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>29</v>
+        <v>665</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>665</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="3">
-        <v>28884503</v>
+        <v>33461124</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>666</v>
@@ -5835,149 +5787,80 @@
         <v>668</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>310</v>
+        <v>87</v>
       </c>
       <c r="F145" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G145" s="4" t="s">
         <v>669</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>670</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="3">
-        <v>24128582</v>
+        <v>33741634</v>
       </c>
       <c r="B146" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="D146" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="E146" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G146" s="4" t="s">
         <v>673</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>675</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="3">
-        <v>34489024</v>
+        <v>33807631</v>
       </c>
       <c r="B147" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="E147" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="F147" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" s="4" t="s">
         <v>678</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="G147" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="3">
-        <v>33461124</v>
+        <v>36866191</v>
       </c>
       <c r="B148" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="D148" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="E148" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="E148" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="F148" s="4"/>
       <c r="G148" s="4" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
-      <c r="A149" s="3">
-        <v>33741634</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
-      <c r="A150" s="3">
-        <v>33807631</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
-      <c r="A151" s="3">
-        <v>36866191</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="F151" s="4"/>
-      <c r="G151" s="4" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/code/Get_Paper_info/Mt_Paper_filter.xlsx
+++ b/code/Get_Paper_info/Mt_Paper_filter.xlsx
@@ -2455,7 +2455,7 @@
     <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="444.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="21.290714285714284" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
